--- a/reportes/cults3d_mercado.xlsx
+++ b/reportes/cults3d_mercado.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>126034</v>
+        <v>126035</v>
       </c>
     </row>
     <row r="5">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1862282.66</v>
+        <v>1862293.89</v>
       </c>
     </row>
     <row r="6">
@@ -886,7 +886,7 @@
         <v>254205</v>
       </c>
       <c r="H7" t="n">
-        <v>0.265661252900232</v>
+        <v>0.2656415694591728</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -932,7 +932,7 @@
         <v>224260</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2656415694591728</v>
+        <v>0.2653534183082271</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -978,7 +978,7 @@
         <v>224260</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2656415694591728</v>
+        <v>0.2653534183082271</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1024,7 +1024,7 @@
         <v>224260</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2656415694591728</v>
+        <v>0.2653534183082271</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1070,7 +1070,7 @@
         <v>243665</v>
       </c>
       <c r="H11" t="n">
-        <v>0.266235973466049</v>
+        <v>0.2662261317455195</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>319315.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2656514111797024</v>
+        <v>0.2654974938837</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1254,7 +1254,7 @@
         <v>254205</v>
       </c>
       <c r="H15" t="n">
-        <v>0.265661252900232</v>
+        <v>0.2656415694591728</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -1668,7 +1668,7 @@
         <v>255407.58</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2637475088675174</v>
+        <v>0.2636034332920446</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1806,7 +1806,7 @@
         <v>440715</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3086522462562396</v>
+        <v>0.3083604777415853</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -3367,7 +3367,7 @@
         <v>3.96</v>
       </c>
       <c r="G61" t="n">
-        <v>31586.68</v>
+        <v>31597.91</v>
       </c>
       <c r="H61" t="n">
         <v>0.03709285622964752</v>
@@ -3600,7 +3600,7 @@
         <v>281235</v>
       </c>
       <c r="H66" t="n">
-        <v>0.265661252900232</v>
+        <v>0.2656415694591728</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -4488,7 +4488,7 @@
         <v>11.23</v>
       </c>
       <c r="F4" t="n">
-        <v>48039.85</v>
+        <v>48051.08</v>
       </c>
       <c r="G4" t="n">
         <v>0.0267175572519084</v>
@@ -4644,7 +4644,7 @@
         <v>11.23</v>
       </c>
       <c r="F2" t="n">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="G2" t="n">
         <v>177</v>
@@ -4664,13 +4664,13 @@
         <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>60.28571428571428</v>
+        <v>60.35714285714285</v>
       </c>
       <c r="M2" t="n">
-        <v>9478.120000000001</v>
+        <v>9489.35</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03303973380309258</v>
+        <v>0.03307888040712468</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
@@ -5494,12 +5494,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Frieren Bust 3D Print</t>
+          <t>Claire Bust 3D Print</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020434</t>
+          <t>https://cults3d.com/:5020453</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46301.76526620371</v>
+        <v>46301.76777777778</v>
       </c>
       <c r="E17" t="n">
         <v>15</v>
@@ -5517,17 +5517,17 @@
         <v>417</v>
       </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>980</v>
+        <v>783</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3dprint, anime, fanart, fantasy, figurine, frieren, mage, stl</t>
+          <t>claire, evil, female, figure, handgun, jacket, re, redfield, resident, survivor, veronica</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -5540,7 +5540,7 @@
         <v>6255</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4255102040816326</v>
+        <v>0.5325670498084292</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -5552,12 +5552,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Claire Bust 3D Print</t>
+          <t>Frieren Bust 3D Print</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020453</t>
+          <t>https://cults3d.com/:5020434</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46301.76777777778</v>
+        <v>46301.76526620371</v>
       </c>
       <c r="E18" t="n">
         <v>15</v>
@@ -5575,17 +5575,17 @@
         <v>417</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H18" t="n">
-        <v>783</v>
+        <v>980</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>claire, evil, female, figure, handgun, jacket, re, redfield, resident, survivor, veronica</t>
+          <t>3dprint, anime, fanart, fantasy, figurine, frieren, mage, stl</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -5598,7 +5598,7 @@
         <v>6255</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5325670498084292</v>
+        <v>0.4255102040816326</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -5842,12 +5842,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Anakin Ronin Bust 3D Print</t>
+          <t>Shanoa Bust 3D Print</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5021462</t>
+          <t>https://cults3d.com/:5020467</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46301.93331018519</v>
+        <v>46301.77025462963</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
@@ -5865,17 +5865,17 @@
         <v>412</v>
       </c>
       <c r="G23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>1256</v>
+        <v>753</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ahsoka, anakin, clone, darth, jedi, lightsaber, maul, rebels, sith, star, stormtrooper, tano, vader, wars</t>
+          <t>boss, castlevania, dracul, dracula, king, shanoa, vampire</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -5888,10 +5888,10 @@
         <v>6180</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3280254777070064</v>
+        <v>0.547144754316069</v>
       </c>
       <c r="O23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
@@ -5900,12 +5900,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shanoa Bust 3D Print</t>
+          <t>Anakin Ronin Bust 3D Print</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020467</t>
+          <t>https://cults3d.com/:5021462</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46301.77025462963</v>
+        <v>46301.93331018519</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
@@ -5923,17 +5923,17 @@
         <v>412</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H24" t="n">
-        <v>753</v>
+        <v>1256</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>boss, castlevania, dracul, dracula, king, shanoa, vampire</t>
+          <t>ahsoka, anakin, clone, darth, jedi, lightsaber, maul, rebels, sith, star, stormtrooper, tano, vader, wars</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -5946,10 +5946,10 @@
         <v>6180</v>
       </c>
       <c r="N24" t="n">
-        <v>0.547144754316069</v>
+        <v>0.3280254777070064</v>
       </c>
       <c r="O24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="b">
         <v>0</v>
@@ -6158,7 +6158,7 @@
         <v>19</v>
       </c>
       <c r="H28" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -6178,7 +6178,7 @@
         <v>5680</v>
       </c>
       <c r="N28" t="n">
-        <v>0.308695652173913</v>
+        <v>0.3083604777415853</v>
       </c>
       <c r="O28" t="b">
         <v>1</v>
@@ -6912,7 +6912,7 @@
         <v>18</v>
       </c>
       <c r="H41" t="n">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -6932,7 +6932,7 @@
         <v>4580</v>
       </c>
       <c r="N41" t="n">
-        <v>0.265661252900232</v>
+        <v>0.2653534183082271</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
@@ -8104,12 +8104,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Savage Land Psylocke Bust 3D Print</t>
+          <t>Cowgirl Rogue Bust 3D Print</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4878923</t>
+          <t>https://cults3d.com/:4878931</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8118,7 +8118,7 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46271.73194444444</v>
+        <v>46271.73293981481</v>
       </c>
       <c r="E62" t="n">
         <v>15</v>
@@ -8127,17 +8127,17 @@
         <v>679</v>
       </c>
       <c r="G62" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H62" t="n">
-        <v>1831</v>
+        <v>1790</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>art, comics, fan, female, figure, figurine, game, garage, kit, miniature, miniatures, movie, psylocke, savage, sculpture, stylized, tabletop, video, xmen</t>
+          <t>cosplay, costume, cowboy, cowgirl, marvel, parts, rebel, rivals, rogue, starlit</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -8150,7 +8150,7 @@
         <v>10185</v>
       </c>
       <c r="N62" t="n">
-        <v>0.3708356089568542</v>
+        <v>0.3793296089385475</v>
       </c>
       <c r="O62" t="b">
         <v>1</v>
@@ -8162,12 +8162,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cowgirl Rogue Bust 3D Print</t>
+          <t>Savage Land Psylocke Bust 3D Print</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4878931</t>
+          <t>https://cults3d.com/:4878923</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46271.73293981481</v>
+        <v>46271.73194444444</v>
       </c>
       <c r="E63" t="n">
         <v>15</v>
@@ -8185,17 +8185,17 @@
         <v>679</v>
       </c>
       <c r="G63" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H63" t="n">
-        <v>1790</v>
+        <v>1831</v>
       </c>
       <c r="I63" t="b">
         <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>cosplay, costume, cowboy, cowgirl, marvel, parts, rebel, rivals, rogue, starlit</t>
+          <t>art, comics, fan, female, figure, figurine, game, garage, kit, miniature, miniatures, movie, psylocke, savage, sculpture, stylized, tabletop, video, xmen</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -8208,7 +8208,7 @@
         <v>10185</v>
       </c>
       <c r="N63" t="n">
-        <v>0.3793296089385475</v>
+        <v>0.3708356089568542</v>
       </c>
       <c r="O63" t="b">
         <v>1</v>
@@ -8478,7 +8478,7 @@
         <v>22</v>
       </c>
       <c r="H68" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
@@ -8498,7 +8498,7 @@
         <v>3980</v>
       </c>
       <c r="N68" t="n">
-        <v>0.3080495356037152</v>
+        <v>0.3075734157650695</v>
       </c>
       <c r="O68" t="b">
         <v>1</v>
@@ -8536,7 +8536,7 @@
         <v>18</v>
       </c>
       <c r="H69" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I69" t="b">
         <v>0</v>
@@ -8556,7 +8556,7 @@
         <v>3980</v>
       </c>
       <c r="N69" t="n">
-        <v>0.3114241001564945</v>
+        <v>0.3109375</v>
       </c>
       <c r="O69" t="b">
         <v>1</v>
@@ -9844,12 +9844,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Big Daddy and Little Sister - BioShock - Bust</t>
+          <t>Deku - My Hero Academia - Bust</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971763</t>
+          <t>https://cults3d.com/:4971767</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46292.21859953704</v>
+        <v>46292.21883101852</v>
       </c>
       <c r="E92" t="n">
         <v>13.49</v>
@@ -9867,17 +9867,17 @@
         <v>306</v>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H92" t="n">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="I92" t="b">
         <v>0</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>big daddy, bioshock, bust, fanart, miniature, resin, stl</t>
+          <t>bust, deku, fanart, miniature, my hero academia, resin, stl</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -9890,7 +9890,7 @@
         <v>4127.940000000001</v>
       </c>
       <c r="N92" t="n">
-        <v>0.6035502958579881</v>
+        <v>0.6144578313253012</v>
       </c>
       <c r="O92" t="b">
         <v>0</v>
@@ -9902,12 +9902,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Deku - My Hero Academia - Bust</t>
+          <t>Big Daddy and Little Sister - BioShock - Bust</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971767</t>
+          <t>https://cults3d.com/:4971763</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9916,7 +9916,7 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46292.21883101852</v>
+        <v>46292.21859953704</v>
       </c>
       <c r="E93" t="n">
         <v>13.49</v>
@@ -9925,17 +9925,17 @@
         <v>306</v>
       </c>
       <c r="G93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="I93" t="b">
         <v>0</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>bust, deku, fanart, miniature, my hero academia, resin, stl</t>
+          <t>big daddy, bioshock, bust, fanart, miniature, resin, stl</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -9948,7 +9948,7 @@
         <v>4127.940000000001</v>
       </c>
       <c r="N93" t="n">
-        <v>0.6144578313253012</v>
+        <v>0.6035502958579881</v>
       </c>
       <c r="O93" t="b">
         <v>0</v>
@@ -10018,12 +10018,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Proxima the Broodseeker</t>
+          <t>pin head Fan art (no ams-multiparts/3mf)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5079132</t>
+          <t>https://cults3d.com/:5055346</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10032,42 +10032,42 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46313.49111111111</v>
+        <v>46308.81805555556</v>
       </c>
       <c r="E95" t="n">
-        <v>17.6</v>
+        <v>3.96</v>
       </c>
       <c r="F95" t="n">
         <v>158</v>
       </c>
       <c r="G95" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="H95" t="n">
-        <v>948</v>
+        <v>3223</v>
       </c>
       <c r="I95" t="b">
         <v>0</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>blasphemous, bloodborne, broodseeker, dark souls, elden ring, eredrim, h3llcreator, hadern, lady maria, lords of the fallen, malenia, mortal shell, mortal shell ii, proxima, tiel</t>
+          <t>3d print, 3mf, decor, decor master, decormaster, gift, multipart, no ams, toy</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L95" t="n">
         <v>11.28571428571429</v>
       </c>
       <c r="M95" t="n">
-        <v>2780.8</v>
+        <v>625.6799999999999</v>
       </c>
       <c r="N95" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.04902264970524356</v>
       </c>
       <c r="O95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P95" t="b">
         <v>0</v>
@@ -10076,12 +10076,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>pin head Fan art (no ams-multiparts/3mf)</t>
+          <t>Proxima the Broodseeker</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5055346</t>
+          <t>https://cults3d.com/:5079132</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10090,42 +10090,42 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46308.81805555556</v>
+        <v>46313.49111111111</v>
       </c>
       <c r="E96" t="n">
-        <v>3.96</v>
+        <v>17.6</v>
       </c>
       <c r="F96" t="n">
         <v>158</v>
       </c>
       <c r="G96" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="H96" t="n">
-        <v>3223</v>
+        <v>949</v>
       </c>
       <c r="I96" t="b">
         <v>0</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>3d print, 3mf, decor, decor master, decormaster, gift, multipart, no ams, toy</t>
+          <t>blasphemous, bloodborne, broodseeker, dark souls, elden ring, eredrim, h3llcreator, hadern, lady maria, lords of the fallen, malenia, mortal shell, mortal shell ii, proxima, tiel</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L96" t="n">
         <v>11.28571428571429</v>
       </c>
       <c r="M96" t="n">
-        <v>625.6799999999999</v>
+        <v>2780.8</v>
       </c>
       <c r="N96" t="n">
-        <v>0.04902264970524356</v>
+        <v>0.166491043203372</v>
       </c>
       <c r="O96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" t="b">
         <v>0</v>
@@ -19174,12 +19174,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Spider Demon P2  (Head-Swap) by E.S Monster</t>
+          <t>ONI P2 (Head-Swap) by E.S Monster</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4780086</t>
+          <t>https://cults3d.com/:4780060</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -19188,7 +19188,7 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46248.29128472223</v>
+        <v>46248.28496527778</v>
       </c>
       <c r="E253" t="n">
         <v>20</v>
@@ -19197,17 +19197,17 @@
         <v>237</v>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H253" t="n">
-        <v>749</v>
+        <v>657</v>
       </c>
       <c r="I253" t="b">
         <v>0</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>3d model, character, fanart, female, myth-inspired, sculpt, spider demon, stl</t>
+          <t>3d model, character, fanart, female, myth-inspired, oni, sculpt, stl</t>
         </is>
       </c>
       <c r="K253" t="n">
@@ -19220,10 +19220,10 @@
         <v>4740</v>
       </c>
       <c r="N253" t="n">
-        <v>0.3164218958611482</v>
+        <v>0.3607305936073059</v>
       </c>
       <c r="O253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P253" t="b">
         <v>0</v>
@@ -19232,12 +19232,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ONI P2 (Head-Swap) by E.S Monster</t>
+          <t>Spider Demon P2  (Head-Swap) by E.S Monster</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4780060</t>
+          <t>https://cults3d.com/:4780086</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -19246,7 +19246,7 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46248.28496527778</v>
+        <v>46248.29128472223</v>
       </c>
       <c r="E254" t="n">
         <v>20</v>
@@ -19255,17 +19255,17 @@
         <v>237</v>
       </c>
       <c r="G254" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H254" t="n">
-        <v>657</v>
+        <v>749</v>
       </c>
       <c r="I254" t="b">
         <v>0</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>3d model, character, fanart, female, myth-inspired, oni, sculpt, stl</t>
+          <t>3d model, character, fanart, female, myth-inspired, sculpt, spider demon, stl</t>
         </is>
       </c>
       <c r="K254" t="n">
@@ -19278,10 +19278,10 @@
         <v>4740</v>
       </c>
       <c r="N254" t="n">
-        <v>0.3607305936073059</v>
+        <v>0.3164218958611482</v>
       </c>
       <c r="O254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P254" t="b">
         <v>0</v>

--- a/reportes/cults3d_mercado.xlsx
+++ b/reportes/cults3d_mercado.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>126035</v>
+        <v>126051</v>
       </c>
     </row>
     <row r="5">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1862293.89</v>
+        <v>1862517.81</v>
       </c>
     </row>
     <row r="6">
@@ -748,7 +748,7 @@
         <v>82770</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3242366056882185</v>
+        <v>0.3241628009411123</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -794,7 +794,7 @@
         <v>101262.96</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3104166666666667</v>
+        <v>0.3102012491325468</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -840,7 +840,7 @@
         <v>68361.77</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3203791469194313</v>
+        <v>0.3197729422894986</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -883,10 +883,10 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>254205</v>
+        <v>254385</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2656415694591728</v>
+        <v>0.2665121668597914</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -929,10 +929,10 @@
         <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>224260</v>
+        <v>224440</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2653534183082271</v>
+        <v>0.2655007949125596</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -975,10 +975,10 @@
         <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>224260</v>
+        <v>224440</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2653534183082271</v>
+        <v>0.2655007949125596</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1021,10 +1021,10 @@
         <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>224260</v>
+        <v>224440</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2653534183082271</v>
+        <v>0.2655007949125596</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1067,10 +1067,10 @@
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>243665</v>
+        <v>243845</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2662261317455195</v>
+        <v>0.2666614304458287</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1159,10 +1159,10 @@
         <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>319315.3</v>
+        <v>319495.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2654974938837</v>
+        <v>0.2660064808861755</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1205,7 +1205,7 @@
         <v>17.5</v>
       </c>
       <c r="G14" t="n">
-        <v>179194.32</v>
+        <v>179214.32</v>
       </c>
       <c r="H14" t="n">
         <v>0.3517095395911514</v>
@@ -1251,10 +1251,10 @@
         <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>254205</v>
+        <v>254385</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2656415694591728</v>
+        <v>0.2665121668597914</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -1389,7 +1389,7 @@
         <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>39560</v>
+        <v>39640</v>
       </c>
       <c r="H18" t="n">
         <v>0.1838750796685787</v>
@@ -1435,7 +1435,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>63540</v>
+        <v>63558</v>
       </c>
       <c r="H19" t="n">
         <v>0.2458253214077384</v>
@@ -1484,7 +1484,7 @@
         <v>8706</v>
       </c>
       <c r="H20" t="n">
-        <v>0.05819104810524661</v>
+        <v>0.05817959918536833</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1527,10 +1527,10 @@
         <v>20</v>
       </c>
       <c r="G21" t="n">
-        <v>413819.26</v>
+        <v>413999.26</v>
       </c>
       <c r="H21" t="n">
-        <v>0.261853448275862</v>
+        <v>0.2617124394184168</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -1573,7 +1573,7 @@
         <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>47336.09</v>
+        <v>47354.09</v>
       </c>
       <c r="H22" t="n">
         <v>0.1418237624806511</v>
@@ -1619,10 +1619,10 @@
         <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>527947.1800000001</v>
+        <v>528127.1800000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3184115523465704</v>
+        <v>0.3179524152847873</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1665,10 +1665,10 @@
         <v>20</v>
       </c>
       <c r="G24" t="n">
-        <v>255407.58</v>
+        <v>255587.58</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2636034332920446</v>
+        <v>0.2636066171654882</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1803,10 +1803,10 @@
         <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>440715</v>
+        <v>440895</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3083604777415853</v>
+        <v>0.3091190108191654</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -1852,7 +1852,7 @@
         <v>61904.14</v>
       </c>
       <c r="H28" t="n">
-        <v>0.299982825085666</v>
+        <v>0.2997740431553964</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -1987,10 +1987,10 @@
         <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>240019.39</v>
+        <v>240199.39</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2560024044036942</v>
+        <v>0.2559406323513077</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -2033,7 +2033,7 @@
         <v>20</v>
       </c>
       <c r="G32" t="n">
-        <v>75160</v>
+        <v>75180</v>
       </c>
       <c r="H32" t="n">
         <v>0.2580046403712297</v>
@@ -2404,7 +2404,7 @@
         <v>51868.82</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2637475088675174</v>
+        <v>0.2636066171654882</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -2579,13 +2579,13 @@
         <v>7</v>
       </c>
       <c r="E44" t="n">
-        <v>6.457142857142857</v>
+        <v>6.471428571428572</v>
       </c>
       <c r="F44" t="n">
         <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>19830</v>
+        <v>19848</v>
       </c>
       <c r="H44" t="n">
         <v>0.05508702673604881</v>
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>6.45714</v>
+        <v>6.47143</v>
       </c>
     </row>
     <row r="45">
@@ -2625,13 +2625,13 @@
         <v>18</v>
       </c>
       <c r="E45" t="n">
-        <v>6.361224489795918</v>
+        <v>6.368367346938776</v>
       </c>
       <c r="F45" t="n">
         <v>6</v>
       </c>
       <c r="G45" t="n">
-        <v>35754</v>
+        <v>35772</v>
       </c>
       <c r="H45" t="n">
         <v>0.05411289662793629</v>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>6.36122</v>
+        <v>6.36837</v>
       </c>
     </row>
     <row r="46">
@@ -2677,7 +2677,7 @@
         <v>4.35</v>
       </c>
       <c r="G46" t="n">
-        <v>36412.05</v>
+        <v>36452.05</v>
       </c>
       <c r="H46" t="n">
         <v>0.05226881102814474</v>
@@ -2769,7 +2769,7 @@
         <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>39758.1</v>
+        <v>39776.1</v>
       </c>
       <c r="H48" t="n">
         <v>0.05313876651982379</v>
@@ -2861,10 +2861,10 @@
         <v>6</v>
       </c>
       <c r="G50" t="n">
-        <v>39606</v>
+        <v>39624</v>
       </c>
       <c r="H50" t="n">
-        <v>0.05138862686391634</v>
+        <v>0.05138517639212377</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
@@ -2907,10 +2907,10 @@
         <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>25824</v>
+        <v>25842</v>
       </c>
       <c r="H51" t="n">
-        <v>0.04834041265615138</v>
+        <v>0.0483369621843588</v>
       </c>
       <c r="I51" t="n">
         <v>1</v>
@@ -2953,10 +2953,10 @@
         <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>39606</v>
+        <v>39624</v>
       </c>
       <c r="H52" t="n">
-        <v>0.05138862686391634</v>
+        <v>0.05138517639212377</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
@@ -2993,16 +2993,16 @@
         <v>12</v>
       </c>
       <c r="E53" t="n">
-        <v>6.125510204081633</v>
+        <v>6.13265306122449</v>
       </c>
       <c r="F53" t="n">
         <v>6</v>
       </c>
       <c r="G53" t="n">
-        <v>27048</v>
+        <v>27066</v>
       </c>
       <c r="H53" t="n">
-        <v>0.05138862686391634</v>
+        <v>0.05138517639212377</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>6.12551</v>
+        <v>6.13265</v>
       </c>
     </row>
     <row r="54">
@@ -3039,13 +3039,13 @@
         <v>18</v>
       </c>
       <c r="E54" t="n">
-        <v>6.361224489795918</v>
+        <v>6.368367346938776</v>
       </c>
       <c r="F54" t="n">
         <v>6</v>
       </c>
       <c r="G54" t="n">
-        <v>35754</v>
+        <v>35772</v>
       </c>
       <c r="H54" t="n">
         <v>0.05411289662793629</v>
@@ -3066,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>5.88413</v>
+        <v>5.89074</v>
       </c>
     </row>
     <row r="55">
@@ -3137,7 +3137,7 @@
         <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>28223.76</v>
+        <v>28241.76</v>
       </c>
       <c r="H56" t="n">
         <v>0.04704233810429386</v>
@@ -3361,13 +3361,13 @@
         <v>22</v>
       </c>
       <c r="E61" t="n">
-        <v>5.012419871794872</v>
+        <v>5.025240384615385</v>
       </c>
       <c r="F61" t="n">
         <v>3.96</v>
       </c>
       <c r="G61" t="n">
-        <v>31597.91</v>
+        <v>31605.83</v>
       </c>
       <c r="H61" t="n">
         <v>0.03709285622964752</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>5.01242</v>
+        <v>5.02524</v>
       </c>
     </row>
     <row r="62">
@@ -3459,10 +3459,10 @@
         <v>9</v>
       </c>
       <c r="G63" t="n">
-        <v>70389.39</v>
+        <v>70407.39</v>
       </c>
       <c r="H63" t="n">
-        <v>0.03267750213857998</v>
+        <v>0.03300838036599966</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -3499,16 +3499,16 @@
         <v>26</v>
       </c>
       <c r="E64" t="n">
-        <v>5.012419871794872</v>
+        <v>5.025240384615385</v>
       </c>
       <c r="F64" t="n">
         <v>3.96</v>
       </c>
       <c r="G64" t="n">
-        <v>24241.88</v>
+        <v>24249.8</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0394332729914571</v>
+        <v>0.03943029431917119</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -3526,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>4.74676</v>
+        <v>4.7589</v>
       </c>
     </row>
     <row r="65">
@@ -3597,10 +3597,10 @@
         <v>20</v>
       </c>
       <c r="G66" t="n">
-        <v>281235</v>
+        <v>281415</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2656415694591728</v>
+        <v>0.2665121668597914</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -3729,16 +3729,16 @@
         <v>26</v>
       </c>
       <c r="E69" t="n">
-        <v>4.489441930618401</v>
+        <v>4.502262443438914</v>
       </c>
       <c r="F69" t="n">
         <v>3.96</v>
       </c>
       <c r="G69" t="n">
-        <v>26512.52</v>
+        <v>26520.44</v>
       </c>
       <c r="H69" t="n">
-        <v>0.03820960558431202</v>
+        <v>0.03820662691202611</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
@@ -3756,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>4.2515</v>
+        <v>4.26364</v>
       </c>
     </row>
     <row r="70">
@@ -3775,13 +3775,13 @@
         <v>26</v>
       </c>
       <c r="E70" t="n">
-        <v>4.489441930618401</v>
+        <v>4.502262443438914</v>
       </c>
       <c r="F70" t="n">
         <v>3.96</v>
       </c>
       <c r="G70" t="n">
-        <v>26654.48</v>
+        <v>26662.4</v>
       </c>
       <c r="H70" t="n">
         <v>0.03730029702167829</v>
@@ -3802,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.2515</v>
+        <v>4.26364</v>
       </c>
     </row>
     <row r="71">
@@ -3830,7 +3830,7 @@
         <v>11958.76</v>
       </c>
       <c r="H71" t="n">
-        <v>0.03544776119402985</v>
+        <v>0.03543307086614173</v>
       </c>
       <c r="I71" t="n">
         <v>1</v>
@@ -3873,10 +3873,10 @@
         <v>3.96</v>
       </c>
       <c r="G72" t="n">
-        <v>19000.08</v>
+        <v>19008</v>
       </c>
       <c r="H72" t="n">
-        <v>0.038978905533476</v>
+        <v>0.03897294818890417</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
@@ -3919,10 +3919,10 @@
         <v>3.96</v>
       </c>
       <c r="G73" t="n">
-        <v>19000.08</v>
+        <v>19008</v>
       </c>
       <c r="H73" t="n">
-        <v>0.038978905533476</v>
+        <v>0.03897294818890417</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
@@ -3959,13 +3959,13 @@
         <v>27</v>
       </c>
       <c r="E74" t="n">
-        <v>4.743589743589744</v>
+        <v>4.769230769230769</v>
       </c>
       <c r="F74" t="n">
         <v>3.96</v>
       </c>
       <c r="G74" t="n">
-        <v>27907.62</v>
+        <v>27915.54</v>
       </c>
       <c r="H74" t="n">
         <v>0.0398876404494382</v>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>4.08423</v>
+        <v>4.10631</v>
       </c>
     </row>
     <row r="75">
@@ -4005,13 +4005,13 @@
         <v>35</v>
       </c>
       <c r="E75" t="n">
-        <v>5.28125</v>
+        <v>5.3125</v>
       </c>
       <c r="F75" t="n">
         <v>3.96</v>
       </c>
       <c r="G75" t="n">
-        <v>95117.62</v>
+        <v>95143.53999999999</v>
       </c>
       <c r="H75" t="n">
         <v>0.03593056116269681</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.84475</v>
+        <v>3.8675</v>
       </c>
     </row>
     <row r="76">
@@ -4057,10 +4057,10 @@
         <v>3.96</v>
       </c>
       <c r="G76" t="n">
-        <v>21768</v>
+        <v>21775.92</v>
       </c>
       <c r="H76" t="n">
-        <v>0.038978905533476</v>
+        <v>0.03897294818890417</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
@@ -4103,10 +4103,10 @@
         <v>9</v>
       </c>
       <c r="G77" t="n">
-        <v>23300.46</v>
+        <v>23318.46</v>
       </c>
       <c r="H77" t="n">
-        <v>0.03053539641243325</v>
+        <v>0.03052285792499316</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -4198,7 +4198,7 @@
         <v>19761.93</v>
       </c>
       <c r="H79" t="n">
-        <v>0.02359235691290688</v>
+        <v>0.02358272004578713</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -4432,10 +4432,10 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1713329.21</v>
+        <v>1713553.13</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2547225122266763</v>
+        <v>0.2546607401742899</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
         <v>54461</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03025768911055694</v>
+        <v>0.03024260551678298</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -4650,7 +4650,7 @@
         <v>177</v>
       </c>
       <c r="H2" t="n">
-        <v>25545</v>
+        <v>25584</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4670,7 +4670,7 @@
         <v>9489.35</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03307888040712468</v>
+        <v>0.03302845528455284</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
@@ -4708,7 +4708,7 @@
         <v>1056</v>
       </c>
       <c r="H3" t="n">
-        <v>279743</v>
+        <v>279756</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>30120.96</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01212541511315743</v>
+        <v>0.01212485165644347</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -4766,7 +4766,7 @@
         <v>111</v>
       </c>
       <c r="H4" t="n">
-        <v>44426</v>
+        <v>44437</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4786,7 +4786,7 @@
         <v>6016</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01692702471525683</v>
+        <v>0.01692283457479128</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -4998,7 +4998,7 @@
         <v>36</v>
       </c>
       <c r="H8" t="n">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -5018,7 +5018,7 @@
         <v>15760</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3411255411255411</v>
+        <v>0.3409779316313284</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -5494,12 +5494,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Claire Bust 3D Print</t>
+          <t>Frieren Bust 3D Print</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020453</t>
+          <t>https://cults3d.com/:5020434</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46301.76777777778</v>
+        <v>46301.76526620371</v>
       </c>
       <c r="E17" t="n">
         <v>15</v>
@@ -5517,17 +5517,17 @@
         <v>417</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
-        <v>783</v>
+        <v>980</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>claire, evil, female, figure, handgun, jacket, re, redfield, resident, survivor, veronica</t>
+          <t>3dprint, anime, fanart, fantasy, figurine, frieren, mage, stl</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -5540,7 +5540,7 @@
         <v>6255</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5325670498084292</v>
+        <v>0.4255102040816326</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -5552,12 +5552,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Frieren Bust 3D Print</t>
+          <t>Strahd von Zarovich Bust3D Print</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020434</t>
+          <t>https://cults3d.com/:5020486</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46301.76526620371</v>
+        <v>46301.77325231482</v>
       </c>
       <c r="E18" t="n">
         <v>15</v>
@@ -5575,17 +5575,17 @@
         <v>417</v>
       </c>
       <c r="G18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H18" t="n">
-        <v>980</v>
+        <v>812</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3dprint, anime, fanart, fantasy, figurine, frieren, mage, stl</t>
+          <t>barovia, castle, dark, king, lord, noble, ruler, sinister, strahd, undead, vampire, villain, von, zarovich</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -5598,10 +5598,10 @@
         <v>6255</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4255102040816326</v>
+        <v>0.5135467980295566</v>
       </c>
       <c r="O18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -5610,12 +5610,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Strahd von Zarovich Bust3D Print</t>
+          <t>Claire Bust 3D Print</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020486</t>
+          <t>https://cults3d.com/:5020453</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5624,7 +5624,7 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46301.77325231482</v>
+        <v>46301.76777777778</v>
       </c>
       <c r="E19" t="n">
         <v>15</v>
@@ -5633,17 +5633,17 @@
         <v>417</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>barovia, castle, dark, king, lord, noble, ruler, sinister, strahd, undead, vampire, villain, von, zarovich</t>
+          <t>claire, evil, female, figure, handgun, jacket, re, redfield, resident, survivor, veronica</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -5656,10 +5656,10 @@
         <v>6255</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5135467980295566</v>
+        <v>0.5325670498084292</v>
       </c>
       <c r="O19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
@@ -5842,12 +5842,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shanoa Bust 3D Print</t>
+          <t>Anakin Ronin Bust 3D Print</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020467</t>
+          <t>https://cults3d.com/:5021462</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46301.77025462963</v>
+        <v>46301.93331018519</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
@@ -5865,17 +5865,17 @@
         <v>412</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H23" t="n">
-        <v>753</v>
+        <v>1256</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>boss, castlevania, dracul, dracula, king, shanoa, vampire</t>
+          <t>ahsoka, anakin, clone, darth, jedi, lightsaber, maul, rebels, sith, star, stormtrooper, tano, vader, wars</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -5888,10 +5888,10 @@
         <v>6180</v>
       </c>
       <c r="N23" t="n">
-        <v>0.547144754316069</v>
+        <v>0.3280254777070064</v>
       </c>
       <c r="O23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
@@ -5900,12 +5900,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Anakin Ronin Bust 3D Print</t>
+          <t>Shanoa Bust 3D Print</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5021462</t>
+          <t>https://cults3d.com/:5020467</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46301.93331018519</v>
+        <v>46301.77025462963</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
@@ -5923,17 +5923,17 @@
         <v>412</v>
       </c>
       <c r="G24" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>1256</v>
+        <v>753</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>ahsoka, anakin, clone, darth, jedi, lightsaber, maul, rebels, sith, star, stormtrooper, tano, vader, wars</t>
+          <t>boss, castlevania, dracul, dracula, king, shanoa, vampire</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -5946,10 +5946,10 @@
         <v>6180</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3280254777070064</v>
+        <v>0.547144754316069</v>
       </c>
       <c r="O24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="b">
         <v>0</v>
@@ -6152,7 +6152,7 @@
         <v>20</v>
       </c>
       <c r="F28" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G28" t="n">
         <v>19</v>
@@ -6172,13 +6172,13 @@
         <v>8</v>
       </c>
       <c r="L28" t="n">
-        <v>20.28571428571428</v>
+        <v>20.35714285714286</v>
       </c>
       <c r="M28" t="n">
-        <v>5680</v>
+        <v>5700</v>
       </c>
       <c r="N28" t="n">
-        <v>0.3083604777415853</v>
+        <v>0.3094462540716613</v>
       </c>
       <c r="O28" t="b">
         <v>1</v>
@@ -6500,13 +6500,13 @@
         <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G34" t="n">
         <v>18</v>
       </c>
       <c r="H34" t="n">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -6520,13 +6520,13 @@
         <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>17.78571428571428</v>
+        <v>17.85714285714286</v>
       </c>
       <c r="M34" t="n">
-        <v>4980</v>
+        <v>5000</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1931730023273856</v>
+        <v>0.1937984496124031</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
@@ -6680,7 +6680,7 @@
         <v>26</v>
       </c>
       <c r="H37" t="n">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -6700,7 +6700,7 @@
         <v>9060</v>
       </c>
       <c r="N37" t="n">
-        <v>0.3077445652173913</v>
+        <v>0.3073270013568521</v>
       </c>
       <c r="O37" t="b">
         <v>0</v>
@@ -6738,7 +6738,7 @@
         <v>27</v>
       </c>
       <c r="H38" t="n">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -6758,7 +6758,7 @@
         <v>8600</v>
       </c>
       <c r="N38" t="n">
-        <v>0.3586321934945788</v>
+        <v>0.3580349708576187</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
@@ -6770,56 +6770,56 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>🏰 Disney Playmobil Kinder Collection Display – 3D Printable Castle</t>
+          <t>Maleficient Diorama with Dragon 300mm  (ALT Version)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4951684</t>
+          <t>https://cults3d.com/:5088769</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Game</t>
+          <t>Art</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46287.81587962963</v>
+        <v>46315.2290162037</v>
       </c>
       <c r="E39" t="n">
-        <v>4.21</v>
+        <v>20</v>
       </c>
       <c r="F39" t="n">
-        <v>508</v>
+        <v>230</v>
       </c>
       <c r="G39" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="H39" t="n">
-        <v>11739</v>
+        <v>863</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>3d printer, 3d printing, castle, collecting, collection, disney, disneyfigures, display, exhibitor, figures, kinder, playmobil, playmobil figures, toy, toycollector, toys</t>
+          <t>fan art, female, figure, game art figurine, garage kit, halloween, maleficient, miniature, miniatures, movie, sculpture, stylized, tabletop, tabletop game, video game</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>16.38709677419355</v>
+        <v>16.42857142857143</v>
       </c>
       <c r="M39" t="n">
-        <v>2138.68</v>
+        <v>4600</v>
       </c>
       <c r="N39" t="n">
-        <v>0.04327455490246188</v>
+        <v>0.2665121668597914</v>
       </c>
       <c r="O39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="b">
         <v>0</v>
@@ -6828,56 +6828,56 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mai Shiranui - The King of Fighters</t>
+          <t>🏰 Disney Playmobil Kinder Collection Display – 3D Printable Castle</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971759</t>
+          <t>https://cults3d.com/:4951684</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Art</t>
+          <t>Game</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46295.05967592593</v>
+        <v>46287.81587962963</v>
       </c>
       <c r="E40" t="n">
-        <v>22.48</v>
+        <v>4.21</v>
       </c>
       <c r="F40" t="n">
-        <v>393</v>
+        <v>508</v>
       </c>
       <c r="G40" t="n">
+        <v>71</v>
+      </c>
+      <c r="H40" t="n">
+        <v>11739</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3d printer, 3d printing, castle, collecting, collection, disney, disneyfigures, display, exhibitor, figures, kinder, playmobil, playmobil figures, toy, toycollector, toys</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
         <v>31</v>
       </c>
-      <c r="H40" t="n">
-        <v>1187</v>
-      </c>
-      <c r="I40" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fanart, king of fighters, mai shiranui, miniature, resin, stl</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>24</v>
-      </c>
       <c r="L40" t="n">
-        <v>16.375</v>
+        <v>16.38709677419355</v>
       </c>
       <c r="M40" t="n">
-        <v>8834.639999999999</v>
+        <v>2138.68</v>
       </c>
       <c r="N40" t="n">
-        <v>0.3310867733782645</v>
+        <v>0.04327455490246188</v>
       </c>
       <c r="O40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" t="b">
         <v>0</v>
@@ -6886,12 +6886,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Maleficient Diorama with Dragon 300mm  (ALT Version)</t>
+          <t>Mai Shiranui - The King of Fighters</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5088769</t>
+          <t>https://cults3d.com/:4971759</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6900,39 +6900,39 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46315.2290162037</v>
+        <v>46295.05967592593</v>
       </c>
       <c r="E41" t="n">
-        <v>20</v>
+        <v>22.48</v>
       </c>
       <c r="F41" t="n">
-        <v>229</v>
+        <v>393</v>
       </c>
       <c r="G41" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H41" t="n">
-        <v>863</v>
+        <v>1187</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fan art, female, figure, game art figurine, garage kit, halloween, maleficient, miniature, miniatures, movie, sculpture, stylized, tabletop, tabletop game, video game</t>
+          <t>fanart, king of fighters, mai shiranui, miniature, resin, stl</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L41" t="n">
-        <v>16.35714285714286</v>
+        <v>16.375</v>
       </c>
       <c r="M41" t="n">
-        <v>4580</v>
+        <v>8834.639999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>0.2653534183082271</v>
+        <v>0.3310867733782645</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
@@ -7260,7 +7260,7 @@
         <v>78</v>
       </c>
       <c r="H47" t="n">
-        <v>15337</v>
+        <v>15348</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -7280,7 +7280,7 @@
         <v>2154.24</v>
       </c>
       <c r="N47" t="n">
-        <v>0.02503749103475256</v>
+        <v>0.02501954652071931</v>
       </c>
       <c r="O47" t="b">
         <v>0</v>
@@ -7350,12 +7350,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lunch 3D Print</t>
+          <t>Cammy Street Fighter 250mm - Miniature Figure STL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4851460</t>
+          <t>https://cults3d.com/:5099745</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7364,42 +7364,42 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46265.57159722222</v>
+        <v>46317.35791666667</v>
       </c>
       <c r="E49" t="n">
         <v>20</v>
       </c>
       <c r="F49" t="n">
-        <v>806</v>
+        <v>213</v>
       </c>
       <c r="G49" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H49" t="n">
-        <v>3001</v>
+        <v>2623</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>anime, ball, blue, chibi, dbz, dragon, hair, launch, lunch, yellow</t>
+          <t>cammy, fan art, female, figure, game art figurine, garage kit, miniature, miniatures, movie, sculpture, street fighter, stylized, tabletop, tabletop game, video game</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>15.20754716981132</v>
+        <v>15.21428571428571</v>
       </c>
       <c r="M49" t="n">
-        <v>16120</v>
+        <v>4260</v>
       </c>
       <c r="N49" t="n">
-        <v>0.2685771409530157</v>
+        <v>0.08120472741136103</v>
       </c>
       <c r="O49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" t="b">
         <v>0</v>
@@ -7408,12 +7408,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cammy Street Fighter 250mm - Miniature Figure STL</t>
+          <t>Lunch 3D Print</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5099745</t>
+          <t>https://cults3d.com/:4851460</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7422,42 +7422,42 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46317.35791666667</v>
+        <v>46265.57159722222</v>
       </c>
       <c r="E50" t="n">
         <v>20</v>
       </c>
       <c r="F50" t="n">
-        <v>212</v>
+        <v>806</v>
       </c>
       <c r="G50" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H50" t="n">
-        <v>2621</v>
+        <v>3001</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>cammy, fan art, female, figure, game art figurine, garage kit, miniature, miniatures, movie, sculpture, street fighter, stylized, tabletop, tabletop game, video game</t>
+          <t>anime, ball, blue, chibi, dbz, dragon, hair, launch, lunch, yellow</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="L50" t="n">
-        <v>15.14285714285714</v>
+        <v>15.20754716981132</v>
       </c>
       <c r="M50" t="n">
-        <v>4240</v>
+        <v>16120</v>
       </c>
       <c r="N50" t="n">
-        <v>0.08088515833651277</v>
+        <v>0.2685771409530157</v>
       </c>
       <c r="O50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P50" t="b">
         <v>0</v>
@@ -7660,13 +7660,13 @@
         <v>20</v>
       </c>
       <c r="F54" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G54" t="n">
         <v>18</v>
       </c>
       <c r="H54" t="n">
-        <v>3440</v>
+        <v>3443</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -7680,13 +7680,13 @@
         <v>2</v>
       </c>
       <c r="L54" t="n">
-        <v>14.85714285714286</v>
+        <v>15</v>
       </c>
       <c r="M54" t="n">
-        <v>4160</v>
+        <v>4200</v>
       </c>
       <c r="N54" t="n">
-        <v>0.06046511627906977</v>
+        <v>0.06099331977926227</v>
       </c>
       <c r="O54" t="b">
         <v>1</v>
@@ -7782,7 +7782,7 @@
         <v>14</v>
       </c>
       <c r="H56" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="I56" t="b">
         <v>0</v>
@@ -7802,7 +7802,7 @@
         <v>6760</v>
       </c>
       <c r="N56" t="n">
-        <v>0.3203791469194313</v>
+        <v>0.3197729422894986</v>
       </c>
       <c r="O56" t="b">
         <v>1</v>
@@ -8014,7 +8014,7 @@
         <v>20</v>
       </c>
       <c r="H60" t="n">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="I60" t="b">
         <v>0</v>
@@ -8034,7 +8034,7 @@
         <v>7260</v>
       </c>
       <c r="N60" t="n">
-        <v>0.3497109826589596</v>
+        <v>0.3493743984600577</v>
       </c>
       <c r="O60" t="b">
         <v>1</v>
@@ -8072,7 +8072,7 @@
         <v>417</v>
       </c>
       <c r="H61" t="n">
-        <v>53411</v>
+        <v>53413</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -8092,7 +8092,7 @@
         <v>20484.9</v>
       </c>
       <c r="N61" t="n">
-        <v>0.007582707681938177</v>
+        <v>0.007582423754516691</v>
       </c>
       <c r="O61" t="b">
         <v>0</v>
@@ -8104,12 +8104,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cowgirl Rogue Bust 3D Print</t>
+          <t>Savage Land Psylocke Bust 3D Print</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4878931</t>
+          <t>https://cults3d.com/:4878923</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8118,7 +8118,7 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46271.73293981481</v>
+        <v>46271.73194444444</v>
       </c>
       <c r="E62" t="n">
         <v>15</v>
@@ -8127,17 +8127,17 @@
         <v>679</v>
       </c>
       <c r="G62" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H62" t="n">
-        <v>1790</v>
+        <v>1831</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>cosplay, costume, cowboy, cowgirl, marvel, parts, rebel, rivals, rogue, starlit</t>
+          <t>art, comics, fan, female, figure, figurine, game, garage, kit, miniature, miniatures, movie, psylocke, savage, sculpture, stylized, tabletop, video, xmen</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -8150,7 +8150,7 @@
         <v>10185</v>
       </c>
       <c r="N62" t="n">
-        <v>0.3793296089385475</v>
+        <v>0.3708356089568542</v>
       </c>
       <c r="O62" t="b">
         <v>1</v>
@@ -8162,12 +8162,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Savage Land Psylocke Bust 3D Print</t>
+          <t>Cowgirl Rogue Bust 3D Print</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4878923</t>
+          <t>https://cults3d.com/:4878931</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46271.73194444444</v>
+        <v>46271.73293981481</v>
       </c>
       <c r="E63" t="n">
         <v>15</v>
@@ -8185,17 +8185,17 @@
         <v>679</v>
       </c>
       <c r="G63" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H63" t="n">
-        <v>1831</v>
+        <v>1790</v>
       </c>
       <c r="I63" t="b">
         <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>art, comics, fan, female, figure, figurine, game, garage, kit, miniature, miniatures, movie, psylocke, savage, sculpture, stylized, tabletop, video, xmen</t>
+          <t>cosplay, costume, cowboy, cowgirl, marvel, parts, rebel, rivals, rogue, starlit</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -8208,7 +8208,7 @@
         <v>10185</v>
       </c>
       <c r="N63" t="n">
-        <v>0.3708356089568542</v>
+        <v>0.3793296089385475</v>
       </c>
       <c r="O63" t="b">
         <v>1</v>
@@ -8336,117 +8336,117 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>rifled AND SMOOTHBORE barrels for toilet plungers</t>
+          <t>Evie Stellar Blade 250mm - Miniature Figure STL (ALT Version)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4880393</t>
+          <t>https://cults3d.com/:5095795</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>Art</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46272.04734953704</v>
+        <v>46316.49896990741</v>
       </c>
       <c r="E66" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F66" t="n">
-        <v>673</v>
+        <v>201</v>
       </c>
       <c r="G66" t="n">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="H66" t="n">
-        <v>33721</v>
+        <v>641</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>airgun, apfsds, artillery, ballistic, bomb, cannon, hand cannon, missle, mortar, pellet, pistol, pneumatic, pnuematic, potato cannon, spinning, spudgun, tank ammo, tank round, toilet plunger, toy</t>
+          <t>evie, fan art, female, figure, game art figurine, garage kit, miniature, miniatures, movie, sculpture, stellar blade, stylized, tabletop, tabletop game, video game</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="L66" t="n">
-        <v>14.31914893617021</v>
+        <v>14.35714285714286</v>
       </c>
       <c r="M66" t="n">
-        <v>14806</v>
+        <v>4020</v>
       </c>
       <c r="N66" t="n">
-        <v>0.01995788974229708</v>
+        <v>0.313572542901716</v>
       </c>
       <c r="O66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Solid Snake Bust 3D Print</t>
+          <t>rifled AND SMOOTHBORE barrels for toilet plungers</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4878977</t>
+          <t>https://cults3d.com/:4880393</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Art</t>
+          <t>Various</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46271.74484953703</v>
+        <v>46272.04734953704</v>
       </c>
       <c r="E67" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F67" t="n">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G67" t="n">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="H67" t="n">
-        <v>2084</v>
+        <v>33724</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>famas, gear, metal, mgs, snake, soldier, solid</t>
+          <t>airgun, apfsds, artillery, ballistic, bomb, cannon, hand cannon, missle, mortar, pellet, pistol, pneumatic, pnuematic, potato cannon, spinning, spudgun, tank ammo, tank round, toilet plunger, toy</t>
         </is>
       </c>
       <c r="K67" t="n">
         <v>47</v>
       </c>
       <c r="L67" t="n">
-        <v>14.27659574468085</v>
+        <v>14.31914893617021</v>
       </c>
       <c r="M67" t="n">
-        <v>10065</v>
+        <v>14806</v>
       </c>
       <c r="N67" t="n">
-        <v>0.3219769673704415</v>
+        <v>0.01995611433993595</v>
       </c>
       <c r="O67" t="b">
         <v>0</v>
       </c>
       <c r="P67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -8472,7 +8472,7 @@
         <v>20</v>
       </c>
       <c r="F68" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G68" t="n">
         <v>22</v>
@@ -8492,13 +8492,13 @@
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>14.21428571428571</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="M68" t="n">
-        <v>3980</v>
+        <v>4000</v>
       </c>
       <c r="N68" t="n">
-        <v>0.3075734157650695</v>
+        <v>0.3091190108191654</v>
       </c>
       <c r="O68" t="b">
         <v>1</v>
@@ -8510,12 +8510,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Evie Stellar Blade 250mm - Miniature Figure STL (ALT Version)</t>
+          <t>Solid Snake Bust 3D Print</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5095795</t>
+          <t>https://cults3d.com/:4878977</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8524,42 +8524,42 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46316.49896990741</v>
+        <v>46271.74484953703</v>
       </c>
       <c r="E69" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>199</v>
+        <v>671</v>
       </c>
       <c r="G69" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H69" t="n">
-        <v>640</v>
+        <v>2084</v>
       </c>
       <c r="I69" t="b">
         <v>0</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>evie, fan art, female, figure, game art figurine, garage kit, miniature, miniatures, movie, sculpture, stellar blade, stylized, tabletop, tabletop game, video game</t>
+          <t>famas, gear, metal, mgs, snake, soldier, solid</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="L69" t="n">
-        <v>14.21428571428571</v>
+        <v>14.27659574468085</v>
       </c>
       <c r="M69" t="n">
-        <v>3980</v>
+        <v>10065</v>
       </c>
       <c r="N69" t="n">
-        <v>0.3109375</v>
+        <v>0.3219769673704415</v>
       </c>
       <c r="O69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P69" t="b">
         <v>0</v>
@@ -8858,12 +8858,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Big Daddy and Little Sister - BioShock</t>
+          <t>Nanami - Jujutsu Kaisen</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971764</t>
+          <t>https://cults3d.com/:4971762</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46292.21871527778</v>
+        <v>46292.2184837963</v>
       </c>
       <c r="E75" t="n">
         <v>22.48</v>
@@ -8881,17 +8881,17 @@
         <v>362</v>
       </c>
       <c r="G75" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H75" t="n">
-        <v>1086</v>
+        <v>865</v>
       </c>
       <c r="I75" t="b">
         <v>0</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>big daddy, bioshock, fanart, miniature, resin, stl</t>
+          <t>fanart, jujutsu kaisen, miniature, nanami, resin, stl</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -8904,7 +8904,7 @@
         <v>8137.76</v>
       </c>
       <c r="N75" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4184971098265896</v>
       </c>
       <c r="O75" t="b">
         <v>0</v>
@@ -8916,12 +8916,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nanami - Jujutsu Kaisen</t>
+          <t>Big Daddy and Little Sister - BioShock</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971762</t>
+          <t>https://cults3d.com/:4971764</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46292.2184837963</v>
+        <v>46292.21871527778</v>
       </c>
       <c r="E76" t="n">
         <v>22.48</v>
@@ -8939,17 +8939,17 @@
         <v>362</v>
       </c>
       <c r="G76" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H76" t="n">
-        <v>865</v>
+        <v>1086</v>
       </c>
       <c r="I76" t="b">
         <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>fanart, jujutsu kaisen, miniature, nanami, resin, stl</t>
+          <t>big daddy, bioshock, fanart, miniature, resin, stl</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -8962,7 +8962,7 @@
         <v>8137.76</v>
       </c>
       <c r="N76" t="n">
-        <v>0.4184971098265896</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O76" t="b">
         <v>0</v>
@@ -9000,7 +9000,7 @@
         <v>14</v>
       </c>
       <c r="H77" t="n">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="I77" t="b">
         <v>0</v>
@@ -9020,7 +9020,7 @@
         <v>6400</v>
       </c>
       <c r="N77" t="n">
-        <v>0.3827751196172249</v>
+        <v>0.3818615751789976</v>
       </c>
       <c r="O77" t="b">
         <v>1</v>
@@ -9058,7 +9058,7 @@
         <v>205</v>
       </c>
       <c r="H78" t="n">
-        <v>17246</v>
+        <v>17248</v>
       </c>
       <c r="I78" t="b">
         <v>0</v>
@@ -9078,7 +9078,7 @@
         <v>4580</v>
       </c>
       <c r="N78" t="n">
-        <v>0.02655688275542155</v>
+        <v>0.02655380333951763</v>
       </c>
       <c r="O78" t="b">
         <v>0</v>
@@ -9116,7 +9116,7 @@
         <v>16</v>
       </c>
       <c r="H79" t="n">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="I79" t="b">
         <v>0</v>
@@ -9136,7 +9136,7 @@
         <v>8820</v>
       </c>
       <c r="N79" t="n">
-        <v>0.3184115523465704</v>
+        <v>0.3179524152847873</v>
       </c>
       <c r="O79" t="b">
         <v>0</v>
@@ -9232,7 +9232,7 @@
         <v>26</v>
       </c>
       <c r="H81" t="n">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="I81" t="b">
         <v>0</v>
@@ -9252,7 +9252,7 @@
         <v>8940</v>
       </c>
       <c r="N81" t="n">
-        <v>0.3104166666666667</v>
+        <v>0.3102012491325468</v>
       </c>
       <c r="O81" t="b">
         <v>1</v>
@@ -9290,7 +9290,7 @@
         <v>10</v>
       </c>
       <c r="H82" t="n">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="I82" t="b">
         <v>0</v>
@@ -9310,7 +9310,7 @@
         <v>5221.7</v>
       </c>
       <c r="N82" t="n">
-        <v>0.3313648293963254</v>
+        <v>0.3311475409836065</v>
       </c>
       <c r="O82" t="b">
         <v>0</v>
@@ -9670,12 +9670,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Silver Surfer - Bust</t>
+          <t>Minthara-Baldurs Gate 3 3D Print</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971680</t>
+          <t>https://cults3d.com/:4729255</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9684,42 +9684,42 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46295.03493055556</v>
+        <v>46234.47359953704</v>
       </c>
       <c r="E89" t="n">
-        <v>13.49</v>
+        <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>300</v>
+        <v>1050</v>
       </c>
       <c r="G89" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="H89" t="n">
-        <v>476</v>
+        <v>7546</v>
       </c>
       <c r="I89" t="b">
         <v>0</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>bust, fanart, herald, marvel, miniature, resin, silver surfer, stl</t>
+          <t>armor, baldur's, baldurs, bg3, bust, dark, dnd, elf, female, figure, gate, larian, mace, minthara, paladin</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L89" t="n">
         <v>12.5</v>
       </c>
       <c r="M89" t="n">
-        <v>4047</v>
+        <v>21000</v>
       </c>
       <c r="N89" t="n">
-        <v>0.6302521008403361</v>
+        <v>0.1391465677179963</v>
       </c>
       <c r="O89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P89" t="b">
         <v>0</v>
@@ -9728,12 +9728,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Minthara-Baldurs Gate 3 3D Print</t>
+          <t>Silver Surfer - Bust</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4729255</t>
+          <t>https://cults3d.com/:4971680</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9742,42 +9742,42 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46234.47359953704</v>
+        <v>46295.03493055556</v>
       </c>
       <c r="E90" t="n">
-        <v>20</v>
+        <v>13.49</v>
       </c>
       <c r="F90" t="n">
-        <v>1050</v>
+        <v>300</v>
       </c>
       <c r="G90" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="H90" t="n">
-        <v>7546</v>
+        <v>476</v>
       </c>
       <c r="I90" t="b">
         <v>0</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>armor, baldur's, baldurs, bg3, bust, dark, dnd, elf, female, figure, gate, larian, mace, minthara, paladin</t>
+          <t>bust, fanart, herald, marvel, miniature, resin, silver surfer, stl</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="L90" t="n">
         <v>12.5</v>
       </c>
       <c r="M90" t="n">
-        <v>21000</v>
+        <v>4047</v>
       </c>
       <c r="N90" t="n">
-        <v>0.1391465677179963</v>
+        <v>0.6302521008403361</v>
       </c>
       <c r="O90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P90" t="b">
         <v>0</v>
@@ -9812,7 +9812,7 @@
         <v>34</v>
       </c>
       <c r="H91" t="n">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="I91" t="b">
         <v>0</v>
@@ -9832,7 +9832,7 @@
         <v>3828</v>
       </c>
       <c r="N91" t="n">
-        <v>0.1689320388349514</v>
+        <v>0.1686046511627907</v>
       </c>
       <c r="O91" t="b">
         <v>1</v>
@@ -9844,12 +9844,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Deku - My Hero Academia - Bust</t>
+          <t>Big Daddy and Little Sister - BioShock - Bust</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971767</t>
+          <t>https://cults3d.com/:4971763</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46292.21883101852</v>
+        <v>46292.21859953704</v>
       </c>
       <c r="E92" t="n">
         <v>13.49</v>
@@ -9867,17 +9867,17 @@
         <v>306</v>
       </c>
       <c r="G92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H92" t="n">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="I92" t="b">
         <v>0</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>bust, deku, fanart, miniature, my hero academia, resin, stl</t>
+          <t>big daddy, bioshock, bust, fanart, miniature, resin, stl</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -9890,7 +9890,7 @@
         <v>4127.940000000001</v>
       </c>
       <c r="N92" t="n">
-        <v>0.6144578313253012</v>
+        <v>0.6035502958579881</v>
       </c>
       <c r="O92" t="b">
         <v>0</v>
@@ -9902,12 +9902,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Big Daddy and Little Sister - BioShock - Bust</t>
+          <t>Deku - My Hero Academia - Bust</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971763</t>
+          <t>https://cults3d.com/:4971767</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9916,7 +9916,7 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46292.21859953704</v>
+        <v>46292.21883101852</v>
       </c>
       <c r="E93" t="n">
         <v>13.49</v>
@@ -9925,17 +9925,17 @@
         <v>306</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H93" t="n">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="I93" t="b">
         <v>0</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>big daddy, bioshock, bust, fanart, miniature, resin, stl</t>
+          <t>bust, deku, fanart, miniature, my hero academia, resin, stl</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -9948,7 +9948,7 @@
         <v>4127.940000000001</v>
       </c>
       <c r="N93" t="n">
-        <v>0.6035502958579881</v>
+        <v>0.6144578313253012</v>
       </c>
       <c r="O93" t="b">
         <v>0</v>
@@ -10044,7 +10044,7 @@
         <v>50</v>
       </c>
       <c r="H95" t="n">
-        <v>3223</v>
+        <v>3226</v>
       </c>
       <c r="I95" t="b">
         <v>0</v>
@@ -10064,7 +10064,7 @@
         <v>625.6799999999999</v>
       </c>
       <c r="N95" t="n">
-        <v>0.04902264970524356</v>
+        <v>0.04897706137631742</v>
       </c>
       <c r="O95" t="b">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>34</v>
       </c>
       <c r="H96" t="n">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="I96" t="b">
         <v>0</v>
@@ -10122,7 +10122,7 @@
         <v>2780.8</v>
       </c>
       <c r="N96" t="n">
-        <v>0.166491043203372</v>
+        <v>0.1663157894736842</v>
       </c>
       <c r="O96" t="b">
         <v>1</v>
@@ -10160,7 +10160,7 @@
         <v>41</v>
       </c>
       <c r="H97" t="n">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="I97" t="b">
         <v>0</v>
@@ -10180,7 +10180,7 @@
         <v>942</v>
       </c>
       <c r="N97" t="n">
-        <v>0.0599694423223835</v>
+        <v>0.05994654448262696</v>
       </c>
       <c r="O97" t="b">
         <v>0</v>
@@ -10218,7 +10218,7 @@
         <v>122</v>
       </c>
       <c r="H98" t="n">
-        <v>14930</v>
+        <v>14932</v>
       </c>
       <c r="I98" t="b">
         <v>0</v>
@@ -10238,7 +10238,7 @@
         <v>2399.76</v>
       </c>
       <c r="N98" t="n">
-        <v>0.040589417280643</v>
+        <v>0.04058398071256362</v>
       </c>
       <c r="O98" t="b">
         <v>0</v>
@@ -10276,7 +10276,7 @@
         <v>40</v>
       </c>
       <c r="H99" t="n">
-        <v>8972</v>
+        <v>8973</v>
       </c>
       <c r="I99" t="b">
         <v>0</v>
@@ -10296,7 +10296,7 @@
         <v>8800</v>
       </c>
       <c r="N99" t="n">
-        <v>0.04904146232724031</v>
+        <v>0.04903599687952747</v>
       </c>
       <c r="O99" t="b">
         <v>1</v>
@@ -10392,7 +10392,7 @@
         <v>70</v>
       </c>
       <c r="H101" t="n">
-        <v>7303</v>
+        <v>7306</v>
       </c>
       <c r="I101" t="b">
         <v>0</v>
@@ -10412,7 +10412,7 @@
         <v>2007</v>
       </c>
       <c r="N101" t="n">
-        <v>0.03053539641243325</v>
+        <v>0.03052285792499316</v>
       </c>
       <c r="O101" t="b">
         <v>0</v>
@@ -10540,12 +10540,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Minthara Bust 3D Print</t>
+          <t>Yuria of Londor Bust 3D Print</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4749441</t>
+          <t>https://cults3d.com/:4749861</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46239.73216435185</v>
+        <v>46239.81805555556</v>
       </c>
       <c r="E104" t="n">
         <v>15</v>
@@ -10563,17 +10563,17 @@
         <v>832</v>
       </c>
       <c r="G104" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H104" t="n">
-        <v>2217</v>
+        <v>3232</v>
       </c>
       <c r="I104" t="b">
         <v>0</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>armor, baldur's, baldurs, bg3, bust, dark, dnd, elf, female, figure, gate, larian, mace, minthara, paladin</t>
+          <t>dark, fromsoftware, game, londor, religion, role-playing, rpg, souls, video, yuria</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -10586,7 +10586,7 @@
         <v>12480</v>
       </c>
       <c r="N104" t="n">
-        <v>0.3752819124943618</v>
+        <v>0.2574257425742574</v>
       </c>
       <c r="O104" t="b">
         <v>0</v>
@@ -10598,12 +10598,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Yuria of Londor Bust 3D Print</t>
+          <t>Minthara Bust 3D Print</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4749861</t>
+          <t>https://cults3d.com/:4749441</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46239.81805555556</v>
+        <v>46239.73216435185</v>
       </c>
       <c r="E105" t="n">
         <v>15</v>
@@ -10621,17 +10621,17 @@
         <v>832</v>
       </c>
       <c r="G105" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H105" t="n">
-        <v>3232</v>
+        <v>2217</v>
       </c>
       <c r="I105" t="b">
         <v>0</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>dark, fromsoftware, game, londor, religion, role-playing, rpg, souls, video, yuria</t>
+          <t>armor, baldur's, baldurs, bg3, bust, dark, dnd, elf, female, figure, gate, larian, mace, minthara, paladin</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -10644,7 +10644,7 @@
         <v>12480</v>
       </c>
       <c r="N105" t="n">
-        <v>0.2574257425742574</v>
+        <v>0.3752819124943618</v>
       </c>
       <c r="O105" t="b">
         <v>0</v>
@@ -11494,7 +11494,7 @@
         <v>26</v>
       </c>
       <c r="H120" t="n">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="I120" t="b">
         <v>0</v>
@@ -11514,7 +11514,7 @@
         <v>10460</v>
       </c>
       <c r="N120" t="n">
-        <v>0.2542537676227516</v>
+        <v>0.2541302235179786</v>
       </c>
       <c r="O120" t="b">
         <v>0</v>
@@ -11552,7 +11552,7 @@
         <v>29</v>
       </c>
       <c r="H121" t="n">
-        <v>2986</v>
+        <v>2987</v>
       </c>
       <c r="I121" t="b">
         <v>0</v>
@@ -11572,7 +11572,7 @@
         <v>1218</v>
       </c>
       <c r="N121" t="n">
-        <v>0.06798392498325519</v>
+        <v>0.06796116504854369</v>
       </c>
       <c r="O121" t="b">
         <v>0</v>
@@ -11610,7 +11610,7 @@
         <v>44</v>
       </c>
       <c r="H122" t="n">
-        <v>3124</v>
+        <v>3125</v>
       </c>
       <c r="I122" t="b">
         <v>0</v>
@@ -11630,7 +11630,7 @@
         <v>10540</v>
       </c>
       <c r="N122" t="n">
-        <v>0.1686939820742638</v>
+        <v>0.16864</v>
       </c>
       <c r="O122" t="b">
         <v>0</v>
@@ -11668,7 +11668,7 @@
         <v>61</v>
       </c>
       <c r="H123" t="n">
-        <v>19776</v>
+        <v>19778</v>
       </c>
       <c r="I123" t="b">
         <v>1</v>
@@ -11688,7 +11688,7 @@
         <v>5850</v>
       </c>
       <c r="N123" t="n">
-        <v>0.01972087378640777</v>
+        <v>0.01971887956315098</v>
       </c>
       <c r="O123" t="b">
         <v>0</v>
@@ -11700,12 +11700,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Grace Ashcroft Miniature Figure (ALT Version)</t>
+          <t>Grace Ashcroft Miniature Figure</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4843587</t>
+          <t>https://cults3d.com/:4843586</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -11714,19 +11714,19 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46265.1003587963</v>
+        <v>46263.66559027778</v>
       </c>
       <c r="E124" t="n">
         <v>20</v>
       </c>
       <c r="F124" t="n">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="G124" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H124" t="n">
-        <v>1856</v>
+        <v>1887</v>
       </c>
       <c r="I124" t="b">
         <v>0</v>
@@ -11737,16 +11737,16 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L124" t="n">
-        <v>9.169811320754716</v>
+        <v>9.109090909090909</v>
       </c>
       <c r="M124" t="n">
-        <v>9720</v>
+        <v>10020</v>
       </c>
       <c r="N124" t="n">
-        <v>0.261853448275862</v>
+        <v>0.2655007949125596</v>
       </c>
       <c r="O124" t="b">
         <v>1</v>
@@ -11758,12 +11758,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Grace Ashcroft Miniature Figure</t>
+          <t>BloodRayne</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4843586</t>
+          <t>https://cults3d.com/:4954039</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -11772,39 +11772,39 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46263.66559027778</v>
+        <v>46288.40895833333</v>
       </c>
       <c r="E125" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F125" t="n">
-        <v>501</v>
+        <v>273</v>
       </c>
       <c r="G125" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H125" t="n">
-        <v>1886</v>
+        <v>1946</v>
       </c>
       <c r="I125" t="b">
         <v>0</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>fan art, female, figure, game art figurine, garage kit, grace ashcroft, miniature, miniatures, movie, resident evil, sculpture, stylized, tabletop, tabletop game, video game</t>
+          <t>alucard, bayonetta, blade, bloodrayne, bloodrayne 2, castlevania, ephemera, ferril, h3llcreator, hellsing, rayne, selene, severin, underworld, vampirella</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="L125" t="n">
-        <v>9.109090909090909</v>
+        <v>9.1</v>
       </c>
       <c r="M125" t="n">
-        <v>10020</v>
+        <v>6006</v>
       </c>
       <c r="N125" t="n">
-        <v>0.2656415694591728</v>
+        <v>0.1402877697841727</v>
       </c>
       <c r="O125" t="b">
         <v>1</v>
@@ -11816,117 +11816,117 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BloodRayne</t>
+          <t>Old Timer Ghost – The Haunted Pensioner</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4954039</t>
+          <t>https://cults3d.com/:4981795</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Art</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46288.40895833333</v>
+        <v>46294.20533564815</v>
       </c>
       <c r="E126" t="n">
-        <v>22</v>
+        <v>2.25</v>
       </c>
       <c r="F126" t="n">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="G126" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H126" t="n">
-        <v>1946</v>
+        <v>4142</v>
       </c>
       <c r="I126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>alucard, bayonetta, blade, bloodrayne, bloodrayne 2, castlevania, ephemera, ferril, h3llcreator, hellsing, rayne, selene, severin, underworld, vampirella</t>
+          <t>cuteghost, funnyghost, ghost, ghost3dprint, ghostlamp, glowinthedark, grandpaghost, halloween, halloween3dprint, halloweendecor, halloweendecoration, ledlamp, oldghost, oldtimerghost, seniorghost, spooky, spookydecor</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L126" t="n">
-        <v>9.1</v>
+        <v>9.083333333333334</v>
       </c>
       <c r="M126" t="n">
-        <v>6006</v>
+        <v>490.5</v>
       </c>
       <c r="N126" t="n">
-        <v>0.1402877697841727</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="O126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Old Timer Ghost – The Haunted Pensioner</t>
+          <t>Grace Ashcroft Miniature Figure (ALT Version)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4981795</t>
+          <t>https://cults3d.com/:4843587</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Art</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46294.20533564815</v>
+        <v>46265.1003587963</v>
       </c>
       <c r="E127" t="n">
-        <v>2.25</v>
+        <v>20</v>
       </c>
       <c r="F127" t="n">
-        <v>218</v>
+        <v>486</v>
       </c>
       <c r="G127" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H127" t="n">
-        <v>4142</v>
+        <v>1857</v>
       </c>
       <c r="I127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>cuteghost, funnyghost, ghost, ghost3dprint, ghostlamp, glowinthedark, grandpaghost, halloween, halloween3dprint, halloweendecor, halloweendecoration, ledlamp, oldghost, oldtimerghost, seniorghost, spooky, spookydecor</t>
+          <t>fan art, female, figure, game art figurine, garage kit, grace ashcroft, miniature, miniatures, movie, resident evil, sculpture, stylized, tabletop, tabletop game, video game</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L127" t="n">
-        <v>9.083333333333334</v>
+        <v>9</v>
       </c>
       <c r="M127" t="n">
-        <v>490.5</v>
+        <v>9720</v>
       </c>
       <c r="N127" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.2617124394184168</v>
       </c>
       <c r="O127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -11958,7 +11958,7 @@
         <v>18</v>
       </c>
       <c r="H128" t="n">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="I128" t="b">
         <v>0</v>
@@ -11978,7 +11978,7 @@
         <v>9380</v>
       </c>
       <c r="N128" t="n">
-        <v>0.2872014696876914</v>
+        <v>0.2870257037943696</v>
       </c>
       <c r="O128" t="b">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>552</v>
       </c>
       <c r="H130" t="n">
-        <v>50955</v>
+        <v>50956</v>
       </c>
       <c r="I130" t="b">
         <v>0</v>
@@ -12094,7 +12094,7 @@
         <v>2262.56</v>
       </c>
       <c r="N130" t="n">
-        <v>0.01405161416936513</v>
+        <v>0.01405133840960829</v>
       </c>
       <c r="O130" t="b">
         <v>0</v>
@@ -12770,7 +12770,7 @@
         <v>26</v>
       </c>
       <c r="H142" t="n">
-        <v>7826</v>
+        <v>7827</v>
       </c>
       <c r="I142" t="b">
         <v>1</v>
@@ -12790,7 +12790,7 @@
         <v>368.16</v>
       </c>
       <c r="N142" t="n">
-        <v>0.01993355481727575</v>
+        <v>0.01993100804906094</v>
       </c>
       <c r="O142" t="b">
         <v>0</v>
@@ -12828,7 +12828,7 @@
         <v>20</v>
       </c>
       <c r="H143" t="n">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="I143" t="b">
         <v>0</v>
@@ -12848,7 +12848,7 @@
         <v>10800</v>
       </c>
       <c r="N143" t="n">
-        <v>0.2461257976298997</v>
+        <v>0.2460136674259681</v>
       </c>
       <c r="O143" t="b">
         <v>0</v>
@@ -13002,7 +13002,7 @@
         <v>165</v>
       </c>
       <c r="H146" t="n">
-        <v>27136</v>
+        <v>27139</v>
       </c>
       <c r="I146" t="b">
         <v>0</v>
@@ -13022,7 +13022,7 @@
         <v>5796</v>
       </c>
       <c r="N146" t="n">
-        <v>0.02373231132075472</v>
+        <v>0.0237296879030178</v>
       </c>
       <c r="O146" t="b">
         <v>0</v>
@@ -14394,7 +14394,7 @@
         <v>92</v>
       </c>
       <c r="H170" t="n">
-        <v>12174</v>
+        <v>12175</v>
       </c>
       <c r="I170" t="b">
         <v>0</v>
@@ -14414,7 +14414,7 @@
         <v>1001.88</v>
       </c>
       <c r="N170" t="n">
-        <v>0.02078199441432561</v>
+        <v>0.02078028747433265</v>
       </c>
       <c r="O170" t="b">
         <v>1</v>
@@ -14426,12 +14426,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Gwen Stacy Miniature Figure (ALT Version)</t>
+          <t>Looney Tunes x Chicago Bulls Trio – BUG BUNNY | No AMS / Multi-Part / 3MF</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4722470</t>
+          <t>https://cults3d.com/:4780697</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -14440,42 +14440,42 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46232.62248842593</v>
+        <v>46248.43832175926</v>
       </c>
       <c r="E171" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F171" t="n">
-        <v>556</v>
+        <v>453</v>
       </c>
       <c r="G171" t="n">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="H171" t="n">
-        <v>2155</v>
+        <v>9674</v>
       </c>
       <c r="I171" t="b">
         <v>0</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>fan art, female, figure, game art figurine, garage kit, gwen stacy, miniature, miniatures, movie, sculpture, stylized, summer, tabletop, tabletop game, video game</t>
+          <t>basketball, bugs bunny, cartoon figure, chicagobulls, cw prestige, cwprestige, daffyduck, fdm printing, lolabunny, looney tunes, multi parts, noams, urban vibes, urban vibes collection</t>
         </is>
       </c>
       <c r="K171" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L171" t="n">
-        <v>6.465116279069767</v>
+        <v>6.471428571428572</v>
       </c>
       <c r="M171" t="n">
-        <v>11120</v>
+        <v>2718</v>
       </c>
       <c r="N171" t="n">
-        <v>0.2580046403712297</v>
+        <v>0.04682654537936737</v>
       </c>
       <c r="O171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P171" t="b">
         <v>0</v>
@@ -14484,12 +14484,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Looney Tunes x Chicago Bulls Trio – BUG BUNNY | No AMS / Multi-Part / 3MF</t>
+          <t>Gwen Stacy Miniature Figure (ALT Version)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4780697</t>
+          <t>https://cults3d.com/:4722470</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -14498,42 +14498,42 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46248.43832175926</v>
+        <v>46232.62248842593</v>
       </c>
       <c r="E172" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F172" t="n">
-        <v>452</v>
+        <v>556</v>
       </c>
       <c r="G172" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="H172" t="n">
-        <v>9672</v>
+        <v>2155</v>
       </c>
       <c r="I172" t="b">
         <v>0</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>basketball, bugs bunny, cartoon figure, chicagobulls, cw prestige, cwprestige, daffyduck, fdm printing, lolabunny, looney tunes, multi parts, noams, urban vibes, urban vibes collection</t>
+          <t>fan art, female, figure, game art figurine, garage kit, gwen stacy, miniature, miniatures, movie, sculpture, stylized, summer, tabletop, tabletop game, video game</t>
         </is>
       </c>
       <c r="K172" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="L172" t="n">
-        <v>6.457142857142857</v>
+        <v>6.465116279069767</v>
       </c>
       <c r="M172" t="n">
-        <v>2712</v>
+        <v>11120</v>
       </c>
       <c r="N172" t="n">
-        <v>0.0467328370554177</v>
+        <v>0.2580046403712297</v>
       </c>
       <c r="O172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P172" t="b">
         <v>0</v>
@@ -14542,12 +14542,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Morrigan P2 by E.S Monster</t>
+          <t>"It Was a Good Day" Rapper Figurine for 3D printing. No AMS / Multi-Part / 3MF</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4800090</t>
+          <t>https://cults3d.com/:4955740</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -14556,39 +14556,39 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46253.16618055556</v>
+        <v>46288.70644675926</v>
       </c>
       <c r="E173" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F173" t="n">
-        <v>417</v>
+        <v>193</v>
       </c>
       <c r="G173" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="H173" t="n">
-        <v>1685</v>
+        <v>5847</v>
       </c>
       <c r="I173" t="b">
         <v>0</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>3d model, character, fanart, female, morrigan, myth-inspired, sculpt, stl</t>
+          <t>art, cartoon, figurine, for children, hip-hop, rap, statue, toy</t>
         </is>
       </c>
       <c r="K173" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="L173" t="n">
-        <v>6.415384615384616</v>
+        <v>6.433333333333334</v>
       </c>
       <c r="M173" t="n">
-        <v>8340</v>
+        <v>1737</v>
       </c>
       <c r="N173" t="n">
-        <v>0.2474777448071217</v>
+        <v>0.03300838036599966</v>
       </c>
       <c r="O173" t="b">
         <v>0</v>
@@ -14600,12 +14600,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Bust of Evie</t>
+          <t>Morrigan P2 by E.S Monster</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4934390</t>
+          <t>https://cults3d.com/:4800090</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -14614,42 +14614,42 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46284.4122337963</v>
+        <v>46253.16618055556</v>
       </c>
       <c r="E174" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F174" t="n">
-        <v>217</v>
+        <v>417</v>
       </c>
       <c r="G174" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H174" t="n">
-        <v>496</v>
+        <v>1685</v>
       </c>
       <c r="I174" t="b">
         <v>0</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>arno dorian, assassin's creed syndicate, bust, corvo attano, dishonored, edward kenway, emily kaldwin, evie frye, ezio auditore, h3llcreator, henry green, jacob frye, lara croft, lydia frye, shao jun, tomb raider</t>
+          <t>3d model, character, fanart, female, morrigan, myth-inspired, sculpt, stl</t>
         </is>
       </c>
       <c r="K174" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="L174" t="n">
-        <v>6.382352941176471</v>
+        <v>6.415384615384616</v>
       </c>
       <c r="M174" t="n">
-        <v>2604</v>
+        <v>8340</v>
       </c>
       <c r="N174" t="n">
-        <v>0.4375</v>
+        <v>0.2474777448071217</v>
       </c>
       <c r="O174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P174" t="b">
         <v>0</v>
@@ -14658,12 +14658,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>"It Was a Good Day" Rapper Figurine for 3D printing. No AMS / Multi-Part / 3MF</t>
+          <t>Bust of Evie</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4955740</t>
+          <t>https://cults3d.com/:4934390</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -14672,42 +14672,42 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46288.70644675926</v>
+        <v>46284.4122337963</v>
       </c>
       <c r="E175" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F175" t="n">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="G175" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="H175" t="n">
-        <v>5845</v>
+        <v>496</v>
       </c>
       <c r="I175" t="b">
         <v>0</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>art, cartoon, figurine, for children, hip-hop, rap, statue, toy</t>
+          <t>arno dorian, assassin's creed syndicate, bust, corvo attano, dishonored, edward kenway, emily kaldwin, evie frye, ezio auditore, h3llcreator, henry green, jacob frye, lara croft, lydia frye, shao jun, tomb raider</t>
         </is>
       </c>
       <c r="K175" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L175" t="n">
-        <v>6.366666666666666</v>
+        <v>6.382352941176471</v>
       </c>
       <c r="M175" t="n">
-        <v>1719</v>
+        <v>2604</v>
       </c>
       <c r="N175" t="n">
-        <v>0.03267750213857998</v>
+        <v>0.4375</v>
       </c>
       <c r="O175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P175" t="b">
         <v>0</v>
@@ -14742,7 +14742,7 @@
         <v>101</v>
       </c>
       <c r="H176" t="n">
-        <v>14474</v>
+        <v>14478</v>
       </c>
       <c r="I176" t="b">
         <v>0</v>
@@ -14762,7 +14762,7 @@
         <v>1257.68</v>
       </c>
       <c r="N176" t="n">
-        <v>0.027497581870941</v>
+        <v>0.02748998480453101</v>
       </c>
       <c r="O176" t="b">
         <v>0</v>
@@ -14858,7 +14858,7 @@
         <v>65</v>
       </c>
       <c r="H178" t="n">
-        <v>7889</v>
+        <v>7893</v>
       </c>
       <c r="I178" t="b">
         <v>0</v>
@@ -14878,7 +14878,7 @@
         <v>1842</v>
       </c>
       <c r="N178" t="n">
-        <v>0.03891494485993155</v>
+        <v>0.03889522361586216</v>
       </c>
       <c r="O178" t="b">
         <v>1</v>
@@ -15090,7 +15090,7 @@
         <v>154</v>
       </c>
       <c r="H182" t="n">
-        <v>28305</v>
+        <v>28306</v>
       </c>
       <c r="I182" t="b">
         <v>0</v>
@@ -15110,7 +15110,7 @@
         <v>799.22</v>
       </c>
       <c r="N182" t="n">
-        <v>0.00628864158275923</v>
+        <v>0.006288419416378153</v>
       </c>
       <c r="O182" t="b">
         <v>0</v>
@@ -15148,7 +15148,7 @@
         <v>85</v>
       </c>
       <c r="H183" t="n">
-        <v>5417</v>
+        <v>5418</v>
       </c>
       <c r="I183" t="b">
         <v>0</v>
@@ -15168,7 +15168,7 @@
         <v>11712.08</v>
       </c>
       <c r="N183" t="n">
-        <v>0.09617869669558797</v>
+        <v>0.09616094499815431</v>
       </c>
       <c r="O183" t="b">
         <v>0</v>
@@ -15548,13 +15548,13 @@
         <v>6</v>
       </c>
       <c r="F190" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G190" t="n">
         <v>57</v>
       </c>
       <c r="H190" t="n">
-        <v>6486</v>
+        <v>6489</v>
       </c>
       <c r="I190" t="b">
         <v>0</v>
@@ -15568,13 +15568,13 @@
         <v>70</v>
       </c>
       <c r="L190" t="n">
-        <v>5.985714285714286</v>
+        <v>6</v>
       </c>
       <c r="M190" t="n">
-        <v>2514</v>
+        <v>2520</v>
       </c>
       <c r="N190" t="n">
-        <v>0.06460067838421214</v>
+        <v>0.06472491909385113</v>
       </c>
       <c r="O190" t="b">
         <v>1</v>
@@ -15606,13 +15606,13 @@
         <v>6</v>
       </c>
       <c r="F191" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G191" t="n">
         <v>87</v>
       </c>
       <c r="H191" t="n">
-        <v>7064</v>
+        <v>7066</v>
       </c>
       <c r="I191" t="b">
         <v>0</v>
@@ -15626,13 +15626,13 @@
         <v>70</v>
       </c>
       <c r="L191" t="n">
-        <v>5.942857142857143</v>
+        <v>5.957142857142857</v>
       </c>
       <c r="M191" t="n">
-        <v>2496</v>
+        <v>2502</v>
       </c>
       <c r="N191" t="n">
-        <v>0.05889014722536806</v>
+        <v>0.05901500141522785</v>
       </c>
       <c r="O191" t="b">
         <v>1</v>
@@ -16192,7 +16192,7 @@
         <v>53</v>
       </c>
       <c r="H201" t="n">
-        <v>6542</v>
+        <v>6543</v>
       </c>
       <c r="I201" t="b">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>1009.8</v>
       </c>
       <c r="N201" t="n">
-        <v>0.038978905533476</v>
+        <v>0.03897294818890417</v>
       </c>
       <c r="O201" t="b">
         <v>1</v>
@@ -16250,7 +16250,7 @@
         <v>105</v>
       </c>
       <c r="H202" t="n">
-        <v>7941</v>
+        <v>7942</v>
       </c>
       <c r="I202" t="b">
         <v>0</v>
@@ -16270,7 +16270,7 @@
         <v>667.26</v>
       </c>
       <c r="N202" t="n">
-        <v>0.02493388741972044</v>
+        <v>0.02493074792243767</v>
       </c>
       <c r="O202" t="b">
         <v>0</v>
@@ -16362,7 +16362,7 @@
         <v>31</v>
       </c>
       <c r="H204" t="n">
-        <v>15261</v>
+        <v>15263</v>
       </c>
       <c r="I204" t="b">
         <v>0</v>
@@ -16382,7 +16382,7 @@
         <v>272.09</v>
       </c>
       <c r="N204" t="n">
-        <v>0.01054976738090558</v>
+        <v>0.01054838498329293</v>
       </c>
       <c r="O204" t="b">
         <v>1</v>
@@ -16916,12 +16916,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Albedo by E.S Monster</t>
+          <t>Shredder Fan art (no ams-multiparts/3mf)</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4779945</t>
+          <t>https://cults3d.com/:4945125</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -16930,39 +16930,39 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46248.24653935185</v>
+        <v>46286.62590277778</v>
       </c>
       <c r="E214" t="n">
-        <v>20</v>
+        <v>3.96</v>
       </c>
       <c r="F214" t="n">
-        <v>371</v>
+        <v>170</v>
       </c>
       <c r="G214" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H214" t="n">
-        <v>1202</v>
+        <v>2974</v>
       </c>
       <c r="I214" t="b">
         <v>0</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>3d model, albedo, character, fanart, female, myth-inspired, sculpt, stl</t>
+          <t>3d print, 3mf, decor, decor master, decormaster, donatello, gift, leonardo, michelangelo, multipart, no ams, raphael, splinter, teenage mutant ninja turtles, tmnt, toy</t>
         </is>
       </c>
       <c r="K214" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="L214" t="n">
-        <v>5.3</v>
+        <v>5.3125</v>
       </c>
       <c r="M214" t="n">
-        <v>7420</v>
+        <v>673.2</v>
       </c>
       <c r="N214" t="n">
-        <v>0.3086522462562396</v>
+        <v>0.05716207128446537</v>
       </c>
       <c r="O214" t="b">
         <v>0</v>
@@ -17000,7 +17000,7 @@
         <v>5</v>
       </c>
       <c r="H215" t="n">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="I215" t="b">
         <v>1</v>
@@ -17020,7 +17020,7 @@
         <v>314.82</v>
       </c>
       <c r="N215" t="n">
-        <v>0.09665653495440729</v>
+        <v>0.09659781287970838</v>
       </c>
       <c r="O215" t="b">
         <v>0</v>
@@ -17032,12 +17032,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Shredder Fan art (no ams-multiparts/3mf)</t>
+          <t>Albedo by E.S Monster</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4945125</t>
+          <t>https://cults3d.com/:4779945</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -17046,39 +17046,39 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46286.62590277778</v>
+        <v>46248.24653935185</v>
       </c>
       <c r="E216" t="n">
-        <v>3.96</v>
+        <v>20</v>
       </c>
       <c r="F216" t="n">
-        <v>169</v>
+        <v>371</v>
       </c>
       <c r="G216" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="H216" t="n">
-        <v>2974</v>
+        <v>1202</v>
       </c>
       <c r="I216" t="b">
         <v>0</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>3d print, 3mf, decor, decor master, decormaster, donatello, gift, leonardo, michelangelo, multipart, no ams, raphael, splinter, teenage mutant ninja turtles, tmnt, toy</t>
+          <t>3d model, albedo, character, fanart, female, myth-inspired, sculpt, stl</t>
         </is>
       </c>
       <c r="K216" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="L216" t="n">
-        <v>5.28125</v>
+        <v>5.3</v>
       </c>
       <c r="M216" t="n">
-        <v>669.24</v>
+        <v>7420</v>
       </c>
       <c r="N216" t="n">
-        <v>0.05682582380632145</v>
+        <v>0.3086522462562396</v>
       </c>
       <c r="O216" t="b">
         <v>0</v>
@@ -17554,12 +17554,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Edward - Assassin's Creed - Bust</t>
+          <t>Master Splinter Fan art (no ams-multiparts/3mf)</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4724633</t>
+          <t>https://cults3d.com/:4911957</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -17568,39 +17568,39 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46234.02446759259</v>
+        <v>46279.61715277778</v>
       </c>
       <c r="E225" t="n">
-        <v>13.49</v>
+        <v>3.96</v>
       </c>
       <c r="F225" t="n">
-        <v>404</v>
+        <v>186</v>
       </c>
       <c r="G225" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="H225" t="n">
-        <v>984</v>
+        <v>3897</v>
       </c>
       <c r="I225" t="b">
         <v>0</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>assassin, assassinscreed, bust, collectible, edward, miniature, pirate, resin, stl, ubisoft</t>
+          <t>3d print, 3mf, decor, decor master, decormaster, donatello, gift, leonardo, michelangelo, multipart, no ams, raphael, splinter, teenage mutant ninja turtles, tmnt, toy</t>
         </is>
       </c>
       <c r="K225" t="n">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="L225" t="n">
-        <v>4.752941176470588</v>
+        <v>4.769230769230769</v>
       </c>
       <c r="M225" t="n">
-        <v>5449.96</v>
+        <v>736.5599999999999</v>
       </c>
       <c r="N225" t="n">
-        <v>0.4105691056910569</v>
+        <v>0.04772902232486528</v>
       </c>
       <c r="O225" t="b">
         <v>0</v>
@@ -17612,12 +17612,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Master Splinter Fan art (no ams-multiparts/3mf)</t>
+          <t>Edward - Assassin's Creed - Bust</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4911957</t>
+          <t>https://cults3d.com/:4724633</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -17626,39 +17626,39 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46279.61715277778</v>
+        <v>46234.02446759259</v>
       </c>
       <c r="E226" t="n">
-        <v>3.96</v>
+        <v>13.49</v>
       </c>
       <c r="F226" t="n">
-        <v>185</v>
+        <v>404</v>
       </c>
       <c r="G226" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="H226" t="n">
-        <v>3897</v>
+        <v>984</v>
       </c>
       <c r="I226" t="b">
         <v>0</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>3d print, 3mf, decor, decor master, decormaster, donatello, gift, leonardo, michelangelo, multipart, no ams, raphael, splinter, teenage mutant ninja turtles, tmnt, toy</t>
+          <t>assassin, assassinscreed, bust, collectible, edward, miniature, pirate, resin, stl, ubisoft</t>
         </is>
       </c>
       <c r="K226" t="n">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="L226" t="n">
-        <v>4.743589743589744</v>
+        <v>4.752941176470588</v>
       </c>
       <c r="M226" t="n">
-        <v>732.6</v>
+        <v>5449.96</v>
       </c>
       <c r="N226" t="n">
-        <v>0.0474724146779574</v>
+        <v>0.4105691056910569</v>
       </c>
       <c r="O226" t="b">
         <v>0</v>
@@ -18044,7 +18044,7 @@
         <v>75</v>
       </c>
       <c r="H233" t="n">
-        <v>4956</v>
+        <v>4959</v>
       </c>
       <c r="I233" t="b">
         <v>0</v>
@@ -18064,7 +18064,7 @@
         <v>7120</v>
       </c>
       <c r="N233" t="n">
-        <v>0.07183212267958031</v>
+        <v>0.07178866706997379</v>
       </c>
       <c r="O233" t="b">
         <v>0</v>
@@ -18334,7 +18334,7 @@
         <v>77</v>
       </c>
       <c r="H238" t="n">
-        <v>7192</v>
+        <v>7193</v>
       </c>
       <c r="I238" t="b">
         <v>0</v>
@@ -18354,7 +18354,7 @@
         <v>2142</v>
       </c>
       <c r="N238" t="n">
-        <v>0.0496384872080089</v>
+        <v>0.04963158626442375</v>
       </c>
       <c r="O238" t="b">
         <v>0</v>
@@ -18450,7 +18450,7 @@
         <v>85</v>
       </c>
       <c r="H240" t="n">
-        <v>3651</v>
+        <v>3652</v>
       </c>
       <c r="I240" t="b">
         <v>0</v>
@@ -18470,7 +18470,7 @@
         <v>1679.92</v>
       </c>
       <c r="N240" t="n">
-        <v>0.04546699534374144</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="O240" t="b">
         <v>0</v>
@@ -18740,7 +18740,7 @@
         <v>70</v>
       </c>
       <c r="H245" t="n">
-        <v>10100</v>
+        <v>10102</v>
       </c>
       <c r="I245" t="b">
         <v>0</v>
@@ -18760,7 +18760,7 @@
         <v>1267.2</v>
       </c>
       <c r="N245" t="n">
-        <v>0.03168316831683168</v>
+        <v>0.03167689566422491</v>
       </c>
       <c r="O245" t="b">
         <v>1</v>
@@ -18856,7 +18856,7 @@
         <v>61</v>
       </c>
       <c r="H247" t="n">
-        <v>7227</v>
+        <v>7230</v>
       </c>
       <c r="I247" t="b">
         <v>0</v>
@@ -18876,7 +18876,7 @@
         <v>1236</v>
       </c>
       <c r="N247" t="n">
-        <v>0.0285042202850422</v>
+        <v>0.0284923928077455</v>
       </c>
       <c r="O247" t="b">
         <v>0</v>
@@ -19174,12 +19174,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ONI P2 (Head-Swap) by E.S Monster</t>
+          <t>Spider Demon P2  (Head-Swap) by E.S Monster</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4780060</t>
+          <t>https://cults3d.com/:4780086</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -19188,7 +19188,7 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46248.28496527778</v>
+        <v>46248.29128472223</v>
       </c>
       <c r="E253" t="n">
         <v>20</v>
@@ -19197,17 +19197,17 @@
         <v>237</v>
       </c>
       <c r="G253" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H253" t="n">
-        <v>657</v>
+        <v>749</v>
       </c>
       <c r="I253" t="b">
         <v>0</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>3d model, character, fanart, female, myth-inspired, oni, sculpt, stl</t>
+          <t>3d model, character, fanart, female, myth-inspired, sculpt, spider demon, stl</t>
         </is>
       </c>
       <c r="K253" t="n">
@@ -19220,10 +19220,10 @@
         <v>4740</v>
       </c>
       <c r="N253" t="n">
-        <v>0.3607305936073059</v>
+        <v>0.3164218958611482</v>
       </c>
       <c r="O253" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P253" t="b">
         <v>0</v>
@@ -19232,12 +19232,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Spider Demon P2  (Head-Swap) by E.S Monster</t>
+          <t>ONI P2 (Head-Swap) by E.S Monster</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4780086</t>
+          <t>https://cults3d.com/:4780060</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -19246,7 +19246,7 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46248.29128472223</v>
+        <v>46248.28496527778</v>
       </c>
       <c r="E254" t="n">
         <v>20</v>
@@ -19255,17 +19255,17 @@
         <v>237</v>
       </c>
       <c r="G254" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H254" t="n">
-        <v>749</v>
+        <v>657</v>
       </c>
       <c r="I254" t="b">
         <v>0</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>3d model, character, fanart, female, myth-inspired, sculpt, spider demon, stl</t>
+          <t>3d model, character, fanart, female, myth-inspired, oni, sculpt, stl</t>
         </is>
       </c>
       <c r="K254" t="n">
@@ -19278,10 +19278,10 @@
         <v>4740</v>
       </c>
       <c r="N254" t="n">
-        <v>0.3164218958611482</v>
+        <v>0.3607305936073059</v>
       </c>
       <c r="O254" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P254" t="b">
         <v>0</v>
@@ -19490,7 +19490,7 @@
         <v>38</v>
       </c>
       <c r="H258" t="n">
-        <v>8022</v>
+        <v>8025</v>
       </c>
       <c r="I258" t="b">
         <v>0</v>
@@ -19510,7 +19510,7 @@
         <v>310.98</v>
       </c>
       <c r="N258" t="n">
-        <v>0.02655198204936425</v>
+        <v>0.02654205607476635</v>
       </c>
       <c r="O258" t="b">
         <v>1</v>
@@ -19548,7 +19548,7 @@
         <v>30</v>
       </c>
       <c r="H259" t="n">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="I259" t="b">
         <v>0</v>
@@ -19568,7 +19568,7 @@
         <v>1554.72</v>
       </c>
       <c r="N259" t="n">
-        <v>0.02791519434628975</v>
+        <v>0.02791026320438085</v>
       </c>
       <c r="O259" t="b">
         <v>0</v>
@@ -19780,7 +19780,7 @@
         <v>65</v>
       </c>
       <c r="H263" t="n">
-        <v>8125</v>
+        <v>8126</v>
       </c>
       <c r="I263" t="b">
         <v>0</v>
@@ -19800,7 +19800,7 @@
         <v>1753.3</v>
       </c>
       <c r="N263" t="n">
-        <v>0.02424615384615385</v>
+        <v>0.02424317007137583</v>
       </c>
       <c r="O263" t="b">
         <v>0</v>
@@ -20418,7 +20418,7 @@
         <v>68</v>
       </c>
       <c r="H274" t="n">
-        <v>8697</v>
+        <v>8699</v>
       </c>
       <c r="I274" t="b">
         <v>0</v>
@@ -20438,7 +20438,7 @@
         <v>902.88</v>
       </c>
       <c r="N274" t="n">
-        <v>0.02621593652983787</v>
+        <v>0.02620990918496379</v>
       </c>
       <c r="O274" t="b">
         <v>1</v>
@@ -20534,7 +20534,7 @@
         <v>39</v>
       </c>
       <c r="H276" t="n">
-        <v>11431</v>
+        <v>11433</v>
       </c>
       <c r="I276" t="b">
         <v>0</v>
@@ -20554,7 +20554,7 @@
         <v>1727.1</v>
       </c>
       <c r="N276" t="n">
-        <v>0.01495932114425685</v>
+        <v>0.01495670427709263</v>
       </c>
       <c r="O276" t="b">
         <v>0</v>
@@ -20592,7 +20592,7 @@
         <v>12</v>
       </c>
       <c r="H277" t="n">
-        <v>5349</v>
+        <v>5350</v>
       </c>
       <c r="I277" t="b">
         <v>0</v>
@@ -20612,7 +20612,7 @@
         <v>707.7</v>
       </c>
       <c r="N277" t="n">
-        <v>0.03925967470555244</v>
+        <v>0.03925233644859813</v>
       </c>
       <c r="O277" t="b">
         <v>0</v>
@@ -20824,7 +20824,7 @@
         <v>43</v>
       </c>
       <c r="H281" t="n">
-        <v>6015</v>
+        <v>6018</v>
       </c>
       <c r="I281" t="b">
         <v>0</v>
@@ -20844,7 +20844,7 @@
         <v>1137.5</v>
       </c>
       <c r="N281" t="n">
-        <v>0.03025768911055694</v>
+        <v>0.03024260551678298</v>
       </c>
       <c r="O281" t="b">
         <v>0</v>
@@ -20940,7 +20940,7 @@
         <v>48</v>
       </c>
       <c r="H283" t="n">
-        <v>5389</v>
+        <v>5390</v>
       </c>
       <c r="I283" t="b">
         <v>0</v>
@@ -20960,7 +20960,7 @@
         <v>712.8</v>
       </c>
       <c r="N283" t="n">
-        <v>0.03340137316756356</v>
+        <v>0.03339517625231911</v>
       </c>
       <c r="O283" t="b">
         <v>1</v>
@@ -21396,7 +21396,7 @@
         <v>34</v>
       </c>
       <c r="H291" t="n">
-        <v>4824</v>
+        <v>4826</v>
       </c>
       <c r="I291" t="b">
         <v>0</v>
@@ -21416,7 +21416,7 @@
         <v>677.16</v>
       </c>
       <c r="N291" t="n">
-        <v>0.03544776119402985</v>
+        <v>0.03543307086614173</v>
       </c>
       <c r="O291" t="b">
         <v>1</v>

--- a/reportes/cults3d_mercado.xlsx
+++ b/reportes/cults3d_mercado.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>126051</v>
+        <v>126056</v>
       </c>
     </row>
     <row r="5">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1862517.81</v>
+        <v>1862617.81</v>
       </c>
     </row>
     <row r="6">
@@ -656,7 +656,7 @@
         <v>60913.77</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4009610784027507</v>
+        <v>0.4007962389810734</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>82770</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3241628009411123</v>
+        <v>0.3238041921463607</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -791,7 +791,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>101262.96</v>
+        <v>101282.96</v>
       </c>
       <c r="H5" t="n">
         <v>0.3102012491325468</v>
@@ -1113,7 +1113,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>141925</v>
+        <v>141945</v>
       </c>
       <c r="H12" t="n">
         <v>0.2668106940318661</v>
@@ -1159,7 +1159,7 @@
         <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>319495.3</v>
+        <v>319515.3</v>
       </c>
       <c r="H13" t="n">
         <v>0.2660064808861755</v>
@@ -1297,7 +1297,7 @@
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>299686.05</v>
+        <v>299706.05</v>
       </c>
       <c r="H16" t="n">
         <v>0.3692458374142997</v>
@@ -1343,10 +1343,10 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>237791.03</v>
+        <v>237831.03</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3412322274881517</v>
+        <v>0.3412220309810671</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1484,7 +1484,7 @@
         <v>8706</v>
       </c>
       <c r="H20" t="n">
-        <v>0.05817959918536833</v>
+        <v>0.05816376412713289</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1573,10 +1573,10 @@
         <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>47354.09</v>
+        <v>47394.09</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1418237624806511</v>
+        <v>0.1419042913608131</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1714,7 +1714,7 @@
         <v>37284</v>
       </c>
       <c r="H25" t="n">
-        <v>0.36330608537693</v>
+        <v>0.3629764065335753</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1803,10 +1803,10 @@
         <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>440895</v>
+        <v>440915</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3091190108191654</v>
+        <v>0.3086522462562396</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -1852,7 +1852,7 @@
         <v>61904.14</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2997740431553964</v>
+        <v>0.2996698645108686</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -1944,7 +1944,7 @@
         <v>20105.16</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0513748488182459</v>
+        <v>0.05136445794598138</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -2082,7 +2082,7 @@
         <v>111895</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3413147913726289</v>
+        <v>0.3411772140806634</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -2125,10 +2125,10 @@
         <v>21</v>
       </c>
       <c r="G34" t="n">
-        <v>49201.2</v>
+        <v>49221.2</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2936682362588529</v>
+        <v>0.2936631380053106</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -2174,7 +2174,7 @@
         <v>85275</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2719898734913903</v>
+        <v>0.2718050776578153</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -2312,7 +2312,7 @@
         <v>52375.21</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3481798699193402</v>
+        <v>0.3480746738824795</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -2355,10 +2355,10 @@
         <v>15</v>
       </c>
       <c r="G39" t="n">
-        <v>68234.03999999999</v>
+        <v>68254.03999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3412322274881517</v>
+        <v>0.3412220309810671</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -2818,7 +2818,7 @@
         <v>8263.889999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>0.05363606449489964</v>
+        <v>0.05361842105263158</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -3091,10 +3091,10 @@
         <v>17.5</v>
       </c>
       <c r="G55" t="n">
-        <v>477059.58</v>
+        <v>477079.58</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3471317758952237</v>
+        <v>0.3469777072440909</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -3370,7 +3370,7 @@
         <v>31605.83</v>
       </c>
       <c r="H61" t="n">
-        <v>0.03709285622964752</v>
+        <v>0.03708928095218044</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
@@ -3459,10 +3459,10 @@
         <v>9</v>
       </c>
       <c r="G63" t="n">
-        <v>70407.39</v>
+        <v>70427.39</v>
       </c>
       <c r="H63" t="n">
-        <v>0.03300838036599966</v>
+        <v>0.03299709352025988</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -3738,7 +3738,7 @@
         <v>26520.44</v>
       </c>
       <c r="H69" t="n">
-        <v>0.03820662691202611</v>
+        <v>0.03820305163455903</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
@@ -3784,7 +3784,7 @@
         <v>26662.4</v>
       </c>
       <c r="H70" t="n">
-        <v>0.03730029702167829</v>
+        <v>0.03729672174421123</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -4014,7 +4014,7 @@
         <v>95143.53999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>0.03593056116269681</v>
+        <v>0.03592330978809283</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
@@ -4106,7 +4106,7 @@
         <v>23318.46</v>
       </c>
       <c r="H77" t="n">
-        <v>0.03052285792499316</v>
+        <v>0.03051868071712057</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -4152,7 +4152,7 @@
         <v>7791.44</v>
       </c>
       <c r="H78" t="n">
-        <v>0.09641349249741815</v>
+        <v>0.09639363907241871</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
@@ -4198,7 +4198,7 @@
         <v>19761.93</v>
       </c>
       <c r="H79" t="n">
-        <v>0.02358272004578713</v>
+        <v>0.02357674439536035</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -4244,7 +4244,7 @@
         <v>5554.059999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1054613935969868</v>
+        <v>0.105421686746988</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -4287,10 +4287,10 @@
         <v>10.12</v>
       </c>
       <c r="G81" t="n">
-        <v>26850.7</v>
+        <v>26870.7</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2251714882195049</v>
+        <v>0.2253353204172876</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -4432,7 +4432,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1713553.13</v>
+        <v>1713653.13</v>
       </c>
       <c r="G2" t="n">
         <v>0.2546607401742899</v>
@@ -4463,7 +4463,7 @@
         <v>54461</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03024260551678298</v>
+        <v>0.03023255813953488</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -4650,7 +4650,7 @@
         <v>177</v>
       </c>
       <c r="H2" t="n">
-        <v>25584</v>
+        <v>25600</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4670,7 +4670,7 @@
         <v>9489.35</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03302845528455284</v>
+        <v>0.0330078125</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
@@ -4708,7 +4708,7 @@
         <v>1056</v>
       </c>
       <c r="H3" t="n">
-        <v>279756</v>
+        <v>279757</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>30120.96</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01212485165644347</v>
+        <v>0.01212480831578834</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -4766,7 +4766,7 @@
         <v>111</v>
       </c>
       <c r="H4" t="n">
-        <v>44437</v>
+        <v>44442</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4786,7 +4786,7 @@
         <v>6016</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01692283457479128</v>
+        <v>0.01692093065118581</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -4824,7 +4824,7 @@
         <v>29</v>
       </c>
       <c r="H5" t="n">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4844,7 +4844,7 @@
         <v>16000</v>
       </c>
       <c r="N5" t="n">
-        <v>0.36330608537693</v>
+        <v>0.3629764065335753</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -4882,7 +4882,7 @@
         <v>33</v>
       </c>
       <c r="H6" t="n">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4902,7 +4902,7 @@
         <v>15900</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3862973760932945</v>
+        <v>0.3859223300970874</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -4934,13 +4934,13 @@
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G7" t="n">
         <v>36</v>
       </c>
       <c r="H7" t="n">
-        <v>2321</v>
+        <v>2324</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4954,13 +4954,13 @@
         <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>34.43478260869565</v>
+        <v>34.47826086956522</v>
       </c>
       <c r="M7" t="n">
-        <v>15840</v>
+        <v>15860</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3412322274881517</v>
+        <v>0.3412220309810671</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -4998,7 +4998,7 @@
         <v>36</v>
       </c>
       <c r="H8" t="n">
-        <v>2311</v>
+        <v>2314</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -5018,7 +5018,7 @@
         <v>15760</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3409779316313284</v>
+        <v>0.3405358686257562</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>256</v>
       </c>
       <c r="H9" t="n">
-        <v>81254</v>
+        <v>81257</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -5076,7 +5076,7 @@
         <v>9574.970000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02556181849508947</v>
+        <v>0.02556087475540569</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
@@ -5114,7 +5114,7 @@
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>2722</v>
+        <v>2724</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>15600</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2865540044085231</v>
+        <v>0.2863436123348018</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
@@ -5166,13 +5166,13 @@
         <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="G11" t="n">
         <v>26</v>
       </c>
       <c r="H11" t="n">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -5186,13 +5186,13 @@
         <v>23</v>
       </c>
       <c r="L11" t="n">
-        <v>33.30434782608695</v>
+        <v>33.34782608695652</v>
       </c>
       <c r="M11" t="n">
-        <v>15320</v>
+        <v>15340</v>
       </c>
       <c r="N11" t="n">
-        <v>0.416984213391399</v>
+        <v>0.4168478260869565</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
@@ -5224,13 +5224,13 @@
         <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G12" t="n">
         <v>74</v>
       </c>
       <c r="H12" t="n">
-        <v>3353</v>
+        <v>3355</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -5244,13 +5244,13 @@
         <v>23</v>
       </c>
       <c r="L12" t="n">
-        <v>32.82608695652174</v>
+        <v>32.8695652173913</v>
       </c>
       <c r="M12" t="n">
-        <v>15100</v>
+        <v>15120</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2251714882195049</v>
+        <v>0.2253353204172876</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -5282,13 +5282,13 @@
         <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G13" t="n">
         <v>54</v>
       </c>
       <c r="H13" t="n">
-        <v>3034</v>
+        <v>3036</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -5302,13 +5302,13 @@
         <v>23</v>
       </c>
       <c r="L13" t="n">
-        <v>31.30434782608696</v>
+        <v>31.34782608695652</v>
       </c>
       <c r="M13" t="n">
-        <v>14400</v>
+        <v>14420</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2373104812129202</v>
+        <v>0.2374835309617918</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
@@ -5340,13 +5340,13 @@
         <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G14" t="n">
         <v>39</v>
       </c>
       <c r="H14" t="n">
-        <v>3110</v>
+        <v>3113</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>23</v>
       </c>
       <c r="L14" t="n">
-        <v>30.73913043478261</v>
+        <v>30.78260869565218</v>
       </c>
       <c r="M14" t="n">
-        <v>14140</v>
+        <v>14160</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2273311897106109</v>
+        <v>0.2274333440411179</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>81</v>
       </c>
       <c r="H16" t="n">
-        <v>40288</v>
+        <v>40290</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -5482,7 +5482,7 @@
         <v>1005</v>
       </c>
       <c r="N16" t="n">
-        <v>0.01861596505162828</v>
+        <v>0.0186150409530901</v>
       </c>
       <c r="O16" t="b">
         <v>1</v>
@@ -5552,12 +5552,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Strahd von Zarovich Bust3D Print</t>
+          <t>Claire Bust 3D Print</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020486</t>
+          <t>https://cults3d.com/:5020453</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46301.77325231482</v>
+        <v>46301.76777777778</v>
       </c>
       <c r="E18" t="n">
         <v>15</v>
@@ -5575,17 +5575,17 @@
         <v>417</v>
       </c>
       <c r="G18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>barovia, castle, dark, king, lord, noble, ruler, sinister, strahd, undead, vampire, villain, von, zarovich</t>
+          <t>claire, evil, female, figure, handgun, jacket, re, redfield, resident, survivor, veronica</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -5598,10 +5598,10 @@
         <v>6255</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5135467980295566</v>
+        <v>0.5325670498084292</v>
       </c>
       <c r="O18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -5610,12 +5610,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Claire Bust 3D Print</t>
+          <t>Strahd von Zarovich Bust3D Print</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020453</t>
+          <t>https://cults3d.com/:5020486</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5624,7 +5624,7 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46301.76777777778</v>
+        <v>46301.77325231482</v>
       </c>
       <c r="E19" t="n">
         <v>15</v>
@@ -5633,17 +5633,17 @@
         <v>417</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>claire, evil, female, figure, handgun, jacket, re, redfield, resident, survivor, veronica</t>
+          <t>barovia, castle, dark, king, lord, noble, ruler, sinister, strahd, undead, vampire, villain, von, zarovich</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -5656,10 +5656,10 @@
         <v>6255</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5325670498084292</v>
+        <v>0.5135467980295566</v>
       </c>
       <c r="O19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
@@ -6680,7 +6680,7 @@
         <v>26</v>
       </c>
       <c r="H37" t="n">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -6700,7 +6700,7 @@
         <v>9060</v>
       </c>
       <c r="N37" t="n">
-        <v>0.3073270013568521</v>
+        <v>0.3071186440677966</v>
       </c>
       <c r="O37" t="b">
         <v>0</v>
@@ -7260,7 +7260,7 @@
         <v>78</v>
       </c>
       <c r="H47" t="n">
-        <v>15348</v>
+        <v>15351</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -7280,7 +7280,7 @@
         <v>2154.24</v>
       </c>
       <c r="N47" t="n">
-        <v>0.02501954652071931</v>
+        <v>0.02501465702560094</v>
       </c>
       <c r="O47" t="b">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -7338,7 +7338,7 @@
         <v>8947.040000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>0.3503521126760563</v>
+        <v>0.3500439753737907</v>
       </c>
       <c r="O48" t="b">
         <v>0</v>
@@ -7376,7 +7376,7 @@
         <v>45</v>
       </c>
       <c r="H49" t="n">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -7396,7 +7396,7 @@
         <v>4260</v>
       </c>
       <c r="N49" t="n">
-        <v>0.08120472741136103</v>
+        <v>0.08117378048780488</v>
       </c>
       <c r="O49" t="b">
         <v>1</v>
@@ -7492,7 +7492,7 @@
         <v>28</v>
       </c>
       <c r="H51" t="n">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -7512,7 +7512,7 @@
         <v>5935.16</v>
       </c>
       <c r="N51" t="n">
-        <v>0.2582096266306793</v>
+        <v>0.2580935251798561</v>
       </c>
       <c r="O51" t="b">
         <v>1</v>
@@ -7550,7 +7550,7 @@
         <v>94</v>
       </c>
       <c r="H52" t="n">
-        <v>6417</v>
+        <v>6418</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -7570,7 +7570,7 @@
         <v>2172</v>
       </c>
       <c r="N52" t="n">
-        <v>0.05641265388810971</v>
+        <v>0.05640386413212839</v>
       </c>
       <c r="O52" t="b">
         <v>0</v>
@@ -7608,7 +7608,7 @@
         <v>23</v>
       </c>
       <c r="H53" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -7628,7 +7628,7 @@
         <v>5914.48</v>
       </c>
       <c r="N53" t="n">
-        <v>0.2907981698017285</v>
+        <v>0.290650406504065</v>
       </c>
       <c r="O53" t="b">
         <v>0</v>
@@ -7666,7 +7666,7 @@
         <v>18</v>
       </c>
       <c r="H54" t="n">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -7686,7 +7686,7 @@
         <v>4200</v>
       </c>
       <c r="N54" t="n">
-        <v>0.06099331977926227</v>
+        <v>0.06097560975609756</v>
       </c>
       <c r="O54" t="b">
         <v>1</v>
@@ -7840,7 +7840,7 @@
         <v>25</v>
       </c>
       <c r="H57" t="n">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -7860,7 +7860,7 @@
         <v>10290</v>
       </c>
       <c r="N57" t="n">
-        <v>0.307347670250896</v>
+        <v>0.3070725156669651</v>
       </c>
       <c r="O57" t="b">
         <v>0</v>
@@ -7898,7 +7898,7 @@
         <v>9</v>
       </c>
       <c r="H58" t="n">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
@@ -7918,7 +7918,7 @@
         <v>4721.5</v>
       </c>
       <c r="N58" t="n">
-        <v>0.4475703324808184</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="O58" t="b">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>10</v>
       </c>
       <c r="H59" t="n">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>8519.92</v>
       </c>
       <c r="N59" t="n">
-        <v>0.5080428954423593</v>
+        <v>0.5066844919786097</v>
       </c>
       <c r="O59" t="b">
         <v>1</v>
@@ -8072,7 +8072,7 @@
         <v>417</v>
       </c>
       <c r="H61" t="n">
-        <v>53413</v>
+        <v>53414</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -8092,7 +8092,7 @@
         <v>20484.9</v>
       </c>
       <c r="N61" t="n">
-        <v>0.007582423754516691</v>
+        <v>0.007582281798779346</v>
       </c>
       <c r="O61" t="b">
         <v>0</v>
@@ -8130,7 +8130,7 @@
         <v>14</v>
       </c>
       <c r="H62" t="n">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
@@ -8150,7 +8150,7 @@
         <v>10185</v>
       </c>
       <c r="N62" t="n">
-        <v>0.3708356089568542</v>
+        <v>0.370430987452264</v>
       </c>
       <c r="O62" t="b">
         <v>1</v>
@@ -8304,7 +8304,7 @@
         <v>22</v>
       </c>
       <c r="H65" t="n">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -8324,7 +8324,7 @@
         <v>10155</v>
       </c>
       <c r="N65" t="n">
-        <v>0.4387556707712249</v>
+        <v>0.4381877022653722</v>
       </c>
       <c r="O65" t="b">
         <v>1</v>
@@ -8362,7 +8362,7 @@
         <v>18</v>
       </c>
       <c r="H66" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
@@ -8382,7 +8382,7 @@
         <v>4020</v>
       </c>
       <c r="N66" t="n">
-        <v>0.313572542901716</v>
+        <v>0.3130841121495327</v>
       </c>
       <c r="O66" t="b">
         <v>1</v>
@@ -8420,7 +8420,7 @@
         <v>136</v>
       </c>
       <c r="H67" t="n">
-        <v>33724</v>
+        <v>33728</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
@@ -8440,7 +8440,7 @@
         <v>14806</v>
       </c>
       <c r="N67" t="n">
-        <v>0.01995611433993595</v>
+        <v>0.01995374762808349</v>
       </c>
       <c r="O67" t="b">
         <v>0</v>
@@ -8478,7 +8478,7 @@
         <v>22</v>
       </c>
       <c r="H68" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
@@ -8498,7 +8498,7 @@
         <v>4000</v>
       </c>
       <c r="N68" t="n">
-        <v>0.3091190108191654</v>
+        <v>0.3081664098613251</v>
       </c>
       <c r="O68" t="b">
         <v>1</v>
@@ -8652,7 +8652,7 @@
         <v>41</v>
       </c>
       <c r="H71" t="n">
-        <v>3473</v>
+        <v>3474</v>
       </c>
       <c r="I71" t="b">
         <v>0</v>
@@ -8672,7 +8672,7 @@
         <v>1440</v>
       </c>
       <c r="N71" t="n">
-        <v>0.06910452058738842</v>
+        <v>0.0690846286701209</v>
       </c>
       <c r="O71" t="b">
         <v>0</v>
@@ -8858,12 +8858,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Nanami - Jujutsu Kaisen</t>
+          <t>Big Daddy and Little Sister - BioShock</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971762</t>
+          <t>https://cults3d.com/:4971764</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46292.2184837963</v>
+        <v>46292.21871527778</v>
       </c>
       <c r="E75" t="n">
         <v>22.48</v>
@@ -8881,17 +8881,17 @@
         <v>362</v>
       </c>
       <c r="G75" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H75" t="n">
-        <v>865</v>
+        <v>1087</v>
       </c>
       <c r="I75" t="b">
         <v>0</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>fanart, jujutsu kaisen, miniature, nanami, resin, stl</t>
+          <t>big daddy, bioshock, fanart, miniature, resin, stl</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -8904,7 +8904,7 @@
         <v>8137.76</v>
       </c>
       <c r="N75" t="n">
-        <v>0.4184971098265896</v>
+        <v>0.3330266789328427</v>
       </c>
       <c r="O75" t="b">
         <v>0</v>
@@ -8916,12 +8916,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Big Daddy and Little Sister - BioShock</t>
+          <t>Nanami - Jujutsu Kaisen</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971764</t>
+          <t>https://cults3d.com/:4971762</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46292.21871527778</v>
+        <v>46292.2184837963</v>
       </c>
       <c r="E76" t="n">
         <v>22.48</v>
@@ -8939,17 +8939,17 @@
         <v>362</v>
       </c>
       <c r="G76" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H76" t="n">
-        <v>1086</v>
+        <v>865</v>
       </c>
       <c r="I76" t="b">
         <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>big daddy, bioshock, fanart, miniature, resin, stl</t>
+          <t>fanart, jujutsu kaisen, miniature, nanami, resin, stl</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -8962,7 +8962,7 @@
         <v>8137.76</v>
       </c>
       <c r="N76" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4184971098265896</v>
       </c>
       <c r="O76" t="b">
         <v>0</v>
@@ -9058,7 +9058,7 @@
         <v>205</v>
       </c>
       <c r="H78" t="n">
-        <v>17248</v>
+        <v>17252</v>
       </c>
       <c r="I78" t="b">
         <v>0</v>
@@ -9078,7 +9078,7 @@
         <v>4580</v>
       </c>
       <c r="N78" t="n">
-        <v>0.02655380333951763</v>
+        <v>0.02654764664966381</v>
       </c>
       <c r="O78" t="b">
         <v>0</v>
@@ -9348,7 +9348,7 @@
         <v>21</v>
       </c>
       <c r="H83" t="n">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="I83" t="b">
         <v>0</v>
@@ -9368,7 +9368,7 @@
         <v>6688</v>
       </c>
       <c r="N83" t="n">
-        <v>0.1166294642857143</v>
+        <v>0.1165644171779141</v>
       </c>
       <c r="O83" t="b">
         <v>1</v>
@@ -9406,7 +9406,7 @@
         <v>5</v>
       </c>
       <c r="H84" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I84" t="b">
         <v>0</v>
@@ -9426,7 +9426,7 @@
         <v>4168.41</v>
       </c>
       <c r="N84" t="n">
-        <v>0.6450939457202505</v>
+        <v>0.64375</v>
       </c>
       <c r="O84" t="b">
         <v>0</v>
@@ -9464,7 +9464,7 @@
         <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I85" t="b">
         <v>0</v>
@@ -9484,7 +9484,7 @@
         <v>4127.940000000001</v>
       </c>
       <c r="N85" t="n">
-        <v>0.5377855887521968</v>
+        <v>0.5368421052631579</v>
       </c>
       <c r="O85" t="b">
         <v>0</v>
@@ -9670,12 +9670,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Minthara-Baldurs Gate 3 3D Print</t>
+          <t>Silver Surfer - Bust</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4729255</t>
+          <t>https://cults3d.com/:4971680</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9684,42 +9684,42 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46234.47359953704</v>
+        <v>46295.03493055556</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>13.49</v>
       </c>
       <c r="F89" t="n">
-        <v>1050</v>
+        <v>300</v>
       </c>
       <c r="G89" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="H89" t="n">
-        <v>7546</v>
+        <v>476</v>
       </c>
       <c r="I89" t="b">
         <v>0</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>armor, baldur's, baldurs, bg3, bust, dark, dnd, elf, female, figure, gate, larian, mace, minthara, paladin</t>
+          <t>bust, fanart, herald, marvel, miniature, resin, silver surfer, stl</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="L89" t="n">
         <v>12.5</v>
       </c>
       <c r="M89" t="n">
-        <v>21000</v>
+        <v>4047</v>
       </c>
       <c r="N89" t="n">
-        <v>0.1391465677179963</v>
+        <v>0.6302521008403361</v>
       </c>
       <c r="O89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P89" t="b">
         <v>0</v>
@@ -9728,12 +9728,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Silver Surfer - Bust</t>
+          <t>Minthara-Baldurs Gate 3 3D Print</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971680</t>
+          <t>https://cults3d.com/:4729255</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9742,42 +9742,42 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46295.03493055556</v>
+        <v>46234.47359953704</v>
       </c>
       <c r="E90" t="n">
-        <v>13.49</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>300</v>
+        <v>1050</v>
       </c>
       <c r="G90" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="H90" t="n">
-        <v>476</v>
+        <v>7546</v>
       </c>
       <c r="I90" t="b">
         <v>0</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>bust, fanart, herald, marvel, miniature, resin, silver surfer, stl</t>
+          <t>armor, baldur's, baldurs, bg3, bust, dark, dnd, elf, female, figure, gate, larian, mace, minthara, paladin</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L90" t="n">
         <v>12.5</v>
       </c>
       <c r="M90" t="n">
-        <v>4047</v>
+        <v>21000</v>
       </c>
       <c r="N90" t="n">
-        <v>0.6302521008403361</v>
+        <v>0.1391465677179963</v>
       </c>
       <c r="O90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P90" t="b">
         <v>0</v>
@@ -9812,7 +9812,7 @@
         <v>34</v>
       </c>
       <c r="H91" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="I91" t="b">
         <v>0</v>
@@ -9832,7 +9832,7 @@
         <v>3828</v>
       </c>
       <c r="N91" t="n">
-        <v>0.1686046511627907</v>
+        <v>0.1684414327202323</v>
       </c>
       <c r="O91" t="b">
         <v>1</v>
@@ -9986,7 +9986,7 @@
         <v>42</v>
       </c>
       <c r="H94" t="n">
-        <v>2336</v>
+        <v>2339</v>
       </c>
       <c r="I94" t="b">
         <v>0</v>
@@ -10006,7 +10006,7 @@
         <v>5720</v>
       </c>
       <c r="N94" t="n">
-        <v>0.1224315068493151</v>
+        <v>0.1222744762719111</v>
       </c>
       <c r="O94" t="b">
         <v>1</v>
@@ -10018,12 +10018,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>pin head Fan art (no ams-multiparts/3mf)</t>
+          <t>Proxima the Broodseeker</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5055346</t>
+          <t>https://cults3d.com/:5079132</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10032,42 +10032,42 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46308.81805555556</v>
+        <v>46313.49111111111</v>
       </c>
       <c r="E95" t="n">
-        <v>3.96</v>
+        <v>17.6</v>
       </c>
       <c r="F95" t="n">
         <v>158</v>
       </c>
       <c r="G95" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="H95" t="n">
-        <v>3226</v>
+        <v>951</v>
       </c>
       <c r="I95" t="b">
         <v>0</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>3d print, 3mf, decor, decor master, decormaster, gift, multipart, no ams, toy</t>
+          <t>blasphemous, bloodborne, broodseeker, dark souls, elden ring, eredrim, h3llcreator, hadern, lady maria, lords of the fallen, malenia, mortal shell, mortal shell ii, proxima, tiel</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L95" t="n">
         <v>11.28571428571429</v>
       </c>
       <c r="M95" t="n">
-        <v>625.6799999999999</v>
+        <v>2780.8</v>
       </c>
       <c r="N95" t="n">
-        <v>0.04897706137631742</v>
+        <v>0.1661409043112513</v>
       </c>
       <c r="O95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P95" t="b">
         <v>0</v>
@@ -10076,12 +10076,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Proxima the Broodseeker</t>
+          <t>pin head Fan art (no ams-multiparts/3mf)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5079132</t>
+          <t>https://cults3d.com/:5055346</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10090,42 +10090,42 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46313.49111111111</v>
+        <v>46308.81805555556</v>
       </c>
       <c r="E96" t="n">
-        <v>17.6</v>
+        <v>3.96</v>
       </c>
       <c r="F96" t="n">
         <v>158</v>
       </c>
       <c r="G96" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="H96" t="n">
-        <v>950</v>
+        <v>3227</v>
       </c>
       <c r="I96" t="b">
         <v>0</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>blasphemous, bloodborne, broodseeker, dark souls, elden ring, eredrim, h3llcreator, hadern, lady maria, lords of the fallen, malenia, mortal shell, mortal shell ii, proxima, tiel</t>
+          <t>3d print, 3mf, decor, decor master, decormaster, gift, multipart, no ams, toy</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L96" t="n">
         <v>11.28571428571429</v>
       </c>
       <c r="M96" t="n">
-        <v>2780.8</v>
+        <v>625.6799999999999</v>
       </c>
       <c r="N96" t="n">
-        <v>0.1663157894736842</v>
+        <v>0.04896188410288194</v>
       </c>
       <c r="O96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P96" t="b">
         <v>0</v>
@@ -10160,7 +10160,7 @@
         <v>41</v>
       </c>
       <c r="H97" t="n">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="I97" t="b">
         <v>0</v>
@@ -10180,7 +10180,7 @@
         <v>942</v>
       </c>
       <c r="N97" t="n">
-        <v>0.05994654448262696</v>
+        <v>0.05992366412213741</v>
       </c>
       <c r="O97" t="b">
         <v>0</v>
@@ -10218,7 +10218,7 @@
         <v>122</v>
       </c>
       <c r="H98" t="n">
-        <v>14932</v>
+        <v>14934</v>
       </c>
       <c r="I98" t="b">
         <v>0</v>
@@ -10238,7 +10238,7 @@
         <v>2399.76</v>
       </c>
       <c r="N98" t="n">
-        <v>0.04058398071256362</v>
+        <v>0.04057854560064283</v>
       </c>
       <c r="O98" t="b">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>70</v>
       </c>
       <c r="H101" t="n">
-        <v>7306</v>
+        <v>7307</v>
       </c>
       <c r="I101" t="b">
         <v>0</v>
@@ -10412,7 +10412,7 @@
         <v>2007</v>
       </c>
       <c r="N101" t="n">
-        <v>0.03052285792499316</v>
+        <v>0.03051868071712057</v>
       </c>
       <c r="O101" t="b">
         <v>0</v>
@@ -10540,12 +10540,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Yuria of Londor Bust 3D Print</t>
+          <t>Minthara Bust 3D Print</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4749861</t>
+          <t>https://cults3d.com/:4749441</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46239.81805555556</v>
+        <v>46239.73216435185</v>
       </c>
       <c r="E104" t="n">
         <v>15</v>
@@ -10563,17 +10563,17 @@
         <v>832</v>
       </c>
       <c r="G104" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H104" t="n">
-        <v>3232</v>
+        <v>2217</v>
       </c>
       <c r="I104" t="b">
         <v>0</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>dark, fromsoftware, game, londor, religion, role-playing, rpg, souls, video, yuria</t>
+          <t>armor, baldur's, baldurs, bg3, bust, dark, dnd, elf, female, figure, gate, larian, mace, minthara, paladin</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -10586,7 +10586,7 @@
         <v>12480</v>
       </c>
       <c r="N104" t="n">
-        <v>0.2574257425742574</v>
+        <v>0.3752819124943618</v>
       </c>
       <c r="O104" t="b">
         <v>0</v>
@@ -10598,12 +10598,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Minthara Bust 3D Print</t>
+          <t>Yuria of Londor Bust 3D Print</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4749441</t>
+          <t>https://cults3d.com/:4749861</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46239.73216435185</v>
+        <v>46239.81805555556</v>
       </c>
       <c r="E105" t="n">
         <v>15</v>
@@ -10621,17 +10621,17 @@
         <v>832</v>
       </c>
       <c r="G105" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H105" t="n">
-        <v>2217</v>
+        <v>3234</v>
       </c>
       <c r="I105" t="b">
         <v>0</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>armor, baldur's, baldurs, bg3, bust, dark, dnd, elf, female, figure, gate, larian, mace, minthara, paladin</t>
+          <t>dark, fromsoftware, game, londor, religion, role-playing, rpg, souls, video, yuria</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -10644,7 +10644,7 @@
         <v>12480</v>
       </c>
       <c r="N105" t="n">
-        <v>0.3752819124943618</v>
+        <v>0.2572665429808287</v>
       </c>
       <c r="O105" t="b">
         <v>0</v>
@@ -10856,7 +10856,7 @@
         <v>24</v>
       </c>
       <c r="H109" t="n">
-        <v>4343</v>
+        <v>4345</v>
       </c>
       <c r="I109" t="b">
         <v>0</v>
@@ -10876,7 +10876,7 @@
         <v>17460</v>
       </c>
       <c r="N109" t="n">
-        <v>0.2010131245682708</v>
+        <v>0.2009205983889528</v>
       </c>
       <c r="O109" t="b">
         <v>0</v>
@@ -10972,7 +10972,7 @@
         <v>62</v>
       </c>
       <c r="H111" t="n">
-        <v>5346</v>
+        <v>5348</v>
       </c>
       <c r="I111" t="b">
         <v>0</v>
@@ -10992,7 +10992,7 @@
         <v>2124</v>
       </c>
       <c r="N111" t="n">
-        <v>0.04414515525626637</v>
+        <v>0.04412864622288706</v>
       </c>
       <c r="O111" t="b">
         <v>0</v>
@@ -11204,7 +11204,7 @@
         <v>6</v>
       </c>
       <c r="H115" t="n">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="I115" t="b">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>922.1999999999999</v>
       </c>
       <c r="N115" t="n">
-        <v>0.1640866873065016</v>
+        <v>0.1635802469135803</v>
       </c>
       <c r="O115" t="b">
         <v>0</v>
@@ -11320,7 +11320,7 @@
         <v>233</v>
       </c>
       <c r="H117" t="n">
-        <v>30139</v>
+        <v>30140</v>
       </c>
       <c r="I117" t="b">
         <v>0</v>
@@ -11340,7 +11340,7 @@
         <v>1134</v>
       </c>
       <c r="N117" t="n">
-        <v>0.006270944623245628</v>
+        <v>0.006270736562707366</v>
       </c>
       <c r="O117" t="b">
         <v>1</v>
@@ -11378,7 +11378,7 @@
         <v>54</v>
       </c>
       <c r="H118" t="n">
-        <v>3863</v>
+        <v>3864</v>
       </c>
       <c r="I118" t="b">
         <v>0</v>
@@ -11398,7 +11398,7 @@
         <v>1611</v>
       </c>
       <c r="N118" t="n">
-        <v>0.04633704374838209</v>
+        <v>0.04632505175983437</v>
       </c>
       <c r="O118" t="b">
         <v>0</v>
@@ -11436,7 +11436,7 @@
         <v>24</v>
       </c>
       <c r="H119" t="n">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="I119" t="b">
         <v>0</v>
@@ -11456,7 +11456,7 @@
         <v>4140</v>
       </c>
       <c r="N119" t="n">
-        <v>0.1633780584056827</v>
+        <v>0.1632492113564669</v>
       </c>
       <c r="O119" t="b">
         <v>0</v>
@@ -11552,7 +11552,7 @@
         <v>29</v>
       </c>
       <c r="H121" t="n">
-        <v>2987</v>
+        <v>2988</v>
       </c>
       <c r="I121" t="b">
         <v>0</v>
@@ -11572,7 +11572,7 @@
         <v>1218</v>
       </c>
       <c r="N121" t="n">
-        <v>0.06796116504854369</v>
+        <v>0.0679384203480589</v>
       </c>
       <c r="O121" t="b">
         <v>0</v>
@@ -11668,7 +11668,7 @@
         <v>61</v>
       </c>
       <c r="H123" t="n">
-        <v>19778</v>
+        <v>19786</v>
       </c>
       <c r="I123" t="b">
         <v>1</v>
@@ -11688,7 +11688,7 @@
         <v>5850</v>
       </c>
       <c r="N123" t="n">
-        <v>0.01971887956315098</v>
+        <v>0.01971090670170828</v>
       </c>
       <c r="O123" t="b">
         <v>0</v>
@@ -11784,7 +11784,7 @@
         <v>39</v>
       </c>
       <c r="H125" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="I125" t="b">
         <v>0</v>
@@ -11804,7 +11804,7 @@
         <v>6006</v>
       </c>
       <c r="N125" t="n">
-        <v>0.1402877697841727</v>
+        <v>0.1402157164869029</v>
       </c>
       <c r="O125" t="b">
         <v>1</v>
@@ -13002,7 +13002,7 @@
         <v>165</v>
       </c>
       <c r="H146" t="n">
-        <v>27139</v>
+        <v>27141</v>
       </c>
       <c r="I146" t="b">
         <v>0</v>
@@ -13022,7 +13022,7 @@
         <v>5796</v>
       </c>
       <c r="N146" t="n">
-        <v>0.0237296879030178</v>
+        <v>0.023727939280056</v>
       </c>
       <c r="O146" t="b">
         <v>0</v>
@@ -13118,7 +13118,7 @@
         <v>271</v>
       </c>
       <c r="H148" t="n">
-        <v>33345</v>
+        <v>33346</v>
       </c>
       <c r="I148" t="b">
         <v>0</v>
@@ -13138,7 +13138,7 @@
         <v>1740</v>
       </c>
       <c r="N148" t="n">
-        <v>0.008696956065377117</v>
+        <v>0.008696695255802795</v>
       </c>
       <c r="O148" t="b">
         <v>0</v>
@@ -14568,7 +14568,7 @@
         <v>68</v>
       </c>
       <c r="H173" t="n">
-        <v>5847</v>
+        <v>5849</v>
       </c>
       <c r="I173" t="b">
         <v>0</v>
@@ -14588,7 +14588,7 @@
         <v>1737</v>
       </c>
       <c r="N173" t="n">
-        <v>0.03300838036599966</v>
+        <v>0.03299709352025988</v>
       </c>
       <c r="O173" t="b">
         <v>0</v>
@@ -14858,7 +14858,7 @@
         <v>65</v>
       </c>
       <c r="H178" t="n">
-        <v>7893</v>
+        <v>7894</v>
       </c>
       <c r="I178" t="b">
         <v>0</v>
@@ -14878,7 +14878,7 @@
         <v>1842</v>
       </c>
       <c r="N178" t="n">
-        <v>0.03889522361586216</v>
+        <v>0.03889029642766658</v>
       </c>
       <c r="O178" t="b">
         <v>1</v>
@@ -14916,7 +14916,7 @@
         <v>11</v>
       </c>
       <c r="H179" t="n">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="I179" t="b">
         <v>0</v>
@@ -14936,7 +14936,7 @@
         <v>152.1</v>
       </c>
       <c r="N179" t="n">
-        <v>0.09564233163554046</v>
+        <v>0.09558823529411764</v>
       </c>
       <c r="O179" t="b">
         <v>1</v>
@@ -15032,7 +15032,7 @@
         <v>53</v>
       </c>
       <c r="H181" t="n">
-        <v>4538</v>
+        <v>4539</v>
       </c>
       <c r="I181" t="b">
         <v>0</v>
@@ -15052,7 +15052,7 @@
         <v>1152</v>
       </c>
       <c r="N181" t="n">
-        <v>0.04230938739532834</v>
+        <v>0.04230006609385327</v>
       </c>
       <c r="O181" t="b">
         <v>1</v>
@@ -15090,7 +15090,7 @@
         <v>154</v>
       </c>
       <c r="H182" t="n">
-        <v>28306</v>
+        <v>28307</v>
       </c>
       <c r="I182" t="b">
         <v>0</v>
@@ -15110,7 +15110,7 @@
         <v>799.22</v>
       </c>
       <c r="N182" t="n">
-        <v>0.006288419416378153</v>
+        <v>0.006288197265693998</v>
       </c>
       <c r="O182" t="b">
         <v>0</v>
@@ -15322,7 +15322,7 @@
         <v>18</v>
       </c>
       <c r="H186" t="n">
-        <v>3039</v>
+        <v>3040</v>
       </c>
       <c r="I186" t="b">
         <v>0</v>
@@ -15342,7 +15342,7 @@
         <v>146.7</v>
       </c>
       <c r="N186" t="n">
-        <v>0.05363606449489964</v>
+        <v>0.05361842105263158</v>
       </c>
       <c r="O186" t="b">
         <v>1</v>
@@ -15470,117 +15470,117 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SPIN POP GRENADE</t>
+          <t>Looney Tunes x Chicago Bulls Trio – Daffy | No AMS / Multi-Part / 3MF</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4837786</t>
+          <t>https://cults3d.com/:4780701</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>Art</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46262.06622685185</v>
+        <v>46248.43848379629</v>
       </c>
       <c r="E189" t="n">
-        <v>3.76</v>
+        <v>6</v>
       </c>
       <c r="F189" t="n">
-        <v>342</v>
+        <v>420</v>
       </c>
       <c r="G189" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H189" t="n">
-        <v>4588</v>
+        <v>6489</v>
       </c>
       <c r="I189" t="b">
         <v>0</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>ball, elastic, grenade, hopping, jumping, mechanical, physics, pop, popper, powered, spin, spinner, stem, toy</t>
+          <t>basketball, bugs bunny, cartoon figure, chicagobulls, cw prestige, cwprestige, daffyduck, fdm printing, lolabunny, looney tunes, multi parts, noams, urban vibes, urban vibes collection</t>
         </is>
       </c>
       <c r="K189" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="L189" t="n">
         <v>6</v>
       </c>
       <c r="M189" t="n">
-        <v>1285.92</v>
+        <v>2520</v>
       </c>
       <c r="N189" t="n">
-        <v>0.07454228421970358</v>
+        <v>0.06472491909385113</v>
       </c>
       <c r="O189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Looney Tunes x Chicago Bulls Trio – Daffy | No AMS / Multi-Part / 3MF</t>
+          <t>SPIN POP GRENADE</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4780701</t>
+          <t>https://cults3d.com/:4837786</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Art</t>
+          <t>Various</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46248.43848379629</v>
+        <v>46262.06622685185</v>
       </c>
       <c r="E190" t="n">
-        <v>6</v>
+        <v>3.76</v>
       </c>
       <c r="F190" t="n">
-        <v>420</v>
+        <v>342</v>
       </c>
       <c r="G190" t="n">
+        <v>41</v>
+      </c>
+      <c r="H190" t="n">
+        <v>4588</v>
+      </c>
+      <c r="I190" t="b">
+        <v>0</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>ball, elastic, grenade, hopping, jumping, mechanical, physics, pop, popper, powered, spin, spinner, stem, toy</t>
+        </is>
+      </c>
+      <c r="K190" t="n">
         <v>57</v>
-      </c>
-      <c r="H190" t="n">
-        <v>6489</v>
-      </c>
-      <c r="I190" t="b">
-        <v>0</v>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>basketball, bugs bunny, cartoon figure, chicagobulls, cw prestige, cwprestige, daffyduck, fdm printing, lolabunny, looney tunes, multi parts, noams, urban vibes, urban vibes collection</t>
-        </is>
-      </c>
-      <c r="K190" t="n">
-        <v>70</v>
       </c>
       <c r="L190" t="n">
         <v>6</v>
       </c>
       <c r="M190" t="n">
-        <v>2520</v>
+        <v>1285.92</v>
       </c>
       <c r="N190" t="n">
-        <v>0.06472491909385113</v>
+        <v>0.07454228421970358</v>
       </c>
       <c r="O190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P190" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -16134,7 +16134,7 @@
         <v>148</v>
       </c>
       <c r="H200" t="n">
-        <v>29941</v>
+        <v>29942</v>
       </c>
       <c r="I200" t="b">
         <v>0</v>
@@ -16154,7 +16154,7 @@
         <v>2700</v>
       </c>
       <c r="N200" t="n">
-        <v>0.01502955813099095</v>
+        <v>0.01502905617527219</v>
       </c>
       <c r="O200" t="b">
         <v>1</v>
@@ -16250,7 +16250,7 @@
         <v>105</v>
       </c>
       <c r="H202" t="n">
-        <v>7942</v>
+        <v>7943</v>
       </c>
       <c r="I202" t="b">
         <v>0</v>
@@ -16270,7 +16270,7 @@
         <v>667.26</v>
       </c>
       <c r="N202" t="n">
-        <v>0.02493074792243767</v>
+        <v>0.02492760921566159</v>
       </c>
       <c r="O202" t="b">
         <v>0</v>
@@ -16362,7 +16362,7 @@
         <v>31</v>
       </c>
       <c r="H204" t="n">
-        <v>15263</v>
+        <v>15264</v>
       </c>
       <c r="I204" t="b">
         <v>0</v>
@@ -16382,7 +16382,7 @@
         <v>272.09</v>
       </c>
       <c r="N204" t="n">
-        <v>0.01054838498329293</v>
+        <v>0.01054769392033543</v>
       </c>
       <c r="O204" t="b">
         <v>1</v>
@@ -16652,7 +16652,7 @@
         <v>15</v>
       </c>
       <c r="H209" t="n">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="I209" t="b">
         <v>0</v>
@@ -16672,7 +16672,7 @@
         <v>940.8</v>
       </c>
       <c r="N209" t="n">
-        <v>0.1054613935969868</v>
+        <v>0.105421686746988</v>
       </c>
       <c r="O209" t="b">
         <v>0</v>
@@ -16710,7 +16710,7 @@
         <v>45</v>
       </c>
       <c r="H210" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="I210" t="b">
         <v>0</v>
@@ -16730,7 +16730,7 @@
         <v>677.16</v>
       </c>
       <c r="N210" t="n">
-        <v>0.05599214145383104</v>
+        <v>0.05597381342062193</v>
       </c>
       <c r="O210" t="b">
         <v>0</v>
@@ -16942,7 +16942,7 @@
         <v>31</v>
       </c>
       <c r="H214" t="n">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="I214" t="b">
         <v>0</v>
@@ -16962,7 +16962,7 @@
         <v>673.2</v>
       </c>
       <c r="N214" t="n">
-        <v>0.05716207128446537</v>
+        <v>0.05714285714285714</v>
       </c>
       <c r="O214" t="b">
         <v>0</v>
@@ -17496,12 +17496,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Eva 01 - Neon Genesis Evangelion - Bust</t>
+          <t>Master Splinter Fan art (no ams-multiparts/3mf)</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4724530</t>
+          <t>https://cults3d.com/:4911957</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -17510,39 +17510,39 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46234.11200231482</v>
+        <v>46279.61715277778</v>
       </c>
       <c r="E224" t="n">
-        <v>13.49</v>
+        <v>3.96</v>
       </c>
       <c r="F224" t="n">
-        <v>402</v>
+        <v>186</v>
       </c>
       <c r="G224" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="H224" t="n">
-        <v>1356</v>
+        <v>3897</v>
       </c>
       <c r="I224" t="b">
         <v>0</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>anime, bust, collectible, eva01, evangelion, mecha, miniature, neongenesisevangelion, resin, stl</t>
+          <t>3d print, 3mf, decor, decor master, decormaster, donatello, gift, leonardo, michelangelo, multipart, no ams, raphael, splinter, teenage mutant ninja turtles, tmnt, toy</t>
         </is>
       </c>
       <c r="K224" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="L224" t="n">
-        <v>4.785714285714286</v>
+        <v>4.769230769230769</v>
       </c>
       <c r="M224" t="n">
-        <v>5422.98</v>
+        <v>736.5599999999999</v>
       </c>
       <c r="N224" t="n">
-        <v>0.2964601769911505</v>
+        <v>0.04772902232486528</v>
       </c>
       <c r="O224" t="b">
         <v>0</v>
@@ -17554,12 +17554,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Master Splinter Fan art (no ams-multiparts/3mf)</t>
+          <t>Edward - Assassin's Creed - Bust</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4911957</t>
+          <t>https://cults3d.com/:4724633</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -17568,39 +17568,39 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46279.61715277778</v>
+        <v>46234.02446759259</v>
       </c>
       <c r="E225" t="n">
-        <v>3.96</v>
+        <v>13.49</v>
       </c>
       <c r="F225" t="n">
-        <v>186</v>
+        <v>404</v>
       </c>
       <c r="G225" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="H225" t="n">
-        <v>3897</v>
+        <v>984</v>
       </c>
       <c r="I225" t="b">
         <v>0</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>3d print, 3mf, decor, decor master, decormaster, donatello, gift, leonardo, michelangelo, multipart, no ams, raphael, splinter, teenage mutant ninja turtles, tmnt, toy</t>
+          <t>assassin, assassinscreed, bust, collectible, edward, miniature, pirate, resin, stl, ubisoft</t>
         </is>
       </c>
       <c r="K225" t="n">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="L225" t="n">
-        <v>4.769230769230769</v>
+        <v>4.752941176470588</v>
       </c>
       <c r="M225" t="n">
-        <v>736.5599999999999</v>
+        <v>5449.96</v>
       </c>
       <c r="N225" t="n">
-        <v>0.04772902232486528</v>
+        <v>0.4105691056910569</v>
       </c>
       <c r="O225" t="b">
         <v>0</v>
@@ -17612,12 +17612,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Edward - Assassin's Creed - Bust</t>
+          <t>Eva 01 - Neon Genesis Evangelion - Bust</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4724633</t>
+          <t>https://cults3d.com/:4724530</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -17626,39 +17626,39 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46234.02446759259</v>
+        <v>46234.11200231482</v>
       </c>
       <c r="E226" t="n">
         <v>13.49</v>
       </c>
       <c r="F226" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G226" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H226" t="n">
-        <v>984</v>
+        <v>1356</v>
       </c>
       <c r="I226" t="b">
         <v>0</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>assassin, assassinscreed, bust, collectible, edward, miniature, pirate, resin, stl, ubisoft</t>
+          <t>anime, bust, collectible, eva01, evangelion, mecha, miniature, neongenesisevangelion, resin, stl</t>
         </is>
       </c>
       <c r="K226" t="n">
         <v>85</v>
       </c>
       <c r="L226" t="n">
-        <v>4.752941176470588</v>
+        <v>4.729411764705882</v>
       </c>
       <c r="M226" t="n">
-        <v>5449.96</v>
+        <v>5422.98</v>
       </c>
       <c r="N226" t="n">
-        <v>0.4105691056910569</v>
+        <v>0.2964601769911505</v>
       </c>
       <c r="O226" t="b">
         <v>0</v>
@@ -18392,7 +18392,7 @@
         <v>60</v>
       </c>
       <c r="H239" t="n">
-        <v>7694</v>
+        <v>7696</v>
       </c>
       <c r="I239" t="b">
         <v>0</v>
@@ -18412,7 +18412,7 @@
         <v>1259.28</v>
       </c>
       <c r="N239" t="n">
-        <v>0.04133090720041591</v>
+        <v>0.04132016632016632</v>
       </c>
       <c r="O239" t="b">
         <v>0</v>
@@ -18450,7 +18450,7 @@
         <v>85</v>
       </c>
       <c r="H240" t="n">
-        <v>3652</v>
+        <v>3653</v>
       </c>
       <c r="I240" t="b">
         <v>0</v>
@@ -18470,7 +18470,7 @@
         <v>1679.92</v>
       </c>
       <c r="N240" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.04544210238160416</v>
       </c>
       <c r="O240" t="b">
         <v>0</v>
@@ -18798,7 +18798,7 @@
         <v>59</v>
       </c>
       <c r="H246" t="n">
-        <v>6098</v>
+        <v>6100</v>
       </c>
       <c r="I246" t="b">
         <v>0</v>
@@ -18818,7 +18818,7 @@
         <v>1306.62</v>
       </c>
       <c r="N246" t="n">
-        <v>0.02509019350606756</v>
+        <v>0.02508196721311476</v>
       </c>
       <c r="O246" t="b">
         <v>0</v>
@@ -18968,7 +18968,7 @@
         <v>27</v>
       </c>
       <c r="H249" t="n">
-        <v>1775</v>
+        <v>1778</v>
       </c>
       <c r="I249" t="b">
         <v>0</v>
@@ -18988,7 +18988,7 @@
         <v>8550</v>
       </c>
       <c r="N249" t="n">
-        <v>0.1605633802816901</v>
+        <v>0.1602924634420697</v>
       </c>
       <c r="O249" t="b">
         <v>1</v>
@@ -19316,7 +19316,7 @@
         <v>57</v>
       </c>
       <c r="H255" t="n">
-        <v>7151</v>
+        <v>7152</v>
       </c>
       <c r="I255" t="b">
         <v>0</v>
@@ -19336,7 +19336,7 @@
         <v>2214</v>
       </c>
       <c r="N255" t="n">
-        <v>0.03440078310725773</v>
+        <v>0.03439597315436242</v>
       </c>
       <c r="O255" t="b">
         <v>0</v>
@@ -19490,7 +19490,7 @@
         <v>38</v>
       </c>
       <c r="H258" t="n">
-        <v>8025</v>
+        <v>8027</v>
       </c>
       <c r="I258" t="b">
         <v>0</v>
@@ -19510,7 +19510,7 @@
         <v>310.98</v>
       </c>
       <c r="N258" t="n">
-        <v>0.02654205607476635</v>
+        <v>0.02653544288027906</v>
       </c>
       <c r="O258" t="b">
         <v>1</v>
@@ -19548,7 +19548,7 @@
         <v>30</v>
       </c>
       <c r="H259" t="n">
-        <v>5661</v>
+        <v>5662</v>
       </c>
       <c r="I259" t="b">
         <v>0</v>
@@ -19568,7 +19568,7 @@
         <v>1554.72</v>
       </c>
       <c r="N259" t="n">
-        <v>0.02791026320438085</v>
+        <v>0.02790533380430943</v>
       </c>
       <c r="O259" t="b">
         <v>0</v>
@@ -20128,7 +20128,7 @@
         <v>48</v>
       </c>
       <c r="H269" t="n">
-        <v>5235</v>
+        <v>5236</v>
       </c>
       <c r="I269" t="b">
         <v>0</v>
@@ -20148,7 +20148,7 @@
         <v>776.16</v>
       </c>
       <c r="N269" t="n">
-        <v>0.03744030563514805</v>
+        <v>0.0374331550802139</v>
       </c>
       <c r="O269" t="b">
         <v>1</v>
@@ -20418,7 +20418,7 @@
         <v>68</v>
       </c>
       <c r="H274" t="n">
-        <v>8699</v>
+        <v>8700</v>
       </c>
       <c r="I274" t="b">
         <v>0</v>
@@ -20438,7 +20438,7 @@
         <v>902.88</v>
       </c>
       <c r="N274" t="n">
-        <v>0.02620990918496379</v>
+        <v>0.02620689655172414</v>
       </c>
       <c r="O274" t="b">
         <v>1</v>
@@ -20650,7 +20650,7 @@
         <v>49</v>
       </c>
       <c r="H278" t="n">
-        <v>4954</v>
+        <v>4955</v>
       </c>
       <c r="I278" t="b">
         <v>0</v>
@@ -20670,7 +20670,7 @@
         <v>704.88</v>
       </c>
       <c r="N278" t="n">
-        <v>0.03593056116269681</v>
+        <v>0.03592330978809283</v>
       </c>
       <c r="O278" t="b">
         <v>1</v>
@@ -20824,7 +20824,7 @@
         <v>43</v>
       </c>
       <c r="H281" t="n">
-        <v>6018</v>
+        <v>6020</v>
       </c>
       <c r="I281" t="b">
         <v>0</v>
@@ -20844,7 +20844,7 @@
         <v>1137.5</v>
       </c>
       <c r="N281" t="n">
-        <v>0.03024260551678298</v>
+        <v>0.03023255813953488</v>
       </c>
       <c r="O281" t="b">
         <v>0</v>
@@ -20940,7 +20940,7 @@
         <v>48</v>
       </c>
       <c r="H283" t="n">
-        <v>5390</v>
+        <v>5391</v>
       </c>
       <c r="I283" t="b">
         <v>0</v>
@@ -20960,7 +20960,7 @@
         <v>712.8</v>
       </c>
       <c r="N283" t="n">
-        <v>0.03339517625231911</v>
+        <v>0.0333889816360601</v>
       </c>
       <c r="O283" t="b">
         <v>1</v>

--- a/reportes/cults3d_mercado.xlsx
+++ b/reportes/cults3d_mercado.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>126056</v>
+        <v>126079</v>
       </c>
     </row>
     <row r="5">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1862617.81</v>
+        <v>1863030.73</v>
       </c>
     </row>
     <row r="6">
@@ -791,7 +791,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>101282.96</v>
+        <v>101302.96</v>
       </c>
       <c r="H5" t="n">
         <v>0.3102012491325468</v>
@@ -883,7 +883,7 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>254385</v>
+        <v>254465</v>
       </c>
       <c r="H7" t="n">
         <v>0.2665121668597914</v>
@@ -929,7 +929,7 @@
         <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>224440</v>
+        <v>224520</v>
       </c>
       <c r="H8" t="n">
         <v>0.2655007949125596</v>
@@ -975,7 +975,7 @@
         <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>224440</v>
+        <v>224520</v>
       </c>
       <c r="H9" t="n">
         <v>0.2655007949125596</v>
@@ -1021,7 +1021,7 @@
         <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>224440</v>
+        <v>224520</v>
       </c>
       <c r="H10" t="n">
         <v>0.2655007949125596</v>
@@ -1067,7 +1067,7 @@
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>243845</v>
+        <v>243925</v>
       </c>
       <c r="H11" t="n">
         <v>0.2666614304458287</v>
@@ -1159,7 +1159,7 @@
         <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>319515.3</v>
+        <v>319615.3</v>
       </c>
       <c r="H13" t="n">
         <v>0.2660064808861755</v>
@@ -1199,13 +1199,13 @@
         <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>11.61075949367089</v>
+        <v>11.63159282700422</v>
       </c>
       <c r="F14" t="n">
         <v>17.5</v>
       </c>
       <c r="G14" t="n">
-        <v>179214.32</v>
+        <v>179270.29</v>
       </c>
       <c r="H14" t="n">
         <v>0.3517095395911514</v>
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>11.61076</v>
+        <v>11.63159</v>
       </c>
     </row>
     <row r="15">
@@ -1251,7 +1251,7 @@
         <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>254385</v>
+        <v>254465</v>
       </c>
       <c r="H15" t="n">
         <v>0.2665121668597914</v>
@@ -1291,16 +1291,16 @@
         <v>39</v>
       </c>
       <c r="E16" t="n">
-        <v>11.76923076923077</v>
+        <v>11.80769230769231</v>
       </c>
       <c r="F16" t="n">
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>299706.05</v>
+        <v>299978.97</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3692458374142997</v>
+        <v>0.3702252693437806</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -1318,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>11.34554</v>
+        <v>11.38262</v>
       </c>
     </row>
     <row r="17">
@@ -1337,13 +1337,13 @@
         <v>23</v>
       </c>
       <c r="E17" t="n">
-        <v>12.70833333333333</v>
+        <v>12.75</v>
       </c>
       <c r="F17" t="n">
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>237831.03</v>
+        <v>237887</v>
       </c>
       <c r="H17" t="n">
         <v>0.3412220309810671</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>11.285</v>
+        <v>11.322</v>
       </c>
     </row>
     <row r="18">
@@ -1389,7 +1389,7 @@
         <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>39640</v>
+        <v>39680</v>
       </c>
       <c r="H18" t="n">
         <v>0.1838750796685787</v>
@@ -1527,7 +1527,7 @@
         <v>20</v>
       </c>
       <c r="G21" t="n">
-        <v>413999.26</v>
+        <v>414099.26</v>
       </c>
       <c r="H21" t="n">
         <v>0.2617124394184168</v>
@@ -1613,13 +1613,13 @@
         <v>65</v>
       </c>
       <c r="E23" t="n">
-        <v>11.76923076923077</v>
+        <v>11.80769230769231</v>
       </c>
       <c r="F23" t="n">
         <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>528127.1800000001</v>
+        <v>528460.1</v>
       </c>
       <c r="H23" t="n">
         <v>0.3179524152847873</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>9.792</v>
+        <v>9.824</v>
       </c>
     </row>
     <row r="24">
@@ -1665,7 +1665,7 @@
         <v>20</v>
       </c>
       <c r="G24" t="n">
-        <v>255587.58</v>
+        <v>255667.58</v>
       </c>
       <c r="H24" t="n">
         <v>0.2636066171654882</v>
@@ -1803,10 +1803,10 @@
         <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>440915</v>
+        <v>440995</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3086522462562396</v>
+        <v>0.3092307692307693</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -1987,7 +1987,7 @@
         <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>240199.39</v>
+        <v>240279.39</v>
       </c>
       <c r="H31" t="n">
         <v>0.2559406323513077</v>
@@ -2447,10 +2447,10 @@
         <v>13.49</v>
       </c>
       <c r="G41" t="n">
-        <v>314454.21</v>
+        <v>314707.13</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3838180897333068</v>
+        <v>0.3843078056980472</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -2723,7 +2723,7 @@
         <v>13.49</v>
       </c>
       <c r="G47" t="n">
-        <v>153989.18</v>
+        <v>154070.12</v>
       </c>
       <c r="H47" t="n">
         <v>0.4327485380116959</v>
@@ -3091,10 +3091,10 @@
         <v>17.5</v>
       </c>
       <c r="G55" t="n">
-        <v>477079.58</v>
+        <v>477332.5</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3469777072440909</v>
+        <v>0.3474174609819977</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -3183,7 +3183,7 @@
         <v>13.49</v>
       </c>
       <c r="G57" t="n">
-        <v>45472.44</v>
+        <v>45485.93</v>
       </c>
       <c r="H57" t="n">
         <v>0.2685771409530157</v>
@@ -3413,7 +3413,7 @@
         <v>13.49</v>
       </c>
       <c r="G62" t="n">
-        <v>225117.29</v>
+        <v>225175.74</v>
       </c>
       <c r="H62" t="n">
         <v>0.3148967551622419</v>
@@ -3597,7 +3597,7 @@
         <v>20</v>
       </c>
       <c r="G66" t="n">
-        <v>281415</v>
+        <v>281495</v>
       </c>
       <c r="H66" t="n">
         <v>0.2665121668597914</v>
@@ -4432,7 +4432,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1713653.13</v>
+        <v>1714066.05</v>
       </c>
       <c r="G2" t="n">
         <v>0.2546607401742899</v>
@@ -6326,7 +6326,7 @@
         <v>20</v>
       </c>
       <c r="F31" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="G31" t="n">
         <v>54</v>
@@ -6346,13 +6346,13 @@
         <v>53</v>
       </c>
       <c r="L31" t="n">
-        <v>18.33962264150943</v>
+        <v>18.35849056603774</v>
       </c>
       <c r="M31" t="n">
-        <v>19440</v>
+        <v>19460</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2958904109589041</v>
+        <v>0.2961948249619483</v>
       </c>
       <c r="O31" t="b">
         <v>1</v>
@@ -6384,7 +6384,7 @@
         <v>20</v>
       </c>
       <c r="F32" t="n">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="G32" t="n">
         <v>25</v>
@@ -6404,13 +6404,13 @@
         <v>53</v>
       </c>
       <c r="L32" t="n">
-        <v>17.9811320754717</v>
+        <v>18</v>
       </c>
       <c r="M32" t="n">
-        <v>19060</v>
+        <v>19080</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2473397352712172</v>
+        <v>0.2475992732935375</v>
       </c>
       <c r="O32" t="b">
         <v>1</v>
@@ -6558,7 +6558,7 @@
         <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="G35" t="n">
         <v>41</v>
@@ -6578,13 +6578,13 @@
         <v>53</v>
       </c>
       <c r="L35" t="n">
-        <v>17.60377358490566</v>
+        <v>17.62264150943396</v>
       </c>
       <c r="M35" t="n">
-        <v>18660</v>
+        <v>18680</v>
       </c>
       <c r="N35" t="n">
-        <v>0.2715366705471479</v>
+        <v>0.2718277066356228</v>
       </c>
       <c r="O35" t="b">
         <v>0</v>
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L37" t="n">
-        <v>17.42307692307692</v>
+        <v>16.77777777777778</v>
       </c>
       <c r="M37" t="n">
         <v>9060</v>
@@ -6712,12 +6712,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Female V CyberPunk 250mm - Miniature Figure STL (ALT Version)</t>
+          <t>Maleficient Diorama with Dragon 300mm  (ALT Version)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4969277</t>
+          <t>https://cults3d.com/:5088769</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6726,39 +6726,39 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46292.11877314815</v>
+        <v>46315.2290162037</v>
       </c>
       <c r="E38" t="n">
         <v>20</v>
       </c>
       <c r="F38" t="n">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="G38" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H38" t="n">
-        <v>1201</v>
+        <v>863</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2077, cyberpunk, fan art, female, female v, figure, game art figurine, garage kit, miniature, miniatures, movie, sculpture, stylized, tabletop, tabletop game, video game</t>
+          <t>fan art, female, figure, game art figurine, garage kit, halloween, maleficient, miniature, miniatures, movie, sculpture, stylized, tabletop, tabletop game, video game</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="L38" t="n">
-        <v>16.53846153846154</v>
+        <v>16.42857142857143</v>
       </c>
       <c r="M38" t="n">
-        <v>8600</v>
+        <v>4600</v>
       </c>
       <c r="N38" t="n">
-        <v>0.3580349708576187</v>
+        <v>0.2665121668597914</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
@@ -6770,12 +6770,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Maleficient Diorama with Dragon 300mm  (ALT Version)</t>
+          <t>Mai Shiranui - The King of Fighters</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5088769</t>
+          <t>https://cults3d.com/:4971759</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6784,39 +6784,39 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46315.2290162037</v>
+        <v>46295.05967592593</v>
       </c>
       <c r="E39" t="n">
-        <v>20</v>
+        <v>22.48</v>
       </c>
       <c r="F39" t="n">
-        <v>230</v>
+        <v>394</v>
       </c>
       <c r="G39" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H39" t="n">
-        <v>863</v>
+        <v>1187</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>fan art, female, figure, game art figurine, garage kit, halloween, maleficient, miniature, miniatures, movie, sculpture, stylized, tabletop, tabletop game, video game</t>
+          <t>fanart, king of fighters, mai shiranui, miniature, resin, stl</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L39" t="n">
-        <v>16.42857142857143</v>
+        <v>16.41666666666667</v>
       </c>
       <c r="M39" t="n">
-        <v>4600</v>
+        <v>8857.120000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>0.2665121668597914</v>
+        <v>0.3319292333614153</v>
       </c>
       <c r="O39" t="b">
         <v>0</v>
@@ -6886,12 +6886,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mai Shiranui - The King of Fighters</t>
+          <t>Darth Vader Samurai 3D Print</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971759</t>
+          <t>https://cults3d.com/:4729172</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6900,39 +6900,39 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46295.05967592593</v>
+        <v>46234.4493287037</v>
       </c>
       <c r="E41" t="n">
-        <v>22.48</v>
+        <v>20</v>
       </c>
       <c r="F41" t="n">
-        <v>393</v>
+        <v>1343</v>
       </c>
       <c r="G41" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H41" t="n">
-        <v>1187</v>
+        <v>5446</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fanart, king of fighters, mai shiranui, miniature, resin, stl</t>
+          <t>anakin, chewbacca, darth, emperor, han, kenobi, leia, luke, obi, palpatine, princess, skywalker, solo, stormtrooper, vader, wan, yoda</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L41" t="n">
-        <v>16.375</v>
+        <v>15.98809523809524</v>
       </c>
       <c r="M41" t="n">
-        <v>8834.639999999999</v>
+        <v>26860</v>
       </c>
       <c r="N41" t="n">
-        <v>0.3310867733782645</v>
+        <v>0.2466030113845024</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
@@ -6944,12 +6944,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Darth Vader Samurai 3D Print</t>
+          <t>Female V CyberPunk 250mm - Miniature Figure STL (ALT Version)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4729172</t>
+          <t>https://cults3d.com/:4969277</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6958,39 +6958,39 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46234.4493287037</v>
+        <v>46292.11877314815</v>
       </c>
       <c r="E42" t="n">
         <v>20</v>
       </c>
       <c r="F42" t="n">
-        <v>1343</v>
+        <v>430</v>
       </c>
       <c r="G42" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="H42" t="n">
-        <v>5446</v>
+        <v>1201</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>anakin, chewbacca, darth, emperor, han, kenobi, leia, luke, obi, palpatine, princess, skywalker, solo, stormtrooper, vader, wan, yoda</t>
+          <t>2077, cyberpunk, fan art, female, female v, figure, game art figurine, garage kit, miniature, miniatures, movie, sculpture, stylized, tabletop, tabletop game, video game</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="L42" t="n">
-        <v>15.98809523809524</v>
+        <v>15.92592592592593</v>
       </c>
       <c r="M42" t="n">
-        <v>26860</v>
+        <v>8600</v>
       </c>
       <c r="N42" t="n">
-        <v>0.2466030113845024</v>
+        <v>0.3580349708576187</v>
       </c>
       <c r="O42" t="b">
         <v>0</v>
@@ -7080,7 +7080,7 @@
         <v>22.48</v>
       </c>
       <c r="F44" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G44" t="n">
         <v>25</v>
@@ -7100,13 +7100,13 @@
         <v>24</v>
       </c>
       <c r="L44" t="n">
-        <v>15.70833333333333</v>
+        <v>15.75</v>
       </c>
       <c r="M44" t="n">
-        <v>8474.960000000001</v>
+        <v>8497.440000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>0.3692458374142997</v>
+        <v>0.3702252693437806</v>
       </c>
       <c r="O44" t="b">
         <v>0</v>
@@ -7118,117 +7118,117 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GHOST WITH BIG MELONS The Curvy Ghost</t>
+          <t>Solid Snake 3D Print</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4955179</t>
+          <t>https://cults3d.com/:4851359</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Art</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46288.59271990741</v>
+        <v>46265.55130787037</v>
       </c>
       <c r="E45" t="n">
-        <v>4.45</v>
+        <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>468</v>
+        <v>827</v>
       </c>
       <c r="G45" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="H45" t="n">
-        <v>9725</v>
+        <v>3677</v>
       </c>
       <c r="I45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>candle, death, decor, fun, ghost, halloween, holder, home, spooky, tealight</t>
+          <t>famas, gear, metal, mgs, snake, soldier, solid</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="L45" t="n">
-        <v>15.6</v>
+        <v>15.60377358490566</v>
       </c>
       <c r="M45" t="n">
-        <v>2082.6</v>
+        <v>16540</v>
       </c>
       <c r="N45" t="n">
-        <v>0.04812339331619538</v>
+        <v>0.2249116127277672</v>
       </c>
       <c r="O45" t="b">
         <v>0</v>
       </c>
       <c r="P45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solid Snake 3D Print</t>
+          <t>GHOST WITH BIG MELONS The Curvy Ghost</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4851359</t>
+          <t>https://cults3d.com/:4955179</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Art</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46265.55130787037</v>
+        <v>46288.59271990741</v>
       </c>
       <c r="E46" t="n">
-        <v>20</v>
+        <v>4.45</v>
       </c>
       <c r="F46" t="n">
-        <v>826</v>
+        <v>468</v>
       </c>
       <c r="G46" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="H46" t="n">
-        <v>3677</v>
+        <v>9725</v>
       </c>
       <c r="I46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>famas, gear, metal, mgs, snake, soldier, solid</t>
+          <t>candle, death, decor, fun, ghost, halloween, holder, home, spooky, tealight</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="L46" t="n">
-        <v>15.58490566037736</v>
+        <v>15.6</v>
       </c>
       <c r="M46" t="n">
-        <v>16520</v>
+        <v>2082.6</v>
       </c>
       <c r="N46" t="n">
-        <v>0.2246396518901278</v>
+        <v>0.04812339331619538</v>
       </c>
       <c r="O46" t="b">
         <v>0</v>
       </c>
       <c r="P46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -7312,7 +7312,7 @@
         <v>22.48</v>
       </c>
       <c r="F48" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G48" t="n">
         <v>13</v>
@@ -7332,13 +7332,13 @@
         <v>26</v>
       </c>
       <c r="L48" t="n">
-        <v>15.30769230769231</v>
+        <v>15.34615384615385</v>
       </c>
       <c r="M48" t="n">
-        <v>8947.040000000001</v>
+        <v>8969.52</v>
       </c>
       <c r="N48" t="n">
-        <v>0.3500439753737907</v>
+        <v>0.3509234828496042</v>
       </c>
       <c r="O48" t="b">
         <v>0</v>
@@ -7370,7 +7370,7 @@
         <v>20</v>
       </c>
       <c r="F49" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G49" t="n">
         <v>45</v>
@@ -7390,13 +7390,13 @@
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>15.21428571428571</v>
+        <v>15.28571428571429</v>
       </c>
       <c r="M49" t="n">
-        <v>4260</v>
+        <v>4280</v>
       </c>
       <c r="N49" t="n">
-        <v>0.08117378048780488</v>
+        <v>0.08155487804878049</v>
       </c>
       <c r="O49" t="b">
         <v>1</v>
@@ -7582,12 +7582,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nina Williams</t>
+          <t>Evie Stellar Blade 250mm - Miniature Figure STL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4888768</t>
+          <t>https://cults3d.com/:5094595</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7596,42 +7596,42 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46280.54935185185</v>
+        <v>46316.4987962963</v>
       </c>
       <c r="E53" t="n">
-        <v>10.34</v>
+        <v>20</v>
       </c>
       <c r="F53" t="n">
-        <v>572</v>
+        <v>211</v>
       </c>
       <c r="G53" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H53" t="n">
-        <v>1968</v>
+        <v>3444</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>nina williams, tekken</t>
+          <t>evie, fan art, female, figure, game art figurine, garage kit, miniature, miniatures, movie, sculpture, stellar blade, stylized, tabletop, tabletop game, video game</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
-        <v>15.05263157894737</v>
+        <v>15.07142857142857</v>
       </c>
       <c r="M53" t="n">
-        <v>5914.48</v>
+        <v>4220</v>
       </c>
       <c r="N53" t="n">
-        <v>0.290650406504065</v>
+        <v>0.06126596980255517</v>
       </c>
       <c r="O53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53" t="b">
         <v>0</v>
@@ -7640,12 +7640,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Evie Stellar Blade 250mm - Miniature Figure STL</t>
+          <t>Nina Williams</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5094595</t>
+          <t>https://cults3d.com/:4888768</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7654,42 +7654,42 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46316.4987962963</v>
+        <v>46280.54935185185</v>
       </c>
       <c r="E54" t="n">
-        <v>20</v>
+        <v>10.34</v>
       </c>
       <c r="F54" t="n">
-        <v>210</v>
+        <v>572</v>
       </c>
       <c r="G54" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H54" t="n">
-        <v>3444</v>
+        <v>1968</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>evie, fan art, female, figure, game art figurine, garage kit, miniature, miniatures, movie, sculpture, stellar blade, stylized, tabletop, tabletop game, video game</t>
+          <t>nina williams, tekken</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="L54" t="n">
-        <v>15</v>
+        <v>15.05263157894737</v>
       </c>
       <c r="M54" t="n">
-        <v>4200</v>
+        <v>5914.48</v>
       </c>
       <c r="N54" t="n">
-        <v>0.06097560975609756</v>
+        <v>0.290650406504065</v>
       </c>
       <c r="O54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P54" t="b">
         <v>0</v>
@@ -7718,13 +7718,13 @@
         <v>10.12</v>
       </c>
       <c r="F55" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G55" t="n">
         <v>7</v>
       </c>
       <c r="H55" t="n">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="I55" t="b">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>24</v>
       </c>
       <c r="L55" t="n">
-        <v>14.75</v>
+        <v>14.79166666666667</v>
       </c>
       <c r="M55" t="n">
-        <v>3582.48</v>
+        <v>3592.6</v>
       </c>
       <c r="N55" t="n">
-        <v>0.4370370370370371</v>
+        <v>0.437192118226601</v>
       </c>
       <c r="O55" t="b">
         <v>0</v>
@@ -7814,12 +7814,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Norse Witch Bust 3D Print</t>
+          <t>Tanya Degurechaff - Saga of Tanya the Evil - Chibi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4878911</t>
+          <t>https://cults3d.com/:4971662</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7828,39 +7828,39 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46271.73016203703</v>
+        <v>46295.02363425926</v>
       </c>
       <c r="E57" t="n">
-        <v>15</v>
+        <v>13.49</v>
       </c>
       <c r="F57" t="n">
-        <v>686</v>
+        <v>351</v>
       </c>
       <c r="G57" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H57" t="n">
-        <v>2234</v>
+        <v>786</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>abominatuion, corrupted, dnd, evil, foul, games, ice, norse, north, parasite, pathfinder, rpg, snow, tabletop, twisted, undead, viking, villagers, zombie</t>
+          <t>chibi, fanart, miniature, resin, saga of tanya the evil, stl, tanya, tanya degurechaff</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="L57" t="n">
-        <v>14.59574468085106</v>
+        <v>14.625</v>
       </c>
       <c r="M57" t="n">
-        <v>10290</v>
+        <v>4734.99</v>
       </c>
       <c r="N57" t="n">
-        <v>0.3070725156669651</v>
+        <v>0.4465648854961832</v>
       </c>
       <c r="O57" t="b">
         <v>0</v>
@@ -7872,12 +7872,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tanya Degurechaff - Saga of Tanya the Evil - Chibi</t>
+          <t>Silver Surfer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971662</t>
+          <t>https://cults3d.com/:4971755</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7886,42 +7886,42 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46295.02363425926</v>
+        <v>46292.21614583334</v>
       </c>
       <c r="E58" t="n">
-        <v>13.49</v>
+        <v>22.48</v>
       </c>
       <c r="F58" t="n">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="G58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H58" t="n">
-        <v>784</v>
+        <v>750</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>chibi, fanart, miniature, resin, saga of tanya the evil, stl, tanya, tanya degurechaff</t>
+          <t>collectible, fanart, herald, marvel, miniature, resin, silver surfer, stl</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L58" t="n">
-        <v>14.58333333333333</v>
+        <v>14.61538461538461</v>
       </c>
       <c r="M58" t="n">
-        <v>4721.5</v>
+        <v>8542.4</v>
       </c>
       <c r="N58" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.5066666666666667</v>
       </c>
       <c r="O58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" t="b">
         <v>0</v>
@@ -7930,12 +7930,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Silver Surfer</t>
+          <t>Norse Witch Bust 3D Print</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971755</t>
+          <t>https://cults3d.com/:4878911</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -7944,42 +7944,42 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46292.21614583334</v>
+        <v>46271.73016203703</v>
       </c>
       <c r="E59" t="n">
-        <v>22.48</v>
+        <v>15</v>
       </c>
       <c r="F59" t="n">
-        <v>379</v>
+        <v>686</v>
       </c>
       <c r="G59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H59" t="n">
-        <v>748</v>
+        <v>2234</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>collectible, fanart, herald, marvel, miniature, resin, silver surfer, stl</t>
+          <t>abominatuion, corrupted, dnd, evil, foul, games, ice, norse, north, parasite, pathfinder, rpg, snow, tabletop, twisted, undead, viking, villagers, zombie</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="L59" t="n">
-        <v>14.57692307692308</v>
+        <v>14.59574468085106</v>
       </c>
       <c r="M59" t="n">
-        <v>8519.92</v>
+        <v>10290</v>
       </c>
       <c r="N59" t="n">
-        <v>0.5066844919786097</v>
+        <v>0.3070725156669651</v>
       </c>
       <c r="O59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59" t="b">
         <v>0</v>
@@ -8104,12 +8104,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Savage Land Psylocke Bust 3D Print</t>
+          <t>Miguel - The Road to El Dorado - Toon</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4878923</t>
+          <t>https://cults3d.com/:4971529</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8118,39 +8118,39 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46271.73194444444</v>
+        <v>46295.00292824074</v>
       </c>
       <c r="E62" t="n">
-        <v>15</v>
+        <v>13.49</v>
       </c>
       <c r="F62" t="n">
-        <v>679</v>
+        <v>347</v>
       </c>
       <c r="G62" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H62" t="n">
-        <v>1833</v>
+        <v>526</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>art, comics, fan, female, figure, figurine, game, garage, kit, miniature, miniatures, movie, psylocke, savage, sculpture, stylized, tabletop, video, xmen</t>
+          <t>collectible, disney, fanart, miguel, miniature, resin, stl, the road to el dorado, toon</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="L62" t="n">
-        <v>14.4468085106383</v>
+        <v>14.45833333333333</v>
       </c>
       <c r="M62" t="n">
-        <v>10185</v>
+        <v>4681.03</v>
       </c>
       <c r="N62" t="n">
-        <v>0.370430987452264</v>
+        <v>0.6596958174904943</v>
       </c>
       <c r="O62" t="b">
         <v>1</v>
@@ -8220,12 +8220,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Miguel - The Road to El Dorado - Toon</t>
+          <t>Savage Land Psylocke Bust 3D Print</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971529</t>
+          <t>https://cults3d.com/:4878923</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8234,39 +8234,39 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46295.00292824074</v>
+        <v>46271.73194444444</v>
       </c>
       <c r="E64" t="n">
-        <v>13.49</v>
+        <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>346</v>
+        <v>679</v>
       </c>
       <c r="G64" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H64" t="n">
-        <v>524</v>
+        <v>1833</v>
       </c>
       <c r="I64" t="b">
         <v>0</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>collectible, disney, fanart, miguel, miniature, resin, stl, the road to el dorado, toon</t>
+          <t>art, comics, fan, female, figure, figurine, game, garage, kit, miniature, miniatures, movie, psylocke, savage, sculpture, stylized, tabletop, video, xmen</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L64" t="n">
-        <v>14.41666666666667</v>
+        <v>14.4468085106383</v>
       </c>
       <c r="M64" t="n">
-        <v>4667.54</v>
+        <v>10185</v>
       </c>
       <c r="N64" t="n">
-        <v>0.6603053435114504</v>
+        <v>0.370430987452264</v>
       </c>
       <c r="O64" t="b">
         <v>1</v>
@@ -8278,12 +8278,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Hellboy Bust 3D Print</t>
+          <t>Evie Stellar Blade 250mm - Miniature Figure STL (ALT Version)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4878878</t>
+          <t>https://cults3d.com/:5095795</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -8292,39 +8292,39 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46271.72582175926</v>
+        <v>46316.49896990741</v>
       </c>
       <c r="E65" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F65" t="n">
-        <v>677</v>
+        <v>202</v>
       </c>
       <c r="G65" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H65" t="n">
-        <v>1545</v>
+        <v>643</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>comics, dc, fanart, hell, hellboy, marvel, sculpture</t>
+          <t>evie, fan art, female, figure, game art figurine, garage kit, miniature, miniatures, movie, sculpture, stellar blade, stylized, tabletop, tabletop game, video game</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="L65" t="n">
-        <v>14.40425531914894</v>
+        <v>14.42857142857143</v>
       </c>
       <c r="M65" t="n">
-        <v>10155</v>
+        <v>4040</v>
       </c>
       <c r="N65" t="n">
-        <v>0.4381877022653722</v>
+        <v>0.3141524105754277</v>
       </c>
       <c r="O65" t="b">
         <v>1</v>
@@ -8336,12 +8336,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Evie Stellar Blade 250mm - Miniature Figure STL (ALT Version)</t>
+          <t>Hellboy Bust 3D Print</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5095795</t>
+          <t>https://cults3d.com/:4878878</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -8350,39 +8350,39 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46316.49896990741</v>
+        <v>46271.72582175926</v>
       </c>
       <c r="E66" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F66" t="n">
-        <v>201</v>
+        <v>677</v>
       </c>
       <c r="G66" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H66" t="n">
-        <v>642</v>
+        <v>1545</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>evie, fan art, female, figure, game art figurine, garage kit, miniature, miniatures, movie, sculpture, stellar blade, stylized, tabletop, tabletop game, video game</t>
+          <t>comics, dc, fanart, hell, hellboy, marvel, sculpture</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="L66" t="n">
-        <v>14.35714285714286</v>
+        <v>14.40425531914894</v>
       </c>
       <c r="M66" t="n">
-        <v>4020</v>
+        <v>10155</v>
       </c>
       <c r="N66" t="n">
-        <v>0.3130841121495327</v>
+        <v>0.4381877022653722</v>
       </c>
       <c r="O66" t="b">
         <v>1</v>
@@ -8394,117 +8394,117 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>rifled AND SMOOTHBORE barrels for toilet plungers</t>
+          <t>Cammy Street Fighter 250mm - Miniature Figure STL (ALT Version)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4880393</t>
+          <t>https://cults3d.com/:5099748</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Various</t>
+          <t>Art</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46272.04734953704</v>
+        <v>46317.35827546296</v>
       </c>
       <c r="E67" t="n">
+        <v>20</v>
+      </c>
+      <c r="F67" t="n">
+        <v>201</v>
+      </c>
+      <c r="G67" t="n">
         <v>22</v>
       </c>
-      <c r="F67" t="n">
-        <v>673</v>
-      </c>
-      <c r="G67" t="n">
-        <v>136</v>
-      </c>
       <c r="H67" t="n">
-        <v>33728</v>
+        <v>650</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>airgun, apfsds, artillery, ballistic, bomb, cannon, hand cannon, missle, mortar, pellet, pistol, pneumatic, pnuematic, potato cannon, spinning, spudgun, tank ammo, tank round, toilet plunger, toy</t>
+          <t>cammy, fan art, female, figure, game art figurine, garage kit, miniature, miniatures, movie, sculpture, street fighter, stylized, tabletop, tabletop game, video game</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>14.31914893617021</v>
+        <v>14.35714285714286</v>
       </c>
       <c r="M67" t="n">
-        <v>14806</v>
+        <v>4020</v>
       </c>
       <c r="N67" t="n">
-        <v>0.01995374762808349</v>
+        <v>0.3092307692307693</v>
       </c>
       <c r="O67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cammy Street Fighter 250mm - Miniature Figure STL (ALT Version)</t>
+          <t>rifled AND SMOOTHBORE barrels for toilet plungers</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5099748</t>
+          <t>https://cults3d.com/:4880393</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Art</t>
+          <t>Various</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46317.35827546296</v>
+        <v>46272.04734953704</v>
       </c>
       <c r="E68" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F68" t="n">
-        <v>200</v>
+        <v>673</v>
       </c>
       <c r="G68" t="n">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="H68" t="n">
-        <v>649</v>
+        <v>33728</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>cammy, fan art, female, figure, game art figurine, garage kit, miniature, miniatures, movie, sculpture, street fighter, stylized, tabletop, tabletop game, video game</t>
+          <t>airgun, apfsds, artillery, ballistic, bomb, cannon, hand cannon, missle, mortar, pellet, pistol, pneumatic, pnuematic, potato cannon, spinning, spudgun, tank ammo, tank round, toilet plunger, toy</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="L68" t="n">
-        <v>14.28571428571429</v>
+        <v>14.31914893617021</v>
       </c>
       <c r="M68" t="n">
-        <v>4000</v>
+        <v>14806</v>
       </c>
       <c r="N68" t="n">
-        <v>0.3081664098613251</v>
+        <v>0.01995374762808349</v>
       </c>
       <c r="O68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -8878,7 +8878,7 @@
         <v>22.48</v>
       </c>
       <c r="F75" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G75" t="n">
         <v>17</v>
@@ -8898,13 +8898,13 @@
         <v>26</v>
       </c>
       <c r="L75" t="n">
-        <v>13.92307692307692</v>
+        <v>13.96153846153846</v>
       </c>
       <c r="M75" t="n">
-        <v>8137.76</v>
+        <v>8160.24</v>
       </c>
       <c r="N75" t="n">
-        <v>0.3330266789328427</v>
+        <v>0.3339466421343146</v>
       </c>
       <c r="O75" t="b">
         <v>0</v>
@@ -8936,13 +8936,13 @@
         <v>22.48</v>
       </c>
       <c r="F76" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G76" t="n">
         <v>10</v>
       </c>
       <c r="H76" t="n">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="I76" t="b">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>26</v>
       </c>
       <c r="L76" t="n">
-        <v>13.92307692307692</v>
+        <v>13.96153846153846</v>
       </c>
       <c r="M76" t="n">
-        <v>8137.76</v>
+        <v>8160.24</v>
       </c>
       <c r="N76" t="n">
-        <v>0.4184971098265896</v>
+        <v>0.4186851211072664</v>
       </c>
       <c r="O76" t="b">
         <v>0</v>
@@ -9400,13 +9400,13 @@
         <v>13.49</v>
       </c>
       <c r="F84" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G84" t="n">
         <v>5</v>
       </c>
       <c r="H84" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="I84" t="b">
         <v>0</v>
@@ -9420,13 +9420,13 @@
         <v>24</v>
       </c>
       <c r="L84" t="n">
-        <v>12.875</v>
+        <v>12.91666666666667</v>
       </c>
       <c r="M84" t="n">
-        <v>4168.41</v>
+        <v>4181.9</v>
       </c>
       <c r="N84" t="n">
-        <v>0.64375</v>
+        <v>0.6431535269709544</v>
       </c>
       <c r="O84" t="b">
         <v>0</v>
@@ -9458,13 +9458,13 @@
         <v>13.49</v>
       </c>
       <c r="F85" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G85" t="n">
         <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="I85" t="b">
         <v>0</v>
@@ -9478,13 +9478,13 @@
         <v>24</v>
       </c>
       <c r="L85" t="n">
-        <v>12.75</v>
+        <v>12.79166666666667</v>
       </c>
       <c r="M85" t="n">
-        <v>4127.940000000001</v>
+        <v>4141.43</v>
       </c>
       <c r="N85" t="n">
-        <v>0.5368421052631579</v>
+        <v>0.5348432055749129</v>
       </c>
       <c r="O85" t="b">
         <v>0</v>
@@ -9496,12 +9496,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Invisible Woman 3D Print</t>
+          <t>Spike Spiegel - Cowboy Bebop - Bust</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4730273</t>
+          <t>https://cults3d.com/:4971677</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9510,42 +9510,42 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46234.68424768518</v>
+        <v>46295.025625</v>
       </c>
       <c r="E86" t="n">
-        <v>20</v>
+        <v>13.49</v>
       </c>
       <c r="F86" t="n">
-        <v>1070</v>
+        <v>306</v>
       </c>
       <c r="G86" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="H86" t="n">
-        <v>4518</v>
+        <v>485</v>
       </c>
       <c r="I86" t="b">
         <v>0</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>fantastic, fields, force, four, human, invisible, marvel, mr, rivals, storm, susan, torch, woman</t>
+          <t>anime, bust, cowboy bebop, fanart, miniature, resin, spike spiegel, stl</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="L86" t="n">
-        <v>12.73809523809524</v>
+        <v>12.75</v>
       </c>
       <c r="M86" t="n">
-        <v>21400</v>
+        <v>4127.940000000001</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2368304559539619</v>
+        <v>0.6309278350515464</v>
       </c>
       <c r="O86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P86" t="b">
         <v>0</v>
@@ -9554,12 +9554,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Spike Spiegel - Cowboy Bebop - Bust</t>
+          <t>Invisible Woman 3D Print</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971677</t>
+          <t>https://cults3d.com/:4730273</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9568,42 +9568,42 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46295.025625</v>
+        <v>46234.68424768518</v>
       </c>
       <c r="E87" t="n">
-        <v>13.49</v>
+        <v>20</v>
       </c>
       <c r="F87" t="n">
-        <v>305</v>
+        <v>1070</v>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="H87" t="n">
-        <v>483</v>
+        <v>4518</v>
       </c>
       <c r="I87" t="b">
         <v>0</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>anime, bust, cowboy bebop, fanart, miniature, resin, spike spiegel, stl</t>
+          <t>fantastic, fields, force, four, human, invisible, marvel, mr, rivals, storm, susan, torch, woman</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L87" t="n">
-        <v>12.70833333333333</v>
+        <v>12.73809523809524</v>
       </c>
       <c r="M87" t="n">
-        <v>4114.45</v>
+        <v>21400</v>
       </c>
       <c r="N87" t="n">
-        <v>0.6314699792960663</v>
+        <v>0.2368304559539619</v>
       </c>
       <c r="O87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" t="b">
         <v>0</v>
@@ -9690,13 +9690,13 @@
         <v>13.49</v>
       </c>
       <c r="F89" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G89" t="n">
         <v>5</v>
       </c>
       <c r="H89" t="n">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="I89" t="b">
         <v>0</v>
@@ -9710,13 +9710,13 @@
         <v>24</v>
       </c>
       <c r="L89" t="n">
-        <v>12.5</v>
+        <v>12.54166666666667</v>
       </c>
       <c r="M89" t="n">
-        <v>4047</v>
+        <v>4060.49</v>
       </c>
       <c r="N89" t="n">
-        <v>0.6302521008403361</v>
+        <v>0.6297071129707112</v>
       </c>
       <c r="O89" t="b">
         <v>1</v>
@@ -9864,13 +9864,13 @@
         <v>13.49</v>
       </c>
       <c r="F92" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G92" t="n">
         <v>2</v>
       </c>
       <c r="H92" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I92" t="b">
         <v>0</v>
@@ -9884,13 +9884,13 @@
         <v>26</v>
       </c>
       <c r="L92" t="n">
-        <v>11.76923076923077</v>
+        <v>11.80769230769231</v>
       </c>
       <c r="M92" t="n">
-        <v>4127.940000000001</v>
+        <v>4141.43</v>
       </c>
       <c r="N92" t="n">
-        <v>0.6035502958579881</v>
+        <v>0.6031434184675835</v>
       </c>
       <c r="O92" t="b">
         <v>0</v>
@@ -9922,13 +9922,13 @@
         <v>13.49</v>
       </c>
       <c r="F93" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G93" t="n">
         <v>4</v>
       </c>
       <c r="H93" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="I93" t="b">
         <v>0</v>
@@ -9942,13 +9942,13 @@
         <v>26</v>
       </c>
       <c r="L93" t="n">
-        <v>11.76923076923077</v>
+        <v>11.80769230769231</v>
       </c>
       <c r="M93" t="n">
-        <v>4127.940000000001</v>
+        <v>4141.43</v>
       </c>
       <c r="N93" t="n">
-        <v>0.6144578313253012</v>
+        <v>0.614</v>
       </c>
       <c r="O93" t="b">
         <v>0</v>
@@ -10482,12 +10482,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Darth Vader Samurai Bust 3D Print</t>
+          <t>Minthara Bust 3D Print</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4747005</t>
+          <t>https://cults3d.com/:4749441</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -10496,39 +10496,39 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46239.11605324074</v>
+        <v>46239.73216435185</v>
       </c>
       <c r="E103" t="n">
         <v>15</v>
       </c>
       <c r="F103" t="n">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G103" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H103" t="n">
-        <v>2293</v>
+        <v>2217</v>
       </c>
       <c r="I103" t="b">
         <v>0</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>anakin, chewbacca, darth, emperor, han, kenobi, leia, luke, obi, palpatine, princess, skywalker, solo, stormtrooper, vader, wan, yoda</t>
+          <t>armor, baldur's, baldurs, bg3, bust, dark, dnd, elf, female, figure, gate, larian, mace, minthara, paladin</t>
         </is>
       </c>
       <c r="K103" t="n">
         <v>79</v>
       </c>
       <c r="L103" t="n">
-        <v>10.54430379746835</v>
+        <v>10.53164556962025</v>
       </c>
       <c r="M103" t="n">
-        <v>12495</v>
+        <v>12480</v>
       </c>
       <c r="N103" t="n">
-        <v>0.3632795464457043</v>
+        <v>0.3752819124943618</v>
       </c>
       <c r="O103" t="b">
         <v>0</v>
@@ -10540,12 +10540,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Minthara Bust 3D Print</t>
+          <t>Yuria of Londor Bust 3D Print</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4749441</t>
+          <t>https://cults3d.com/:4749861</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46239.73216435185</v>
+        <v>46239.81805555556</v>
       </c>
       <c r="E104" t="n">
         <v>15</v>
@@ -10563,17 +10563,17 @@
         <v>832</v>
       </c>
       <c r="G104" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H104" t="n">
-        <v>2217</v>
+        <v>3234</v>
       </c>
       <c r="I104" t="b">
         <v>0</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>armor, baldur's, baldurs, bg3, bust, dark, dnd, elf, female, figure, gate, larian, mace, minthara, paladin</t>
+          <t>dark, fromsoftware, game, londor, religion, role-playing, rpg, souls, video, yuria</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -10586,7 +10586,7 @@
         <v>12480</v>
       </c>
       <c r="N104" t="n">
-        <v>0.3752819124943618</v>
+        <v>0.2572665429808287</v>
       </c>
       <c r="O104" t="b">
         <v>0</v>
@@ -10598,12 +10598,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Yuria of Londor Bust 3D Print</t>
+          <t>Symbiote Spiderman Bust 3D Print</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4749861</t>
+          <t>https://cults3d.com/:4749510</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -10612,42 +10612,42 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46239.81805555556</v>
+        <v>46239.74586805556</v>
       </c>
       <c r="E105" t="n">
         <v>15</v>
       </c>
       <c r="F105" t="n">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="G105" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H105" t="n">
-        <v>3234</v>
+        <v>2384</v>
       </c>
       <c r="I105" t="b">
         <v>0</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>dark, fromsoftware, game, londor, religion, role-playing, rpg, souls, video, yuria</t>
+          <t>black, evil, man, miles-morales, parker, peter, spider, spider-man, spiderman, suit, venom</t>
         </is>
       </c>
       <c r="K105" t="n">
         <v>79</v>
       </c>
       <c r="L105" t="n">
-        <v>10.53164556962025</v>
+        <v>10.46835443037975</v>
       </c>
       <c r="M105" t="n">
-        <v>12480</v>
+        <v>12405</v>
       </c>
       <c r="N105" t="n">
-        <v>0.2572665429808287</v>
+        <v>0.3468959731543624</v>
       </c>
       <c r="O105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P105" t="b">
         <v>0</v>
@@ -10656,12 +10656,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Symbiote Spiderman Bust 3D Print</t>
+          <t>Warrior of the North 3D Print</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4749510</t>
+          <t>https://cults3d.com/:4729315</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -10670,39 +10670,39 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46239.74586805556</v>
+        <v>46234.48478009259</v>
       </c>
       <c r="E106" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F106" t="n">
-        <v>827</v>
+        <v>878</v>
       </c>
       <c r="G106" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H106" t="n">
-        <v>2384</v>
+        <v>3905</v>
       </c>
       <c r="I106" t="b">
         <v>0</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>black, evil, man, miles-morales, parker, peter, spider, spider-man, spiderman, suit, venom</t>
+          <t>advertising, armour, art, axe, barbarian, batman, battle, conan, crusader, god, knight, marvel, odin, sculptures, shield, superhero, superman, thor, warrior</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L106" t="n">
-        <v>10.46835443037975</v>
+        <v>10.45238095238095</v>
       </c>
       <c r="M106" t="n">
-        <v>12405</v>
+        <v>17560</v>
       </c>
       <c r="N106" t="n">
-        <v>0.3468959731543624</v>
+        <v>0.2248399487836107</v>
       </c>
       <c r="O106" t="b">
         <v>1</v>
@@ -10714,12 +10714,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Warrior of the North 3D Print</t>
+          <t>Darth Vader Samurai Bust 3D Print</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4729315</t>
+          <t>https://cults3d.com/:4747005</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -10728,42 +10728,42 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46234.48478009259</v>
+        <v>46239.11605324074</v>
       </c>
       <c r="E107" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F107" t="n">
-        <v>878</v>
+        <v>833</v>
       </c>
       <c r="G107" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H107" t="n">
-        <v>3905</v>
+        <v>2293</v>
       </c>
       <c r="I107" t="b">
         <v>0</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>advertising, armour, art, axe, barbarian, batman, battle, conan, crusader, god, knight, marvel, odin, sculptures, shield, superhero, superman, thor, warrior</t>
+          <t>anakin, chewbacca, darth, emperor, han, kenobi, leia, luke, obi, palpatine, princess, skywalker, solo, stormtrooper, vader, wan, yoda</t>
         </is>
       </c>
       <c r="K107" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L107" t="n">
-        <v>10.45238095238095</v>
+        <v>10.4125</v>
       </c>
       <c r="M107" t="n">
-        <v>17560</v>
+        <v>12495</v>
       </c>
       <c r="N107" t="n">
-        <v>0.2248399487836107</v>
+        <v>0.3632795464457043</v>
       </c>
       <c r="O107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P107" t="b">
         <v>0</v>
@@ -11120,53 +11120,53 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EDWARD ELRIC Bust 3D Print</t>
+          <t>Cute Flexi Bear 🐻 + Cute Flexi Maker Access</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4747013</t>
+          <t>https://cults3d.com/:4996776</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Art</t>
+          <t>Game</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46239.11833333333</v>
+        <v>46297.30413194445</v>
       </c>
       <c r="E114" t="n">
-        <v>15</v>
+        <v>4.35</v>
       </c>
       <c r="F114" t="n">
-        <v>802</v>
+        <v>212</v>
       </c>
       <c r="G114" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H114" t="n">
-        <v>2150</v>
+        <v>1296</v>
       </c>
       <c r="I114" t="b">
         <v>0</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>3d, action, alchimist, alphonse, anime, animes, brotherhood, diorama, edward, figures, full, fullmetal, metal, obj, printer, stl, toy</t>
+          <t>articulated, articulating, bear, cute, flexi, flexy, halloween, polar, santa</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="L114" t="n">
-        <v>10.15189873417722</v>
+        <v>10.09523809523809</v>
       </c>
       <c r="M114" t="n">
-        <v>12030</v>
+        <v>922.1999999999999</v>
       </c>
       <c r="N114" t="n">
-        <v>0.3730232558139535</v>
+        <v>0.1635802469135803</v>
       </c>
       <c r="O114" t="b">
         <v>0</v>
@@ -11178,53 +11178,53 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Cute Flexi Bear 🐻 + Cute Flexi Maker Access</t>
+          <t>EDWARD ELRIC Bust 3D Print</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4996776</t>
+          <t>https://cults3d.com/:4747013</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Game</t>
+          <t>Art</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46297.30413194445</v>
+        <v>46239.11833333333</v>
       </c>
       <c r="E115" t="n">
-        <v>4.35</v>
+        <v>15</v>
       </c>
       <c r="F115" t="n">
-        <v>212</v>
+        <v>802</v>
       </c>
       <c r="G115" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H115" t="n">
-        <v>1296</v>
+        <v>2150</v>
       </c>
       <c r="I115" t="b">
         <v>0</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>articulated, articulating, bear, cute, flexi, flexy, halloween, polar, santa</t>
+          <t>3d, action, alchimist, alphonse, anime, animes, brotherhood, diorama, edward, figures, full, fullmetal, metal, obj, printer, stl, toy</t>
         </is>
       </c>
       <c r="K115" t="n">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="L115" t="n">
-        <v>10.09523809523809</v>
+        <v>10.025</v>
       </c>
       <c r="M115" t="n">
-        <v>922.1999999999999</v>
+        <v>12030</v>
       </c>
       <c r="N115" t="n">
-        <v>0.1635802469135803</v>
+        <v>0.3730232558139535</v>
       </c>
       <c r="O115" t="b">
         <v>0</v>

--- a/reportes/cults3d_mercado.xlsx
+++ b/reportes/cults3d_mercado.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>126079</v>
+        <v>126080</v>
       </c>
     </row>
     <row r="5">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1863030.73</v>
+        <v>1863053.21</v>
       </c>
     </row>
     <row r="6">
@@ -656,7 +656,7 @@
         <v>60913.77</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4007962389810734</v>
+        <v>0.4005495400187715</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -702,7 +702,7 @@
         <v>61123.16</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3589256134849335</v>
+        <v>0.3588196645551598</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>82770</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3238041921463607</v>
+        <v>0.3236571559336553</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1297,10 +1297,10 @@
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>299978.97</v>
+        <v>300001.45</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3702252693437806</v>
+        <v>0.3695014662756598</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -1346,7 +1346,7 @@
         <v>237887</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3412220309810671</v>
+        <v>0.3404894804637184</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1484,7 +1484,7 @@
         <v>8706</v>
       </c>
       <c r="H20" t="n">
-        <v>0.05816376412713289</v>
+        <v>0.0581391562559921</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1576,7 +1576,7 @@
         <v>47394.09</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1419042913608131</v>
+        <v>0.1417750907456387</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1619,7 +1619,7 @@
         <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>528460.1</v>
+        <v>528482.58</v>
       </c>
       <c r="H23" t="n">
         <v>0.3179524152847873</v>
@@ -1714,7 +1714,7 @@
         <v>37284</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3629764065335753</v>
+        <v>0.3624830086089715</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1760,7 +1760,7 @@
         <v>43989</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2285851780558229</v>
+        <v>0.2285301900408949</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -1806,7 +1806,7 @@
         <v>440995</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3092307692307693</v>
+        <v>0.3086522462562396</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -1852,7 +1852,7 @@
         <v>61904.14</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2996698645108686</v>
+        <v>0.2994619304255147</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -1944,7 +1944,7 @@
         <v>20105.16</v>
       </c>
       <c r="H30" t="n">
-        <v>0.05136445794598138</v>
+        <v>0.05133929884264102</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -2128,7 +2128,7 @@
         <v>49221.2</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2936631380053106</v>
+        <v>0.2932968627466362</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -2174,7 +2174,7 @@
         <v>85275</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2718050776578153</v>
+        <v>0.2717000359805097</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -2312,7 +2312,7 @@
         <v>52375.21</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3480746738824795</v>
+        <v>0.347969632205174</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -2358,7 +2358,7 @@
         <v>68254.03999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3412220309810671</v>
+        <v>0.3404894804637184</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -2447,10 +2447,10 @@
         <v>13.49</v>
       </c>
       <c r="G41" t="n">
-        <v>314707.13</v>
+        <v>314729.61</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3843078056980472</v>
+        <v>0.3839459041639869</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -2818,7 +2818,7 @@
         <v>8263.889999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>0.05361842105263158</v>
+        <v>0.05358316896778435</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -3091,10 +3091,10 @@
         <v>17.5</v>
       </c>
       <c r="G55" t="n">
-        <v>477332.5</v>
+        <v>477354.98</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3474174609819977</v>
+        <v>0.3468023453240667</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -4106,7 +4106,7 @@
         <v>23318.46</v>
       </c>
       <c r="H77" t="n">
-        <v>0.03051868071712057</v>
+        <v>0.03051450465243569</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -4198,7 +4198,7 @@
         <v>19761.93</v>
       </c>
       <c r="H79" t="n">
-        <v>0.02357674439536035</v>
+        <v>0.02357347238736032</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -4290,7 +4290,7 @@
         <v>26870.7</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2253353204172876</v>
+        <v>0.2251340083382966</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -4432,7 +4432,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1714066.05</v>
+        <v>1714088.53</v>
       </c>
       <c r="G2" t="n">
         <v>0.2546607401742899</v>
@@ -4463,7 +4463,7 @@
         <v>54461</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03023255813953488</v>
+        <v>0.03022753695399435</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -4519,7 +4519,7 @@
         <v>38946.4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04090751690391053</v>
+        <v>0.04090567386494535</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -4650,7 +4650,7 @@
         <v>177</v>
       </c>
       <c r="H2" t="n">
-        <v>25600</v>
+        <v>25614</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4670,7 +4670,7 @@
         <v>9489.35</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0330078125</v>
+        <v>0.03298977121886468</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
@@ -4708,7 +4708,7 @@
         <v>1056</v>
       </c>
       <c r="H3" t="n">
-        <v>279757</v>
+        <v>279761</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>30120.96</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01212480831578834</v>
+        <v>0.01212463495626624</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -4766,7 +4766,7 @@
         <v>111</v>
       </c>
       <c r="H4" t="n">
-        <v>44442</v>
+        <v>44446</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4786,7 +4786,7 @@
         <v>6016</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01692093065118581</v>
+        <v>0.01691940782072628</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -4824,7 +4824,7 @@
         <v>29</v>
       </c>
       <c r="H5" t="n">
-        <v>2204</v>
+        <v>2207</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4844,7 +4844,7 @@
         <v>16000</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3629764065335753</v>
+        <v>0.3624830086089715</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -4882,7 +4882,7 @@
         <v>33</v>
       </c>
       <c r="H6" t="n">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4902,7 +4902,7 @@
         <v>15900</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3859223300970874</v>
+        <v>0.3855480116391853</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>36</v>
       </c>
       <c r="H7" t="n">
-        <v>2324</v>
+        <v>2329</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4960,7 +4960,7 @@
         <v>15860</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3412220309810671</v>
+        <v>0.3404894804637184</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -4998,7 +4998,7 @@
         <v>36</v>
       </c>
       <c r="H8" t="n">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -5018,7 +5018,7 @@
         <v>15760</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3405358686257562</v>
+        <v>0.3402417962003454</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>256</v>
       </c>
       <c r="H9" t="n">
-        <v>81257</v>
+        <v>81258</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -5076,7 +5076,7 @@
         <v>9574.970000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02556087475540569</v>
+        <v>0.02556056019099658</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
@@ -5114,7 +5114,7 @@
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>2724</v>
+        <v>2726</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>15600</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2863436123348018</v>
+        <v>0.2861335289801907</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
@@ -5172,7 +5172,7 @@
         <v>26</v>
       </c>
       <c r="H11" t="n">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -5192,7 +5192,7 @@
         <v>15340</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4168478260869565</v>
+        <v>0.4163952225841477</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
@@ -5230,7 +5230,7 @@
         <v>74</v>
       </c>
       <c r="H12" t="n">
-        <v>3355</v>
+        <v>3358</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -5250,7 +5250,7 @@
         <v>15120</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2253353204172876</v>
+        <v>0.2251340083382966</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -5288,7 +5288,7 @@
         <v>54</v>
       </c>
       <c r="H13" t="n">
-        <v>3036</v>
+        <v>3039</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -5308,7 +5308,7 @@
         <v>14420</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2374835309617918</v>
+        <v>0.2372490950970714</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
@@ -5346,7 +5346,7 @@
         <v>39</v>
       </c>
       <c r="H14" t="n">
-        <v>3113</v>
+        <v>3115</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -5366,7 +5366,7 @@
         <v>14160</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2274333440411179</v>
+        <v>0.2272873194221509</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
@@ -5404,7 +5404,7 @@
         <v>11</v>
       </c>
       <c r="H15" t="n">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -5424,7 +5424,7 @@
         <v>13420</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3771781899943789</v>
+        <v>0.3769662921348315</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>81</v>
       </c>
       <c r="H16" t="n">
-        <v>40290</v>
+        <v>40292</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -5482,7 +5482,7 @@
         <v>1005</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0186150409530901</v>
+        <v>0.01861411694629207</v>
       </c>
       <c r="O16" t="b">
         <v>1</v>
@@ -6274,7 +6274,7 @@
         <v>46</v>
       </c>
       <c r="H30" t="n">
-        <v>5784</v>
+        <v>5786</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>19480</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1683955739972338</v>
+        <v>0.1683373660559972</v>
       </c>
       <c r="O30" t="b">
         <v>1</v>
@@ -6332,7 +6332,7 @@
         <v>54</v>
       </c>
       <c r="H31" t="n">
-        <v>3285</v>
+        <v>3286</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -6352,7 +6352,7 @@
         <v>19460</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2961948249619483</v>
+        <v>0.2961046865489957</v>
       </c>
       <c r="O31" t="b">
         <v>1</v>
@@ -6390,7 +6390,7 @@
         <v>25</v>
       </c>
       <c r="H32" t="n">
-        <v>3853</v>
+        <v>3854</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -6410,7 +6410,7 @@
         <v>19080</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2475992732935375</v>
+        <v>0.2475350285417748</v>
       </c>
       <c r="O32" t="b">
         <v>1</v>
@@ -6448,7 +6448,7 @@
         <v>33</v>
       </c>
       <c r="H33" t="n">
-        <v>4156</v>
+        <v>4157</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -6468,7 +6468,7 @@
         <v>19000</v>
       </c>
       <c r="N33" t="n">
-        <v>0.2285851780558229</v>
+        <v>0.2285301900408949</v>
       </c>
       <c r="O33" t="b">
         <v>1</v>
@@ -6564,7 +6564,7 @@
         <v>41</v>
       </c>
       <c r="H35" t="n">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -6584,7 +6584,7 @@
         <v>18680</v>
       </c>
       <c r="N35" t="n">
-        <v>0.2718277066356228</v>
+        <v>0.2717486179807972</v>
       </c>
       <c r="O35" t="b">
         <v>0</v>
@@ -6622,7 +6622,7 @@
         <v>17</v>
       </c>
       <c r="H36" t="n">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -6642,7 +6642,7 @@
         <v>18640</v>
       </c>
       <c r="N36" t="n">
-        <v>0.3058746307843781</v>
+        <v>0.3057742782152231</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
@@ -6680,7 +6680,7 @@
         <v>26</v>
       </c>
       <c r="H37" t="n">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -6700,7 +6700,7 @@
         <v>9060</v>
       </c>
       <c r="N37" t="n">
-        <v>0.3071186440677966</v>
+        <v>0.3067027758970887</v>
       </c>
       <c r="O37" t="b">
         <v>0</v>
@@ -6796,7 +6796,7 @@
         <v>31</v>
       </c>
       <c r="H39" t="n">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -6816,7 +6816,7 @@
         <v>8857.120000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>0.3319292333614153</v>
+        <v>0.3313708999158957</v>
       </c>
       <c r="O39" t="b">
         <v>0</v>
@@ -6854,7 +6854,7 @@
         <v>71</v>
       </c>
       <c r="H40" t="n">
-        <v>11739</v>
+        <v>11740</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6874,7 +6874,7 @@
         <v>2138.68</v>
       </c>
       <c r="N40" t="n">
-        <v>0.04327455490246188</v>
+        <v>0.04327086882453152</v>
       </c>
       <c r="O40" t="b">
         <v>1</v>
@@ -7028,7 +7028,7 @@
         <v>50</v>
       </c>
       <c r="H43" t="n">
-        <v>5055</v>
+        <v>5056</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -7048,7 +7048,7 @@
         <v>16740</v>
       </c>
       <c r="N43" t="n">
-        <v>0.1655786350148368</v>
+        <v>0.1655458860759494</v>
       </c>
       <c r="O43" t="b">
         <v>0</v>
@@ -7086,7 +7086,7 @@
         <v>25</v>
       </c>
       <c r="H44" t="n">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -7106,7 +7106,7 @@
         <v>8497.440000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>0.3702252693437806</v>
+        <v>0.3695014662756598</v>
       </c>
       <c r="O44" t="b">
         <v>0</v>
@@ -7144,7 +7144,7 @@
         <v>39</v>
       </c>
       <c r="H45" t="n">
-        <v>3677</v>
+        <v>3678</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -7164,7 +7164,7 @@
         <v>16540</v>
       </c>
       <c r="N45" t="n">
-        <v>0.2249116127277672</v>
+        <v>0.2248504622077216</v>
       </c>
       <c r="O45" t="b">
         <v>0</v>
@@ -7260,7 +7260,7 @@
         <v>78</v>
       </c>
       <c r="H47" t="n">
-        <v>15351</v>
+        <v>15355</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -7280,7 +7280,7 @@
         <v>2154.24</v>
       </c>
       <c r="N47" t="n">
-        <v>0.02501465702560094</v>
+        <v>0.02500814067079127</v>
       </c>
       <c r="O47" t="b">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -7338,7 +7338,7 @@
         <v>8969.52</v>
       </c>
       <c r="N48" t="n">
-        <v>0.3509234828496042</v>
+        <v>0.3496932515337423</v>
       </c>
       <c r="O48" t="b">
         <v>0</v>
@@ -7376,7 +7376,7 @@
         <v>45</v>
       </c>
       <c r="H49" t="n">
-        <v>2624</v>
+        <v>2627</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -7396,7 +7396,7 @@
         <v>4280</v>
       </c>
       <c r="N49" t="n">
-        <v>0.08155487804878049</v>
+        <v>0.08146174343357442</v>
       </c>
       <c r="O49" t="b">
         <v>1</v>
@@ -7550,7 +7550,7 @@
         <v>94</v>
       </c>
       <c r="H52" t="n">
-        <v>6418</v>
+        <v>6421</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -7570,7 +7570,7 @@
         <v>2172</v>
       </c>
       <c r="N52" t="n">
-        <v>0.05640386413212839</v>
+        <v>0.05637751129107615</v>
       </c>
       <c r="O52" t="b">
         <v>0</v>
@@ -7608,7 +7608,7 @@
         <v>18</v>
       </c>
       <c r="H53" t="n">
-        <v>3444</v>
+        <v>3446</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -7628,7 +7628,7 @@
         <v>4220</v>
       </c>
       <c r="N53" t="n">
-        <v>0.06126596980255517</v>
+        <v>0.0612304120719675</v>
       </c>
       <c r="O53" t="b">
         <v>1</v>
@@ -7840,7 +7840,7 @@
         <v>9</v>
       </c>
       <c r="H57" t="n">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -7860,7 +7860,7 @@
         <v>4734.99</v>
       </c>
       <c r="N57" t="n">
-        <v>0.4465648854961832</v>
+        <v>0.4454314720812182</v>
       </c>
       <c r="O57" t="b">
         <v>0</v>
@@ -7898,7 +7898,7 @@
         <v>10</v>
       </c>
       <c r="H58" t="n">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
@@ -7918,7 +7918,7 @@
         <v>8542.4</v>
       </c>
       <c r="N58" t="n">
-        <v>0.5066666666666667</v>
+        <v>0.5053191489361702</v>
       </c>
       <c r="O58" t="b">
         <v>1</v>
@@ -8072,7 +8072,7 @@
         <v>417</v>
       </c>
       <c r="H61" t="n">
-        <v>53414</v>
+        <v>53416</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -8092,7 +8092,7 @@
         <v>20484.9</v>
       </c>
       <c r="N61" t="n">
-        <v>0.007582281798779346</v>
+        <v>0.007581997903249963</v>
       </c>
       <c r="O61" t="b">
         <v>0</v>
@@ -8420,7 +8420,7 @@
         <v>22</v>
       </c>
       <c r="H67" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
@@ -8440,7 +8440,7 @@
         <v>4020</v>
       </c>
       <c r="N67" t="n">
-        <v>0.3092307692307693</v>
+        <v>0.3078101071975498</v>
       </c>
       <c r="O67" t="b">
         <v>1</v>
@@ -8478,7 +8478,7 @@
         <v>136</v>
       </c>
       <c r="H68" t="n">
-        <v>33728</v>
+        <v>33729</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
@@ -8498,7 +8498,7 @@
         <v>14806</v>
       </c>
       <c r="N68" t="n">
-        <v>0.01995374762808349</v>
+        <v>0.01995315603783095</v>
       </c>
       <c r="O68" t="b">
         <v>0</v>
@@ -8652,7 +8652,7 @@
         <v>41</v>
       </c>
       <c r="H71" t="n">
-        <v>3474</v>
+        <v>3476</v>
       </c>
       <c r="I71" t="b">
         <v>0</v>
@@ -8672,7 +8672,7 @@
         <v>1440</v>
       </c>
       <c r="N71" t="n">
-        <v>0.0690846286701209</v>
+        <v>0.06904487917146145</v>
       </c>
       <c r="O71" t="b">
         <v>0</v>
@@ -8858,12 +8858,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Big Daddy and Little Sister - BioShock</t>
+          <t>Nanami - Jujutsu Kaisen</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971764</t>
+          <t>https://cults3d.com/:4971762</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8872,39 +8872,39 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46292.21871527778</v>
+        <v>46292.2184837963</v>
       </c>
       <c r="E75" t="n">
         <v>22.48</v>
       </c>
       <c r="F75" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G75" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H75" t="n">
-        <v>1087</v>
+        <v>868</v>
       </c>
       <c r="I75" t="b">
         <v>0</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>big daddy, bioshock, fanart, miniature, resin, stl</t>
+          <t>fanart, jujutsu kaisen, miniature, nanami, resin, stl</t>
         </is>
       </c>
       <c r="K75" t="n">
         <v>26</v>
       </c>
       <c r="L75" t="n">
-        <v>13.96153846153846</v>
+        <v>14</v>
       </c>
       <c r="M75" t="n">
-        <v>8160.24</v>
+        <v>8182.72</v>
       </c>
       <c r="N75" t="n">
-        <v>0.3339466421343146</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="O75" t="b">
         <v>0</v>
@@ -8916,12 +8916,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nanami - Jujutsu Kaisen</t>
+          <t>Big Daddy and Little Sister - BioShock</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4971762</t>
+          <t>https://cults3d.com/:4971764</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46292.2184837963</v>
+        <v>46292.21871527778</v>
       </c>
       <c r="E76" t="n">
         <v>22.48</v>
@@ -8939,17 +8939,17 @@
         <v>363</v>
       </c>
       <c r="G76" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H76" t="n">
-        <v>867</v>
+        <v>1089</v>
       </c>
       <c r="I76" t="b">
         <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>fanart, jujutsu kaisen, miniature, nanami, resin, stl</t>
+          <t>big daddy, bioshock, fanart, miniature, resin, stl</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -8962,7 +8962,7 @@
         <v>8160.24</v>
       </c>
       <c r="N76" t="n">
-        <v>0.4186851211072664</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O76" t="b">
         <v>0</v>
@@ -9058,7 +9058,7 @@
         <v>205</v>
       </c>
       <c r="H78" t="n">
-        <v>17252</v>
+        <v>17253</v>
       </c>
       <c r="I78" t="b">
         <v>0</v>
@@ -9078,7 +9078,7 @@
         <v>4580</v>
       </c>
       <c r="N78" t="n">
-        <v>0.02654764664966381</v>
+        <v>0.02654610792325972</v>
       </c>
       <c r="O78" t="b">
         <v>0</v>
@@ -9348,7 +9348,7 @@
         <v>21</v>
       </c>
       <c r="H83" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="I83" t="b">
         <v>0</v>
@@ -9368,7 +9368,7 @@
         <v>6688</v>
       </c>
       <c r="N83" t="n">
-        <v>0.1165644171779141</v>
+        <v>0.1164994425863991</v>
       </c>
       <c r="O83" t="b">
         <v>1</v>
@@ -9406,7 +9406,7 @@
         <v>5</v>
       </c>
       <c r="H84" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I84" t="b">
         <v>0</v>
@@ -9426,7 +9426,7 @@
         <v>4181.9</v>
       </c>
       <c r="N84" t="n">
-        <v>0.6431535269709544</v>
+        <v>0.640495867768595</v>
       </c>
       <c r="O84" t="b">
         <v>0</v>
@@ -9464,7 +9464,7 @@
         <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I85" t="b">
         <v>0</v>
@@ -9484,7 +9484,7 @@
         <v>4141.43</v>
       </c>
       <c r="N85" t="n">
-        <v>0.5348432055749129</v>
+        <v>0.5329861111111112</v>
       </c>
       <c r="O85" t="b">
         <v>0</v>
@@ -9986,7 +9986,7 @@
         <v>42</v>
       </c>
       <c r="H94" t="n">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="I94" t="b">
         <v>0</v>
@@ -10006,7 +10006,7 @@
         <v>5720</v>
       </c>
       <c r="N94" t="n">
-        <v>0.1222744762719111</v>
+        <v>0.1222222222222222</v>
       </c>
       <c r="O94" t="b">
         <v>1</v>
@@ -10044,7 +10044,7 @@
         <v>34</v>
       </c>
       <c r="H95" t="n">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="I95" t="b">
         <v>0</v>
@@ -10064,7 +10064,7 @@
         <v>2780.8</v>
       </c>
       <c r="N95" t="n">
-        <v>0.1661409043112513</v>
+        <v>0.1657922350472193</v>
       </c>
       <c r="O95" t="b">
         <v>1</v>
@@ -10102,7 +10102,7 @@
         <v>50</v>
       </c>
       <c r="H96" t="n">
-        <v>3227</v>
+        <v>3228</v>
       </c>
       <c r="I96" t="b">
         <v>0</v>
@@ -10122,7 +10122,7 @@
         <v>625.6799999999999</v>
       </c>
       <c r="N96" t="n">
-        <v>0.04896188410288194</v>
+        <v>0.04894671623296159</v>
       </c>
       <c r="O96" t="b">
         <v>0</v>
@@ -10160,7 +10160,7 @@
         <v>41</v>
       </c>
       <c r="H97" t="n">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="I97" t="b">
         <v>0</v>
@@ -10180,7 +10180,7 @@
         <v>942</v>
       </c>
       <c r="N97" t="n">
-        <v>0.05992366412213741</v>
+        <v>0.05990080122090805</v>
       </c>
       <c r="O97" t="b">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>70</v>
       </c>
       <c r="H101" t="n">
-        <v>7307</v>
+        <v>7308</v>
       </c>
       <c r="I101" t="b">
         <v>0</v>
@@ -10412,7 +10412,7 @@
         <v>2007</v>
       </c>
       <c r="N101" t="n">
-        <v>0.03051868071712057</v>
+        <v>0.03051450465243569</v>
       </c>
       <c r="O101" t="b">
         <v>0</v>
@@ -10424,12 +10424,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Eve Bust 3D Print</t>
+          <t>Minthara Bust 3D Print</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4747016</t>
+          <t>https://cults3d.com/:4749441</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -10438,39 +10438,39 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46239.1196875</v>
+        <v>46239.73216435185</v>
       </c>
       <c r="E102" t="n">
         <v>15</v>
       </c>
       <c r="F102" t="n">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="G102" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H102" t="n">
-        <v>2486</v>
+        <v>2217</v>
       </c>
       <c r="I102" t="b">
         <v>0</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>adam, bible, christian, eden, eva, eve, garden, genesis, pinup, snake, temptation</t>
+          <t>armor, baldur's, baldurs, bg3, bust, dark, dnd, elf, female, figure, gate, larian, mace, minthara, paladin</t>
         </is>
       </c>
       <c r="K102" t="n">
         <v>79</v>
       </c>
       <c r="L102" t="n">
-        <v>10.60759493670886</v>
+        <v>10.53164556962025</v>
       </c>
       <c r="M102" t="n">
-        <v>12570</v>
+        <v>12480</v>
       </c>
       <c r="N102" t="n">
-        <v>0.337087691069992</v>
+        <v>0.3752819124943618</v>
       </c>
       <c r="O102" t="b">
         <v>0</v>
@@ -10482,12 +10482,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Minthara Bust 3D Print</t>
+          <t>Yuria of Londor Bust 3D Print</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4749441</t>
+          <t>https://cults3d.com/:4749861</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -10496,7 +10496,7 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46239.73216435185</v>
+        <v>46239.81805555556</v>
       </c>
       <c r="E103" t="n">
         <v>15</v>
@@ -10505,17 +10505,17 @@
         <v>832</v>
       </c>
       <c r="G103" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H103" t="n">
-        <v>2217</v>
+        <v>3234</v>
       </c>
       <c r="I103" t="b">
         <v>0</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>armor, baldur's, baldurs, bg3, bust, dark, dnd, elf, female, figure, gate, larian, mace, minthara, paladin</t>
+          <t>dark, fromsoftware, game, londor, religion, role-playing, rpg, souls, video, yuria</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -10528,7 +10528,7 @@
         <v>12480</v>
       </c>
       <c r="N103" t="n">
-        <v>0.3752819124943618</v>
+        <v>0.2572665429808287</v>
       </c>
       <c r="O103" t="b">
         <v>0</v>
@@ -10540,12 +10540,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Yuria of Londor Bust 3D Print</t>
+          <t>Eve Bust 3D Print</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4749861</t>
+          <t>https://cults3d.com/:4747016</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10554,39 +10554,39 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46239.81805555556</v>
+        <v>46239.1196875</v>
       </c>
       <c r="E104" t="n">
         <v>15</v>
       </c>
       <c r="F104" t="n">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="G104" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H104" t="n">
-        <v>3234</v>
+        <v>2486</v>
       </c>
       <c r="I104" t="b">
         <v>0</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>dark, fromsoftware, game, londor, religion, role-playing, rpg, souls, video, yuria</t>
+          <t>adam, bible, christian, eden, eva, eve, garden, genesis, pinup, snake, temptation</t>
         </is>
       </c>
       <c r="K104" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L104" t="n">
-        <v>10.53164556962025</v>
+        <v>10.475</v>
       </c>
       <c r="M104" t="n">
-        <v>12480</v>
+        <v>12570</v>
       </c>
       <c r="N104" t="n">
-        <v>0.2572665429808287</v>
+        <v>0.337087691069992</v>
       </c>
       <c r="O104" t="b">
         <v>0</v>
@@ -10972,7 +10972,7 @@
         <v>62</v>
       </c>
       <c r="H111" t="n">
-        <v>5348</v>
+        <v>5349</v>
       </c>
       <c r="I111" t="b">
         <v>0</v>
@@ -10992,7 +10992,7 @@
         <v>2124</v>
       </c>
       <c r="N111" t="n">
-        <v>0.04412864622288706</v>
+        <v>0.04412039633576369</v>
       </c>
       <c r="O111" t="b">
         <v>0</v>
@@ -11262,7 +11262,7 @@
         <v>37</v>
       </c>
       <c r="H116" t="n">
-        <v>4070</v>
+        <v>4071</v>
       </c>
       <c r="I116" t="b">
         <v>0</v>
@@ -11282,7 +11282,7 @@
         <v>16760</v>
       </c>
       <c r="N116" t="n">
-        <v>0.2058968058968059</v>
+        <v>0.205846229427659</v>
       </c>
       <c r="O116" t="b">
         <v>0</v>
@@ -11320,7 +11320,7 @@
         <v>233</v>
       </c>
       <c r="H117" t="n">
-        <v>30140</v>
+        <v>30141</v>
       </c>
       <c r="I117" t="b">
         <v>0</v>
@@ -11340,7 +11340,7 @@
         <v>1134</v>
       </c>
       <c r="N117" t="n">
-        <v>0.006270736562707366</v>
+        <v>0.006270528515974918</v>
       </c>
       <c r="O117" t="b">
         <v>1</v>
@@ -11378,7 +11378,7 @@
         <v>54</v>
       </c>
       <c r="H118" t="n">
-        <v>3864</v>
+        <v>3866</v>
       </c>
       <c r="I118" t="b">
         <v>0</v>
@@ -11398,7 +11398,7 @@
         <v>1611</v>
       </c>
       <c r="N118" t="n">
-        <v>0.04632505175983437</v>
+        <v>0.0463010863942059</v>
       </c>
       <c r="O118" t="b">
         <v>0</v>
@@ -11436,7 +11436,7 @@
         <v>24</v>
       </c>
       <c r="H119" t="n">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="I119" t="b">
         <v>0</v>
@@ -11456,7 +11456,7 @@
         <v>4140</v>
       </c>
       <c r="N119" t="n">
-        <v>0.1632492113564669</v>
+        <v>0.1631205673758865</v>
       </c>
       <c r="O119" t="b">
         <v>0</v>
@@ -11784,7 +11784,7 @@
         <v>39</v>
       </c>
       <c r="H125" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="I125" t="b">
         <v>0</v>
@@ -11804,7 +11804,7 @@
         <v>6006</v>
       </c>
       <c r="N125" t="n">
-        <v>0.1402157164869029</v>
+        <v>0.1401437371663244</v>
       </c>
       <c r="O125" t="b">
         <v>1</v>
@@ -12074,7 +12074,7 @@
         <v>552</v>
       </c>
       <c r="H130" t="n">
-        <v>50956</v>
+        <v>50958</v>
       </c>
       <c r="I130" t="b">
         <v>0</v>
@@ -12094,7 +12094,7 @@
         <v>2262.56</v>
       </c>
       <c r="N130" t="n">
-        <v>0.01405133840960829</v>
+        <v>0.01405078692256368</v>
       </c>
       <c r="O130" t="b">
         <v>0</v>
@@ -13614,12 +13614,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Raven Stellar Blade Miniature Figure</t>
+          <t>Griffith - Berserk - Bust</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4728114</t>
+          <t>https://cults3d.com/:4845135</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -13628,39 +13628,39 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46234.12288194444</v>
+        <v>46265.17157407408</v>
       </c>
       <c r="E157" t="n">
-        <v>20</v>
+        <v>13.49</v>
       </c>
       <c r="F157" t="n">
-        <v>577</v>
+        <v>364</v>
       </c>
       <c r="G157" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="H157" t="n">
-        <v>3138</v>
+        <v>833</v>
       </c>
       <c r="I157" t="b">
         <v>0</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>fan art, female, figure, game art figurine, garage kit, miniature, miniatures, movie, raven, sculpture, stellar blade, stylized, tabletop, tabletop game, video game</t>
+          <t>anime, band of the hawk, berserk, bust, collectible, griffith, manga, resin, stl, tanuki figures</t>
         </is>
       </c>
       <c r="K157" t="n">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="L157" t="n">
-        <v>6.869047619047619</v>
+        <v>6.867924528301887</v>
       </c>
       <c r="M157" t="n">
-        <v>11540</v>
+        <v>4910.36</v>
       </c>
       <c r="N157" t="n">
-        <v>0.1838750796685787</v>
+        <v>0.4369747899159664</v>
       </c>
       <c r="O157" t="b">
         <v>1</v>
@@ -13672,12 +13672,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Griffith - Berserk - Bust</t>
+          <t>Raven Stellar Blade Miniature Figure</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4845135</t>
+          <t>https://cults3d.com/:4728114</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -13686,39 +13686,39 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46265.17157407408</v>
+        <v>46234.12288194444</v>
       </c>
       <c r="E158" t="n">
-        <v>13.49</v>
+        <v>20</v>
       </c>
       <c r="F158" t="n">
-        <v>364</v>
+        <v>577</v>
       </c>
       <c r="G158" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="H158" t="n">
-        <v>833</v>
+        <v>3138</v>
       </c>
       <c r="I158" t="b">
         <v>0</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>anime, band of the hawk, berserk, bust, collectible, griffith, manga, resin, stl, tanuki figures</t>
+          <t>fan art, female, figure, game art figurine, garage kit, miniature, miniatures, movie, raven, sculpture, stellar blade, stylized, tabletop, tabletop game, video game</t>
         </is>
       </c>
       <c r="K158" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="L158" t="n">
-        <v>6.867924528301887</v>
+        <v>6.788235294117647</v>
       </c>
       <c r="M158" t="n">
-        <v>4910.36</v>
+        <v>11540</v>
       </c>
       <c r="N158" t="n">
-        <v>0.4369747899159664</v>
+        <v>0.1838750796685787</v>
       </c>
       <c r="O158" t="b">
         <v>1</v>
@@ -14858,7 +14858,7 @@
         <v>65</v>
       </c>
       <c r="H178" t="n">
-        <v>7894</v>
+        <v>7895</v>
       </c>
       <c r="I178" t="b">
         <v>0</v>
@@ -14878,7 +14878,7 @@
         <v>1842</v>
       </c>
       <c r="N178" t="n">
-        <v>0.03889029642766658</v>
+        <v>0.03888537048765041</v>
       </c>
       <c r="O178" t="b">
         <v>1</v>
@@ -14916,7 +14916,7 @@
         <v>11</v>
       </c>
       <c r="H179" t="n">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="I179" t="b">
         <v>0</v>
@@ -14936,7 +14936,7 @@
         <v>152.1</v>
       </c>
       <c r="N179" t="n">
-        <v>0.09558823529411764</v>
+        <v>0.09553420011305823</v>
       </c>
       <c r="O179" t="b">
         <v>1</v>
@@ -15032,7 +15032,7 @@
         <v>53</v>
       </c>
       <c r="H181" t="n">
-        <v>4539</v>
+        <v>4541</v>
       </c>
       <c r="I181" t="b">
         <v>0</v>
@@ -15052,7 +15052,7 @@
         <v>1152</v>
       </c>
       <c r="N181" t="n">
-        <v>0.04230006609385327</v>
+        <v>0.04228143580709095</v>
       </c>
       <c r="O181" t="b">
         <v>1</v>
@@ -15090,7 +15090,7 @@
         <v>154</v>
       </c>
       <c r="H182" t="n">
-        <v>28307</v>
+        <v>28308</v>
       </c>
       <c r="I182" t="b">
         <v>0</v>
@@ -15110,7 +15110,7 @@
         <v>799.22</v>
       </c>
       <c r="N182" t="n">
-        <v>0.006288197265693998</v>
+        <v>0.006287975130705101</v>
       </c>
       <c r="O182" t="b">
         <v>0</v>
@@ -15322,7 +15322,7 @@
         <v>18</v>
       </c>
       <c r="H186" t="n">
-        <v>3040</v>
+        <v>3042</v>
       </c>
       <c r="I186" t="b">
         <v>0</v>
@@ -15342,7 +15342,7 @@
         <v>146.7</v>
       </c>
       <c r="N186" t="n">
-        <v>0.05361842105263158</v>
+        <v>0.05358316896778435</v>
       </c>
       <c r="O186" t="b">
         <v>1</v>
@@ -15496,7 +15496,7 @@
         <v>57</v>
       </c>
       <c r="H189" t="n">
-        <v>6489</v>
+        <v>6490</v>
       </c>
       <c r="I189" t="b">
         <v>0</v>
@@ -15516,7 +15516,7 @@
         <v>2520</v>
       </c>
       <c r="N189" t="n">
-        <v>0.06472491909385113</v>
+        <v>0.06471494607087827</v>
       </c>
       <c r="O189" t="b">
         <v>1</v>
@@ -16250,7 +16250,7 @@
         <v>105</v>
       </c>
       <c r="H202" t="n">
-        <v>7943</v>
+        <v>7944</v>
       </c>
       <c r="I202" t="b">
         <v>0</v>
@@ -16270,7 +16270,7 @@
         <v>667.26</v>
       </c>
       <c r="N202" t="n">
-        <v>0.02492760921566159</v>
+        <v>0.02492447129909366</v>
       </c>
       <c r="O202" t="b">
         <v>0</v>
@@ -16362,7 +16362,7 @@
         <v>31</v>
       </c>
       <c r="H204" t="n">
-        <v>15264</v>
+        <v>15265</v>
       </c>
       <c r="I204" t="b">
         <v>0</v>
@@ -16382,7 +16382,7 @@
         <v>272.09</v>
       </c>
       <c r="N204" t="n">
-        <v>0.01054769392033543</v>
+        <v>0.01054700294792008</v>
       </c>
       <c r="O204" t="b">
         <v>1</v>
@@ -16710,7 +16710,7 @@
         <v>45</v>
       </c>
       <c r="H210" t="n">
-        <v>3055</v>
+        <v>3057</v>
       </c>
       <c r="I210" t="b">
         <v>0</v>
@@ -16730,7 +16730,7 @@
         <v>677.16</v>
       </c>
       <c r="N210" t="n">
-        <v>0.05597381342062193</v>
+        <v>0.05593719332679097</v>
       </c>
       <c r="O210" t="b">
         <v>0</v>
@@ -16942,7 +16942,7 @@
         <v>31</v>
       </c>
       <c r="H214" t="n">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="I214" t="b">
         <v>0</v>
@@ -16962,7 +16962,7 @@
         <v>673.2</v>
       </c>
       <c r="N214" t="n">
-        <v>0.05714285714285714</v>
+        <v>0.05712365591397849</v>
       </c>
       <c r="O214" t="b">
         <v>0</v>
@@ -17116,7 +17116,7 @@
         <v>47</v>
       </c>
       <c r="H217" t="n">
-        <v>3185</v>
+        <v>3187</v>
       </c>
       <c r="I217" t="b">
         <v>0</v>
@@ -17136,7 +17136,7 @@
         <v>669.24</v>
       </c>
       <c r="N217" t="n">
-        <v>0.05306122448979592</v>
+        <v>0.0530279259491685</v>
       </c>
       <c r="O217" t="b">
         <v>0</v>
@@ -18044,7 +18044,7 @@
         <v>75</v>
       </c>
       <c r="H233" t="n">
-        <v>4959</v>
+        <v>4961</v>
       </c>
       <c r="I233" t="b">
         <v>0</v>
@@ -18064,7 +18064,7 @@
         <v>7120</v>
       </c>
       <c r="N233" t="n">
-        <v>0.07178866706997379</v>
+        <v>0.07175972586172143</v>
       </c>
       <c r="O233" t="b">
         <v>0</v>
@@ -19548,7 +19548,7 @@
         <v>30</v>
       </c>
       <c r="H259" t="n">
-        <v>5662</v>
+        <v>5663</v>
       </c>
       <c r="I259" t="b">
         <v>0</v>
@@ -19568,7 +19568,7 @@
         <v>1554.72</v>
       </c>
       <c r="N259" t="n">
-        <v>0.02790533380430943</v>
+        <v>0.02790040614515275</v>
       </c>
       <c r="O259" t="b">
         <v>0</v>
@@ -20824,7 +20824,7 @@
         <v>43</v>
       </c>
       <c r="H281" t="n">
-        <v>6020</v>
+        <v>6021</v>
       </c>
       <c r="I281" t="b">
         <v>0</v>
@@ -20844,7 +20844,7 @@
         <v>1137.5</v>
       </c>
       <c r="N281" t="n">
-        <v>0.03023255813953488</v>
+        <v>0.03022753695399435</v>
       </c>
       <c r="O281" t="b">
         <v>0</v>
@@ -21226,7 +21226,7 @@
         <v>45</v>
       </c>
       <c r="H288" t="n">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="I288" t="b">
         <v>0</v>
@@ -21246,7 +21246,7 @@
         <v>792.9599999999999</v>
       </c>
       <c r="N288" t="n">
-        <v>0.04913717461245978</v>
+        <v>0.04912280701754386</v>
       </c>
       <c r="O288" t="b">
         <v>1</v>

--- a/reportes/cults3d_mercado.xlsx
+++ b/reportes/cults3d_mercado.xlsx
@@ -656,7 +656,7 @@
         <v>60913.77</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4005495400187715</v>
+        <v>0.4003854463073142</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>82770</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3236571559336553</v>
+        <v>0.3235103734503937</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1346,7 +1346,7 @@
         <v>237887</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3404894804637184</v>
+        <v>0.3401973401973402</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1484,7 +1484,7 @@
         <v>8706</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0581391562559921</v>
+        <v>0.05810754206150943</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1576,7 +1576,7 @@
         <v>47394.09</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1417750907456387</v>
+        <v>0.1416791231476022</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1714,7 +1714,7 @@
         <v>37284</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3624830086089715</v>
+        <v>0.362154821186057</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1852,7 +1852,7 @@
         <v>61904.14</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2994619304255147</v>
+        <v>0.2992545587041509</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -1944,7 +1944,7 @@
         <v>20105.16</v>
       </c>
       <c r="H30" t="n">
-        <v>0.05133929884264102</v>
+        <v>0.05131257060446902</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -2128,7 +2128,7 @@
         <v>49221.2</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2932968627466362</v>
+        <v>0.2931507926134471</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -2174,7 +2174,7 @@
         <v>85275</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2717000359805097</v>
+        <v>0.2715951483232589</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -2312,7 +2312,7 @@
         <v>52375.21</v>
       </c>
       <c r="H38" t="n">
-        <v>0.347969632205174</v>
+        <v>0.3478647445479232</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -2358,7 +2358,7 @@
         <v>68254.03999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3404894804637184</v>
+        <v>0.3401973401973402</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -2818,7 +2818,7 @@
         <v>8263.889999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>0.05358316896778435</v>
+        <v>0.05354796320630749</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -3094,7 +3094,7 @@
         <v>477354.98</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3468023453240667</v>
+        <v>0.3464964019718937</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -3370,7 +3370,7 @@
         <v>31605.83</v>
       </c>
       <c r="H61" t="n">
-        <v>0.03708928095218044</v>
+        <v>0.03708687015262499</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
@@ -3462,7 +3462,7 @@
         <v>70427.39</v>
       </c>
       <c r="H63" t="n">
-        <v>0.03299709352025988</v>
+        <v>0.03299145299145299</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -3554,7 +3554,7 @@
         <v>134590.8</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1697490092470277</v>
+        <v>0.1696369636963696</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -4014,7 +4014,7 @@
         <v>95143.53999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>0.03592330978809283</v>
+        <v>0.03591606133979015</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
@@ -4106,7 +4106,7 @@
         <v>23318.46</v>
       </c>
       <c r="H77" t="n">
-        <v>0.03051450465243569</v>
+        <v>0.03049364146041296</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -4198,7 +4198,7 @@
         <v>19761.93</v>
       </c>
       <c r="H79" t="n">
-        <v>0.02357347238736032</v>
+        <v>0.0235725208110279</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -4290,7 +4290,7 @@
         <v>26870.7</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2251340083382966</v>
+        <v>0.225</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -4650,7 +4650,7 @@
         <v>177</v>
       </c>
       <c r="H2" t="n">
-        <v>25614</v>
+        <v>25642</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4670,7 +4670,7 @@
         <v>9489.35</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03298977121886468</v>
+        <v>0.03295374775758521</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
@@ -4708,7 +4708,7 @@
         <v>1056</v>
       </c>
       <c r="H3" t="n">
-        <v>279761</v>
+        <v>279763</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>30120.96</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01212463495626624</v>
+        <v>0.01212454827836419</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -4766,7 +4766,7 @@
         <v>111</v>
       </c>
       <c r="H4" t="n">
-        <v>44446</v>
+        <v>44451</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4786,7 +4786,7 @@
         <v>6016</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01691940782072628</v>
+        <v>0.01691750466806146</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -4824,7 +4824,7 @@
         <v>29</v>
       </c>
       <c r="H5" t="n">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4844,7 +4844,7 @@
         <v>16000</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3624830086089715</v>
+        <v>0.362154821186057</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -4882,7 +4882,7 @@
         <v>33</v>
       </c>
       <c r="H6" t="n">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4902,7 +4902,7 @@
         <v>15900</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3855480116391853</v>
+        <v>0.3851744186046512</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>36</v>
       </c>
       <c r="H7" t="n">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4960,7 +4960,7 @@
         <v>15860</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3404894804637184</v>
+        <v>0.3401973401973402</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -4998,7 +4998,7 @@
         <v>36</v>
       </c>
       <c r="H8" t="n">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -5018,7 +5018,7 @@
         <v>15760</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3402417962003454</v>
+        <v>0.3399482312338223</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -5114,7 +5114,7 @@
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>2726</v>
+        <v>2728</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>15600</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2861335289801907</v>
+        <v>0.2859237536656892</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
@@ -5172,7 +5172,7 @@
         <v>26</v>
       </c>
       <c r="H11" t="n">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -5192,7 +5192,7 @@
         <v>15340</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4163952225841477</v>
+        <v>0.415943600867679</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
@@ -5230,7 +5230,7 @@
         <v>74</v>
       </c>
       <c r="H12" t="n">
-        <v>3358</v>
+        <v>3360</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -5250,7 +5250,7 @@
         <v>15120</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2251340083382966</v>
+        <v>0.225</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -5288,7 +5288,7 @@
         <v>54</v>
       </c>
       <c r="H13" t="n">
-        <v>3039</v>
+        <v>3041</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -5308,7 +5308,7 @@
         <v>14420</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2372490950970714</v>
+        <v>0.23709306149293</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
@@ -5346,7 +5346,7 @@
         <v>39</v>
       </c>
       <c r="H14" t="n">
-        <v>3115</v>
+        <v>3117</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -5366,7 +5366,7 @@
         <v>14160</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2272873194221509</v>
+        <v>0.2271414821944177</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>81</v>
       </c>
       <c r="H16" t="n">
-        <v>40292</v>
+        <v>40294</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -5482,7 +5482,7 @@
         <v>1005</v>
       </c>
       <c r="N16" t="n">
-        <v>0.01861411694629207</v>
+        <v>0.01861319303122053</v>
       </c>
       <c r="O16" t="b">
         <v>1</v>
@@ -6680,7 +6680,7 @@
         <v>26</v>
       </c>
       <c r="H37" t="n">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -6700,7 +6700,7 @@
         <v>9060</v>
       </c>
       <c r="N37" t="n">
-        <v>0.3067027758970887</v>
+        <v>0.306288032454361</v>
       </c>
       <c r="O37" t="b">
         <v>0</v>
@@ -7260,7 +7260,7 @@
         <v>78</v>
       </c>
       <c r="H47" t="n">
-        <v>15355</v>
+        <v>15361</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -7280,7 +7280,7 @@
         <v>2154.24</v>
       </c>
       <c r="N47" t="n">
-        <v>0.02500814067079127</v>
+        <v>0.02499837250179025</v>
       </c>
       <c r="O47" t="b">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -7338,7 +7338,7 @@
         <v>8969.52</v>
       </c>
       <c r="N48" t="n">
-        <v>0.3496932515337423</v>
+        <v>0.3490813648293963</v>
       </c>
       <c r="O48" t="b">
         <v>0</v>
@@ -7376,7 +7376,7 @@
         <v>45</v>
       </c>
       <c r="H49" t="n">
-        <v>2627</v>
+        <v>2629</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -7396,7 +7396,7 @@
         <v>4280</v>
       </c>
       <c r="N49" t="n">
-        <v>0.08146174343357442</v>
+        <v>0.08139977177634082</v>
       </c>
       <c r="O49" t="b">
         <v>1</v>
@@ -7550,7 +7550,7 @@
         <v>94</v>
       </c>
       <c r="H52" t="n">
-        <v>6421</v>
+        <v>6423</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -7570,7 +7570,7 @@
         <v>2172</v>
       </c>
       <c r="N52" t="n">
-        <v>0.05637751129107615</v>
+        <v>0.05635995640666355</v>
       </c>
       <c r="O52" t="b">
         <v>0</v>
@@ -7840,7 +7840,7 @@
         <v>9</v>
       </c>
       <c r="H57" t="n">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -7860,7 +7860,7 @@
         <v>4734.99</v>
       </c>
       <c r="N57" t="n">
-        <v>0.4454314720812182</v>
+        <v>0.4448669201520912</v>
       </c>
       <c r="O57" t="b">
         <v>0</v>
@@ -7898,7 +7898,7 @@
         <v>10</v>
       </c>
       <c r="H58" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
@@ -7918,7 +7918,7 @@
         <v>8542.4</v>
       </c>
       <c r="N58" t="n">
-        <v>0.5053191489361702</v>
+        <v>0.5046480743691899</v>
       </c>
       <c r="O58" t="b">
         <v>1</v>
@@ -8072,7 +8072,7 @@
         <v>417</v>
       </c>
       <c r="H61" t="n">
-        <v>53416</v>
+        <v>53420</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -8092,7 +8092,7 @@
         <v>20484.9</v>
       </c>
       <c r="N61" t="n">
-        <v>0.007581997903249963</v>
+        <v>0.007581430175964059</v>
       </c>
       <c r="O61" t="b">
         <v>0</v>
@@ -8420,7 +8420,7 @@
         <v>22</v>
       </c>
       <c r="H67" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
@@ -8440,7 +8440,7 @@
         <v>4020</v>
       </c>
       <c r="N67" t="n">
-        <v>0.3078101071975498</v>
+        <v>0.3073394495412844</v>
       </c>
       <c r="O67" t="b">
         <v>1</v>
@@ -8652,7 +8652,7 @@
         <v>41</v>
       </c>
       <c r="H71" t="n">
-        <v>3476</v>
+        <v>3478</v>
       </c>
       <c r="I71" t="b">
         <v>0</v>
@@ -8672,7 +8672,7 @@
         <v>1440</v>
       </c>
       <c r="N71" t="n">
-        <v>0.06904487917146145</v>
+        <v>0.06900517538815411</v>
       </c>
       <c r="O71" t="b">
         <v>0</v>
@@ -8942,7 +8942,7 @@
         <v>17</v>
       </c>
       <c r="H76" t="n">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="I76" t="b">
         <v>0</v>
@@ -8962,7 +8962,7 @@
         <v>8160.24</v>
       </c>
       <c r="N76" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3324175824175824</v>
       </c>
       <c r="O76" t="b">
         <v>0</v>
@@ -9058,7 +9058,7 @@
         <v>205</v>
       </c>
       <c r="H78" t="n">
-        <v>17253</v>
+        <v>17254</v>
       </c>
       <c r="I78" t="b">
         <v>0</v>
@@ -9078,7 +9078,7 @@
         <v>4580</v>
       </c>
       <c r="N78" t="n">
-        <v>0.02654610792325972</v>
+        <v>0.02654456937521734</v>
       </c>
       <c r="O78" t="b">
         <v>0</v>
@@ -9348,7 +9348,7 @@
         <v>21</v>
       </c>
       <c r="H83" t="n">
-        <v>1794</v>
+        <v>1797</v>
       </c>
       <c r="I83" t="b">
         <v>0</v>
@@ -9368,7 +9368,7 @@
         <v>6688</v>
       </c>
       <c r="N83" t="n">
-        <v>0.1164994425863991</v>
+        <v>0.1163049526989427</v>
       </c>
       <c r="O83" t="b">
         <v>1</v>
@@ -9406,7 +9406,7 @@
         <v>5</v>
       </c>
       <c r="H84" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I84" t="b">
         <v>0</v>
@@ -9426,7 +9426,7 @@
         <v>4181.9</v>
       </c>
       <c r="N84" t="n">
-        <v>0.640495867768595</v>
+        <v>0.6391752577319587</v>
       </c>
       <c r="O84" t="b">
         <v>0</v>
@@ -9464,7 +9464,7 @@
         <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I85" t="b">
         <v>0</v>
@@ -9484,7 +9484,7 @@
         <v>4141.43</v>
       </c>
       <c r="N85" t="n">
-        <v>0.5329861111111112</v>
+        <v>0.5320623916811091</v>
       </c>
       <c r="O85" t="b">
         <v>0</v>
@@ -9812,7 +9812,7 @@
         <v>34</v>
       </c>
       <c r="H91" t="n">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="I91" t="b">
         <v>0</v>
@@ -9832,7 +9832,7 @@
         <v>3828</v>
       </c>
       <c r="N91" t="n">
-        <v>0.1684414327202323</v>
+        <v>0.1677917068466731</v>
       </c>
       <c r="O91" t="b">
         <v>1</v>
@@ -9986,7 +9986,7 @@
         <v>42</v>
       </c>
       <c r="H94" t="n">
-        <v>2340</v>
+        <v>2343</v>
       </c>
       <c r="I94" t="b">
         <v>0</v>
@@ -10006,7 +10006,7 @@
         <v>5720</v>
       </c>
       <c r="N94" t="n">
-        <v>0.1222222222222222</v>
+        <v>0.1220657276995305</v>
       </c>
       <c r="O94" t="b">
         <v>1</v>
@@ -10044,7 +10044,7 @@
         <v>34</v>
       </c>
       <c r="H95" t="n">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="I95" t="b">
         <v>0</v>
@@ -10064,7 +10064,7 @@
         <v>2780.8</v>
       </c>
       <c r="N95" t="n">
-        <v>0.1657922350472193</v>
+        <v>0.1656184486373166</v>
       </c>
       <c r="O95" t="b">
         <v>1</v>
@@ -10102,7 +10102,7 @@
         <v>50</v>
       </c>
       <c r="H96" t="n">
-        <v>3228</v>
+        <v>3230</v>
       </c>
       <c r="I96" t="b">
         <v>0</v>
@@ -10122,7 +10122,7 @@
         <v>625.6799999999999</v>
       </c>
       <c r="N96" t="n">
-        <v>0.04894671623296159</v>
+        <v>0.04891640866873065</v>
       </c>
       <c r="O96" t="b">
         <v>0</v>
@@ -10160,7 +10160,7 @@
         <v>41</v>
       </c>
       <c r="H97" t="n">
-        <v>2621</v>
+        <v>2623</v>
       </c>
       <c r="I97" t="b">
         <v>0</v>
@@ -10180,7 +10180,7 @@
         <v>942</v>
       </c>
       <c r="N97" t="n">
-        <v>0.05990080122090805</v>
+        <v>0.05985512771635532</v>
       </c>
       <c r="O97" t="b">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>70</v>
       </c>
       <c r="H101" t="n">
-        <v>7308</v>
+        <v>7313</v>
       </c>
       <c r="I101" t="b">
         <v>0</v>
@@ -10412,7 +10412,7 @@
         <v>2007</v>
       </c>
       <c r="N101" t="n">
-        <v>0.03051450465243569</v>
+        <v>0.03049364146041296</v>
       </c>
       <c r="O101" t="b">
         <v>0</v>
@@ -10772,12 +10772,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Invisible Woman Bust 3D Print</t>
+          <t>Yuria of Londor 3D Print</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4747045</t>
+          <t>https://cults3d.com/:4729353</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -10786,42 +10786,42 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46239.12717592593</v>
+        <v>46234.49375</v>
       </c>
       <c r="E108" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F108" t="n">
-        <v>822</v>
+        <v>873</v>
       </c>
       <c r="G108" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H108" t="n">
-        <v>2193</v>
+        <v>4345</v>
       </c>
       <c r="I108" t="b">
         <v>0</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>fantastic, fields, force, four, human, invisible, marvel, mr, rivals, storm, susan, torch, woman</t>
+          <t>dark, fromsoftware, game, londor, religion, role-playing, rpg, souls, video, yuria</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L108" t="n">
-        <v>10.40506329113924</v>
+        <v>10.39285714285714</v>
       </c>
       <c r="M108" t="n">
-        <v>12330</v>
+        <v>17460</v>
       </c>
       <c r="N108" t="n">
-        <v>0.3748290013679891</v>
+        <v>0.2009205983889528</v>
       </c>
       <c r="O108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P108" t="b">
         <v>0</v>
@@ -10830,12 +10830,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Yuria of Londor 3D Print</t>
+          <t>Ivy Valentine Bust - Soul Calibur 3D Print</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4729353</t>
+          <t>https://cults3d.com/:4747742</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -10844,39 +10844,39 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46234.49375</v>
+        <v>46239.39113425926</v>
       </c>
       <c r="E109" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F109" t="n">
-        <v>873</v>
+        <v>820</v>
       </c>
       <c r="G109" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H109" t="n">
-        <v>4345</v>
+        <v>2407</v>
       </c>
       <c r="I109" t="b">
         <v>0</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>dark, fromsoftware, game, londor, religion, role-playing, rpg, souls, video, yuria</t>
+          <t>fighter, ivy, ivyvalentine, soulcalibur, sword, valentine, whip</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L109" t="n">
-        <v>10.39285714285714</v>
+        <v>10.37974683544304</v>
       </c>
       <c r="M109" t="n">
-        <v>17460</v>
+        <v>12300</v>
       </c>
       <c r="N109" t="n">
-        <v>0.2009205983889528</v>
+        <v>0.3406730369754882</v>
       </c>
       <c r="O109" t="b">
         <v>0</v>
@@ -10888,12 +10888,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ivy Valentine Bust - Soul Calibur 3D Print</t>
+          <t>Invisible Woman Bust 3D Print</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:4747742</t>
+          <t>https://cults3d.com/:4747045</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10902,42 +10902,42 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46239.39113425926</v>
+        <v>46239.12717592593</v>
       </c>
       <c r="E110" t="n">
         <v>15</v>
       </c>
       <c r="F110" t="n">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="G110" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H110" t="n">
-        <v>2407</v>
+        <v>2193</v>
       </c>
       <c r="I110" t="b">
         <v>0</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>fighter, ivy, ivyvalentine, soulcalibur, sword, valentine, whip</t>
+          <t>fantastic, fields, force, four, human, invisible, marvel, mr, rivals, storm, susan, torch, woman</t>
         </is>
       </c>
       <c r="K110" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L110" t="n">
-        <v>10.37974683544304</v>
+        <v>10.275</v>
       </c>
       <c r="M110" t="n">
-        <v>12300</v>
+        <v>12330</v>
       </c>
       <c r="N110" t="n">
-        <v>0.3406730369754882</v>
+        <v>0.3748290013679891</v>
       </c>
       <c r="O110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" t="b">
         <v>0</v>
@@ -10972,7 +10972,7 @@
         <v>62</v>
       </c>
       <c r="H111" t="n">
-        <v>5349</v>
+        <v>5354</v>
       </c>
       <c r="I111" t="b">
         <v>0</v>
@@ -10992,7 +10992,7 @@
         <v>2124</v>
       </c>
       <c r="N111" t="n">
-        <v>0.04412039633576369</v>
+        <v>0.04407919312663429</v>
       </c>
       <c r="O111" t="b">
         <v>0</v>
@@ -11146,7 +11146,7 @@
         <v>6</v>
       </c>
       <c r="H114" t="n">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="I114" t="b">
         <v>0</v>
@@ -11166,7 +11166,7 @@
         <v>922.1999999999999</v>
       </c>
       <c r="N114" t="n">
-        <v>0.1635802469135803</v>
+        <v>0.1632024634334103</v>
       </c>
       <c r="O114" t="b">
         <v>0</v>
@@ -11320,7 +11320,7 @@
         <v>233</v>
       </c>
       <c r="H117" t="n">
-        <v>30141</v>
+        <v>30145</v>
       </c>
       <c r="I117" t="b">
         <v>0</v>
@@ -11340,7 +11340,7 @@
         <v>1134</v>
       </c>
       <c r="N117" t="n">
-        <v>0.006270528515974918</v>
+        <v>0.006269696467075801</v>
       </c>
       <c r="O117" t="b">
         <v>1</v>
@@ -11378,7 +11378,7 @@
         <v>54</v>
       </c>
       <c r="H118" t="n">
-        <v>3866</v>
+        <v>3869</v>
       </c>
       <c r="I118" t="b">
         <v>0</v>
@@ -11398,7 +11398,7 @@
         <v>1611</v>
       </c>
       <c r="N118" t="n">
-        <v>0.0463010863942059</v>
+        <v>0.04626518480227449</v>
       </c>
       <c r="O118" t="b">
         <v>0</v>
@@ -11436,7 +11436,7 @@
         <v>24</v>
       </c>
       <c r="H119" t="n">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="I119" t="b">
         <v>0</v>
@@ -11456,7 +11456,7 @@
         <v>4140</v>
       </c>
       <c r="N119" t="n">
-        <v>0.1631205673758865</v>
+        <v>0.1627358490566038</v>
       </c>
       <c r="O119" t="b">
         <v>0</v>
@@ -11552,7 +11552,7 @@
         <v>29</v>
       </c>
       <c r="H121" t="n">
-        <v>2988</v>
+        <v>2991</v>
       </c>
       <c r="I121" t="b">
         <v>0</v>
@@ -11572,7 +11572,7 @@
         <v>1218</v>
       </c>
       <c r="N121" t="n">
-        <v>0.0679384203480589</v>
+        <v>0.06787027749916416</v>
       </c>
       <c r="O121" t="b">
         <v>0</v>
@@ -11668,7 +11668,7 @@
         <v>61</v>
       </c>
       <c r="H123" t="n">
-        <v>19786</v>
+        <v>19789</v>
       </c>
       <c r="I123" t="b">
         <v>1</v>
@@ -11688,7 +11688,7 @@
         <v>5850</v>
       </c>
       <c r="N123" t="n">
-        <v>0.01971090670170828</v>
+        <v>0.01970791854060337</v>
       </c>
       <c r="O123" t="b">
         <v>0</v>
@@ -11784,7 +11784,7 @@
         <v>39</v>
       </c>
       <c r="H125" t="n">
-        <v>1948</v>
+        <v>1951</v>
       </c>
       <c r="I125" t="b">
         <v>0</v>
@@ -11804,7 +11804,7 @@
         <v>6006</v>
       </c>
       <c r="N125" t="n">
-        <v>0.1401437371663244</v>
+        <v>0.1399282419272168</v>
       </c>
       <c r="O125" t="b">
         <v>1</v>
@@ -12364,7 +12364,7 @@
         <v>24</v>
       </c>
       <c r="H135" t="n">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="I135" t="b">
         <v>0</v>
@@ -12384,7 +12384,7 @@
         <v>7008</v>
       </c>
       <c r="N135" t="n">
-        <v>0.1931216931216931</v>
+        <v>0.1929940515532056</v>
       </c>
       <c r="O135" t="b">
         <v>1</v>
@@ -13060,7 +13060,7 @@
         <v>60</v>
       </c>
       <c r="H147" t="n">
-        <v>10437</v>
+        <v>10438</v>
       </c>
       <c r="I147" t="b">
         <v>0</v>
@@ -13080,7 +13080,7 @@
         <v>3762</v>
       </c>
       <c r="N147" t="n">
-        <v>0.06007473411899971</v>
+        <v>0.06006897873155777</v>
       </c>
       <c r="O147" t="b">
         <v>1</v>
@@ -13118,7 +13118,7 @@
         <v>271</v>
       </c>
       <c r="H148" t="n">
-        <v>33346</v>
+        <v>33347</v>
       </c>
       <c r="I148" t="b">
         <v>0</v>
@@ -13138,7 +13138,7 @@
         <v>1740</v>
       </c>
       <c r="N148" t="n">
-        <v>0.008696695255802795</v>
+        <v>0.008696434461870633</v>
       </c>
       <c r="O148" t="b">
         <v>0</v>
@@ -13176,7 +13176,7 @@
         <v>29</v>
       </c>
       <c r="H149" t="n">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="I149" t="b">
         <v>0</v>
@@ -13196,7 +13196,7 @@
         <v>6578</v>
       </c>
       <c r="N149" t="n">
-        <v>0.1024674434544208</v>
+        <v>0.1024323398424118</v>
       </c>
       <c r="O149" t="b">
         <v>1</v>
@@ -13930,7 +13930,7 @@
         <v>22</v>
       </c>
       <c r="H162" t="n">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="I162" t="b">
         <v>0</v>
@@ -13950,7 +13950,7 @@
         <v>5760</v>
       </c>
       <c r="N162" t="n">
-        <v>0.2467866323907455</v>
+        <v>0.2465753424657534</v>
       </c>
       <c r="O162" t="b">
         <v>0</v>
@@ -14394,7 +14394,7 @@
         <v>92</v>
       </c>
       <c r="H170" t="n">
-        <v>12175</v>
+        <v>12177</v>
       </c>
       <c r="I170" t="b">
         <v>0</v>
@@ -14414,7 +14414,7 @@
         <v>1001.88</v>
       </c>
       <c r="N170" t="n">
-        <v>0.02078028747433265</v>
+        <v>0.02077687443541102</v>
       </c>
       <c r="O170" t="b">
         <v>1</v>
@@ -14452,7 +14452,7 @@
         <v>88</v>
       </c>
       <c r="H171" t="n">
-        <v>9674</v>
+        <v>9675</v>
       </c>
       <c r="I171" t="b">
         <v>0</v>
@@ -14472,7 +14472,7 @@
         <v>2718</v>
       </c>
       <c r="N171" t="n">
-        <v>0.04682654537936737</v>
+        <v>0.04682170542635659</v>
       </c>
       <c r="O171" t="b">
         <v>1</v>
@@ -14568,7 +14568,7 @@
         <v>68</v>
       </c>
       <c r="H173" t="n">
-        <v>5849</v>
+        <v>5850</v>
       </c>
       <c r="I173" t="b">
         <v>0</v>
@@ -14588,7 +14588,7 @@
         <v>1737</v>
       </c>
       <c r="N173" t="n">
-        <v>0.03299709352025988</v>
+        <v>0.03299145299145299</v>
       </c>
       <c r="O173" t="b">
         <v>0</v>
@@ -14916,7 +14916,7 @@
         <v>11</v>
       </c>
       <c r="H179" t="n">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="I179" t="b">
         <v>0</v>
@@ -14936,7 +14936,7 @@
         <v>152.1</v>
       </c>
       <c r="N179" t="n">
-        <v>0.09553420011305823</v>
+        <v>0.09542631281761717</v>
       </c>
       <c r="O179" t="b">
         <v>1</v>
@@ -14974,7 +14974,7 @@
         <v>69</v>
       </c>
       <c r="H180" t="n">
-        <v>7620</v>
+        <v>7621</v>
       </c>
       <c r="I180" t="b">
         <v>0</v>
@@ -14994,7 +14994,7 @@
         <v>1108.8</v>
       </c>
       <c r="N180" t="n">
-        <v>0.03674540682414698</v>
+        <v>0.03674058522503609</v>
       </c>
       <c r="O180" t="b">
         <v>1</v>
@@ -15032,7 +15032,7 @@
         <v>53</v>
       </c>
       <c r="H181" t="n">
-        <v>4541</v>
+        <v>4543</v>
       </c>
       <c r="I181" t="b">
         <v>0</v>
@@ -15052,7 +15052,7 @@
         <v>1152</v>
       </c>
       <c r="N181" t="n">
-        <v>0.04228143580709095</v>
+        <v>0.04226282192383887</v>
       </c>
       <c r="O181" t="b">
         <v>1</v>
@@ -15090,7 +15090,7 @@
         <v>154</v>
       </c>
       <c r="H182" t="n">
-        <v>28308</v>
+        <v>28311</v>
       </c>
       <c r="I182" t="b">
         <v>0</v>
@@ -15110,7 +15110,7 @@
         <v>799.22</v>
       </c>
       <c r="N182" t="n">
-        <v>0.006287975130705101</v>
+        <v>0.006287308819893328</v>
       </c>
       <c r="O182" t="b">
         <v>0</v>
@@ -15322,7 +15322,7 @@
         <v>18</v>
       </c>
       <c r="H186" t="n">
-        <v>3042</v>
+        <v>3044</v>
       </c>
       <c r="I186" t="b">
         <v>0</v>
@@ -15342,7 +15342,7 @@
         <v>146.7</v>
       </c>
       <c r="N186" t="n">
-        <v>0.05358316896778435</v>
+        <v>0.05354796320630749</v>
       </c>
       <c r="O186" t="b">
         <v>1</v>
@@ -15438,7 +15438,7 @@
         <v>20</v>
       </c>
       <c r="H188" t="n">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="I188" t="b">
         <v>0</v>
@@ -15458,7 +15458,7 @@
         <v>6226</v>
       </c>
       <c r="N188" t="n">
-        <v>0.1606129398410897</v>
+        <v>0.1605218377765173</v>
       </c>
       <c r="O188" t="b">
         <v>0</v>
@@ -15496,7 +15496,7 @@
         <v>57</v>
       </c>
       <c r="H189" t="n">
-        <v>6490</v>
+        <v>6492</v>
       </c>
       <c r="I189" t="b">
         <v>0</v>
@@ -15516,7 +15516,7 @@
         <v>2520</v>
       </c>
       <c r="N189" t="n">
-        <v>0.06471494607087827</v>
+        <v>0.06469500924214418</v>
       </c>
       <c r="O189" t="b">
         <v>1</v>
@@ -15612,7 +15612,7 @@
         <v>87</v>
       </c>
       <c r="H191" t="n">
-        <v>7066</v>
+        <v>7067</v>
       </c>
       <c r="I191" t="b">
         <v>0</v>
@@ -15632,7 +15632,7 @@
         <v>2502</v>
       </c>
       <c r="N191" t="n">
-        <v>0.05901500141522785</v>
+        <v>0.05900665062968728</v>
       </c>
       <c r="O191" t="b">
         <v>1</v>
@@ -15902,7 +15902,7 @@
         <v>37</v>
       </c>
       <c r="H196" t="n">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="I196" t="b">
         <v>0</v>
@@ -15922,7 +15922,7 @@
         <v>7128</v>
       </c>
       <c r="N196" t="n">
-        <v>0.1105047748976808</v>
+        <v>0.1104670985339243</v>
       </c>
       <c r="O196" t="b">
         <v>1</v>
@@ -16362,7 +16362,7 @@
         <v>31</v>
       </c>
       <c r="H204" t="n">
-        <v>15265</v>
+        <v>15266</v>
       </c>
       <c r="I204" t="b">
         <v>0</v>
@@ -16382,7 +16382,7 @@
         <v>272.09</v>
       </c>
       <c r="N204" t="n">
-        <v>0.01054700294792008</v>
+        <v>0.01054631206602908</v>
       </c>
       <c r="O204" t="b">
         <v>1</v>
@@ -16710,7 +16710,7 @@
         <v>45</v>
       </c>
       <c r="H210" t="n">
-        <v>3057</v>
+        <v>3059</v>
       </c>
       <c r="I210" t="b">
         <v>0</v>
@@ -16730,7 +16730,7 @@
         <v>677.16</v>
       </c>
       <c r="N210" t="n">
-        <v>0.05593719332679097</v>
+        <v>0.05590062111801242</v>
       </c>
       <c r="O210" t="b">
         <v>0</v>
@@ -17174,7 +17174,7 @@
         <v>233</v>
       </c>
       <c r="H218" t="n">
-        <v>39534</v>
+        <v>39536</v>
       </c>
       <c r="I218" t="b">
         <v>0</v>
@@ -17194,7 +17194,7 @@
         <v>9788.16</v>
       </c>
       <c r="N218" t="n">
-        <v>0.009713158294126575</v>
+        <v>0.00971266693646297</v>
       </c>
       <c r="O218" t="b">
         <v>0</v>
@@ -17406,7 +17406,7 @@
         <v>24</v>
       </c>
       <c r="H222" t="n">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="I222" t="b">
         <v>0</v>
@@ -17426,7 +17426,7 @@
         <v>5654</v>
       </c>
       <c r="N222" t="n">
-        <v>0.1697490092470277</v>
+        <v>0.1696369636963696</v>
       </c>
       <c r="O222" t="b">
         <v>1</v>
@@ -17464,7 +17464,7 @@
         <v>89</v>
       </c>
       <c r="H223" t="n">
-        <v>8009</v>
+        <v>8010</v>
       </c>
       <c r="I223" t="b">
         <v>0</v>
@@ -17484,7 +17484,7 @@
         <v>1698</v>
       </c>
       <c r="N223" t="n">
-        <v>0.03533524784617306</v>
+        <v>0.03533083645443196</v>
       </c>
       <c r="O223" t="b">
         <v>0</v>
@@ -17522,7 +17522,7 @@
         <v>52</v>
       </c>
       <c r="H224" t="n">
-        <v>3897</v>
+        <v>3898</v>
       </c>
       <c r="I224" t="b">
         <v>0</v>
@@ -17542,7 +17542,7 @@
         <v>736.5599999999999</v>
       </c>
       <c r="N224" t="n">
-        <v>0.04772902232486528</v>
+        <v>0.04771677783478707</v>
       </c>
       <c r="O224" t="b">
         <v>0</v>
@@ -17928,7 +17928,7 @@
         <v>25</v>
       </c>
       <c r="H231" t="n">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="I231" t="b">
         <v>0</v>
@@ -17948,7 +17948,7 @@
         <v>7200</v>
       </c>
       <c r="N231" t="n">
-        <v>0.1647446457990115</v>
+        <v>0.1646542261251372</v>
       </c>
       <c r="O231" t="b">
         <v>0</v>
@@ -18450,7 +18450,7 @@
         <v>85</v>
       </c>
       <c r="H240" t="n">
-        <v>3653</v>
+        <v>3654</v>
       </c>
       <c r="I240" t="b">
         <v>0</v>
@@ -18470,7 +18470,7 @@
         <v>1679.92</v>
       </c>
       <c r="N240" t="n">
-        <v>0.04544210238160416</v>
+        <v>0.04542966611932129</v>
       </c>
       <c r="O240" t="b">
         <v>0</v>
@@ -18508,7 +18508,7 @@
         <v>41</v>
       </c>
       <c r="H241" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="I241" t="b">
         <v>0</v>
@@ -18528,7 +18528,7 @@
         <v>6710</v>
       </c>
       <c r="N241" t="n">
-        <v>0.1500245941957698</v>
+        <v>0.1499508357915438</v>
       </c>
       <c r="O241" t="b">
         <v>0</v>
@@ -19548,7 +19548,7 @@
         <v>30</v>
       </c>
       <c r="H259" t="n">
-        <v>5663</v>
+        <v>5667</v>
       </c>
       <c r="I259" t="b">
         <v>0</v>
@@ -19568,7 +19568,7 @@
         <v>1554.72</v>
       </c>
       <c r="N259" t="n">
-        <v>0.02790040614515275</v>
+        <v>0.02788071289924122</v>
       </c>
       <c r="O259" t="b">
         <v>0</v>
@@ -19838,7 +19838,7 @@
         <v>18</v>
       </c>
       <c r="H264" t="n">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="I264" t="b">
         <v>0</v>
@@ -19858,7 +19858,7 @@
         <v>5240</v>
       </c>
       <c r="N264" t="n">
-        <v>0.197289156626506</v>
+        <v>0.1971407072987209</v>
       </c>
       <c r="O264" t="b">
         <v>0</v>
@@ -20244,7 +20244,7 @@
         <v>32</v>
       </c>
       <c r="H271" t="n">
-        <v>3748</v>
+        <v>3749</v>
       </c>
       <c r="I271" t="b">
         <v>0</v>
@@ -20264,7 +20264,7 @@
         <v>1038</v>
       </c>
       <c r="N271" t="n">
-        <v>0.04615795090715048</v>
+        <v>0.0461456388370232</v>
       </c>
       <c r="O271" t="b">
         <v>0</v>
@@ -20418,7 +20418,7 @@
         <v>68</v>
       </c>
       <c r="H274" t="n">
-        <v>8700</v>
+        <v>8701</v>
       </c>
       <c r="I274" t="b">
         <v>0</v>
@@ -20438,7 +20438,7 @@
         <v>902.88</v>
       </c>
       <c r="N274" t="n">
-        <v>0.02620689655172414</v>
+        <v>0.02620388461096426</v>
       </c>
       <c r="O274" t="b">
         <v>1</v>
@@ -20650,7 +20650,7 @@
         <v>49</v>
       </c>
       <c r="H278" t="n">
-        <v>4955</v>
+        <v>4956</v>
       </c>
       <c r="I278" t="b">
         <v>0</v>
@@ -20670,7 +20670,7 @@
         <v>704.88</v>
       </c>
       <c r="N278" t="n">
-        <v>0.03592330978809283</v>
+        <v>0.03591606133979015</v>
       </c>
       <c r="O278" t="b">
         <v>1</v>
